--- a/outputs/aasted3_run_comparison/summary/aasted3_reference_based_comparison_summary.xlsx
+++ b/outputs/aasted3_run_comparison/summary/aasted3_reference_based_comparison_summary.xlsx
@@ -16,11 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contour Overview" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$C$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sensor Coordinates'!$A$1:$E$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mechanical By Zone'!$A$1:$EP$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Hotspot Summary'!$A$1:$S$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mechanical By Zone'!$A$1:$EP$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Hotspot Summary'!$A$1:$AE$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +56,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB84"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8696B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0063BE7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -89,6 +114,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -529,7 +559,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2971800" cy="1485900"/>
@@ -554,7 +584,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2971800" cy="1485900"/>
@@ -577,9 +607,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2971800" cy="1485900"/>
@@ -602,7 +632,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>53</row>
       <rowOff>0</rowOff>
@@ -627,7 +657,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>53</row>
       <rowOff>0</rowOff>
@@ -652,9 +682,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2971800" cy="1485900"/>
@@ -677,7 +707,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>62</row>
       <rowOff>0</rowOff>
@@ -702,7 +732,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>62</row>
       <rowOff>0</rowOff>
@@ -727,9 +757,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2971800" cy="1485900"/>
@@ -752,7 +782,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>71</row>
       <rowOff>0</rowOff>
@@ -777,7 +807,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>71</row>
       <rowOff>0</rowOff>
@@ -802,9 +832,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2971800" cy="1485900"/>
@@ -815,6 +845,106 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2971800" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2971800" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2971800" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2971800" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1117,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1204,36 +1334,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A separate repeatability analysis can be added when multiple repetitions are uploaded. That mode should compare runs within a setup, quantify CV/spread, inspect detachment patterns, and use an optional xxx_summary input for landmarks and metadata.</t>
+          <t>A separate repeatability analysis can be added when multiple repetitions are uploaded. That mode should compare runs within a setup, quantify CV/spread, inspect detachment patterns, and use an optional xxx_summary or parameter_summary input for landmarks and metadata.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mechanical outlier roadmap</t>
+          <t>Aasted detachment offset</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mechanical-zone outlier detection should be trained from accumulated reference/repeatability runs. The current output summarizes all available IMU axes by zone; future calibration can define expected ranges by line, mould, conveyor speed, and zone.</t>
+          <t>Optional architecture is installed. When a parameter_summary file is placed in inputs/aasted3, the report can mark crystallization onset, detachment onset, and complete/partial ultrasound detachment offsets using positive change points and a pre-deposition reference minus 10% threshold.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Demoulding subclasses</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The former broad demoulding zone is split into demoulding_twisting, demoulding_vibration, and final_demoulding. Twisting is identified from the acc-z plateau drop with the acc-x negative-parabola movement; vibration uses elevated IMU variability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mechanical outlier roadmap</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mechanical-zone outlier detection should be trained from accumulated reference/repeatability runs. The current output summarizes all available IMU axes by zone; future calibration can define expected ranges by line, mould, conveyor speed, and zone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Prompt keywords to provide</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Please specify: analysis_mode = reference_based_comparison or repeatability_analysis; line_profile = Aasted-3; reference_run; comparison labels; conveyor_belt_speed; raw_data files; optional xxx_summary file; and desired customer/report detail level.</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Please specify: analysis_mode = reference_based_comparison or repeatability_analysis; line_profile = Aasted-3; reference_run; comparison labels; conveyor_belt_speed; raw_data files; optional parameter_summary/xxx_summary file; detachment_threshold_percent if not 10%; and desired customer/report detail level.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1515,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1779,125 +1933,99 @@
       <c r="A80" t="n">
         <v>1786</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" t="n">
+        <v>1802</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>demoulding_twisting</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>First demoulding subphase: acc z shifts from high plateau to low plateau while acc x shows a negative parabolic movement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>demoulding_vibration</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Second demoulding subphase: vibration/shaking visible in acc z, acc x/y, and gyro y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>run_end</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>demoulding</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Demoulding zone / run end.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>final_demoulding</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Final demoulding/run-out after twisting and vibration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Detected Zones</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
+      <c r="B86" s="1" t="inlineStr">
         <is>
           <t>zone</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>detected_start_s</t>
         </is>
       </c>
-      <c r="D84" s="1" t="inlineStr">
+      <c r="D86" s="1" t="inlineStr">
         <is>
           <t>detected_end_s</t>
         </is>
       </c>
-      <c r="E84" s="1" t="inlineStr">
+      <c r="E86" s="1" t="inlineStr">
         <is>
           <t>duration_s</t>
         </is>
       </c>
-      <c r="F84" s="1" t="inlineStr">
+      <c r="F86" s="1" t="inlineStr">
         <is>
           <t>detection_basis</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
+      <c r="G86" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>reference_2291-4160</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>movement_to_conditioning</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>20</v>
-      </c>
-      <c r="E85" t="n">
-        <v>20</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>first warm-up/IMU-change landmark</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>reference_2291-4160</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>mould_conditioning</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>20</v>
-      </c>
-      <c r="D86" t="n">
-        <v>212</v>
-      </c>
-      <c r="E86" t="n">
-        <v>192</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>T8 high/conditioning phase before deposition event</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1909,21 +2037,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>deposition_transfer</t>
+          <t>movement_to_conditioning</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="E87" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>pre-vibration deposition/transfer IMU event</t>
+          <t>first warm-up/IMU-change landmark</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -1940,26 +2068,26 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>vibration_warming</t>
+          <t>mould_conditioning</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
-        <v>430</v>
+        <v>212</v>
       </c>
       <c r="E88" t="n">
-        <v>118</v>
+        <v>192</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>longest sustained high gyro-y variability segment</t>
+          <t>T8 high/conditioning phase before deposition event</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1971,26 +2099,26 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>transition_to_cooling</t>
+          <t>deposition_transfer</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>430</v>
+        <v>212</v>
       </c>
       <c r="D89" t="n">
-        <v>514</v>
+        <v>312</v>
       </c>
       <c r="E89" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>post-vibration transition until first T8 valley</t>
+          <t>pre-vibration deposition/transfer IMU event</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2130,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>cooling_1</t>
+          <t>vibration_warming</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>514</v>
+        <v>312</v>
       </c>
       <c r="D90" t="n">
-        <v>613</v>
+        <v>430</v>
       </c>
       <c r="E90" t="n">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>T8 valley-to-valley cooling cycle</t>
+          <t>longest sustained high gyro-y variability segment</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2033,21 +2161,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>cooling_2</t>
+          <t>transition_to_cooling</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>613</v>
+        <v>430</v>
       </c>
       <c r="D91" t="n">
-        <v>751</v>
+        <v>514</v>
       </c>
       <c r="E91" t="n">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>T8 valley-to-valley cooling cycle</t>
+          <t>post-vibration transition until first T8 valley</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -2064,17 +2192,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>cooling_3</t>
+          <t>cooling_1</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>751</v>
+        <v>514</v>
       </c>
       <c r="D92" t="n">
-        <v>889</v>
+        <v>613</v>
       </c>
       <c r="E92" t="n">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -2095,14 +2223,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>cooling_4</t>
+          <t>cooling_2</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>889</v>
+        <v>613</v>
       </c>
       <c r="D93" t="n">
-        <v>1027</v>
+        <v>751</v>
       </c>
       <c r="E93" t="n">
         <v>138</v>
@@ -2126,26 +2254,26 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>less_periodic_cooling_2</t>
+          <t>cooling_3</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1027</v>
+        <v>751</v>
       </c>
       <c r="D94" t="n">
-        <v>1629</v>
+        <v>889</v>
       </c>
       <c r="E94" t="n">
-        <v>602</v>
+        <v>138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>after periodic valleys until the last cold T8 minimum</t>
+          <t>T8 valley-to-valley cooling cycle</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -2157,26 +2285,26 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>transition_2</t>
+          <t>cooling_4</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1629</v>
+        <v>889</v>
       </c>
       <c r="D95" t="n">
-        <v>1792</v>
+        <v>1027</v>
       </c>
       <c r="E95" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>last cold T8 minimum until sharp acc-z regime change</t>
+          <t>T8 valley-to-valley cooling cycle</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -2188,21 +2316,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>demoulding</t>
+          <t>less_periodic_cooling_2</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1792</v>
+        <v>1027</v>
       </c>
       <c r="D96" t="n">
-        <v>1869</v>
+        <v>1629</v>
       </c>
       <c r="E96" t="n">
-        <v>77</v>
+        <v>602</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>after sharp acc-z regime change</t>
+          <t>after periodic valleys until the last cold T8 minimum</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -2214,26 +2342,26 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>reference_2291-4160</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>movement_to_conditioning</t>
+          <t>transition_2</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1629</v>
       </c>
       <c r="D97" t="n">
-        <v>67</v>
+        <v>1792</v>
       </c>
       <c r="E97" t="n">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>first warm-up/IMU-change landmark</t>
+          <t>last cold T8 minimum until sharp acc-z regime change</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -2245,26 +2373,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>reference_2291-4160</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>mould_conditioning</t>
+          <t>demoulding_twisting</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>67</v>
+        <v>1792</v>
       </c>
       <c r="D98" t="n">
-        <v>493</v>
+        <v>1799</v>
       </c>
       <c r="E98" t="n">
-        <v>426</v>
+        <v>7</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>T8 high/conditioning phase before deposition event</t>
+          <t>acc-z plateau drop with acc-x negative parabolic movement</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -2276,26 +2404,26 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>reference_2291-4160</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>deposition_transfer</t>
+          <t>demoulding_vibration</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>493</v>
+        <v>1799</v>
       </c>
       <c r="D99" t="n">
-        <v>600</v>
+        <v>1860</v>
       </c>
       <c r="E99" t="n">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>pre-vibration deposition/transfer IMU event</t>
+          <t>high IMU variability during demoulding vibration/shaking</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -2307,31 +2435,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>reference_2291-4160</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>vibration_warming</t>
+          <t>final_demoulding</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>600</v>
+        <v>1860</v>
       </c>
       <c r="D100" t="n">
-        <v>646</v>
+        <v>1869</v>
       </c>
       <c r="E100" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>longest sustained high gyro-y variability segment</t>
+          <t>after twisting/vibration subphases</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -2343,26 +2471,26 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>transition_to_cooling</t>
+          <t>movement_to_conditioning</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>646</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>794</v>
+        <v>67</v>
       </c>
       <c r="E101" t="n">
-        <v>148</v>
+        <v>67</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>post-vibration transition until first T8 valley</t>
+          <t>first warm-up/IMU-change landmark</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -2374,26 +2502,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>cooling_1</t>
+          <t>mould_conditioning</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>794</v>
+        <v>67</v>
       </c>
       <c r="D102" t="n">
-        <v>891</v>
+        <v>493</v>
       </c>
       <c r="E102" t="n">
-        <v>97</v>
+        <v>426</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>T8 valley-to-valley cooling cycle</t>
+          <t>T8 high/conditioning phase before deposition event</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -2405,26 +2533,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>cooling_2</t>
+          <t>deposition_transfer</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>891</v>
+        <v>493</v>
       </c>
       <c r="D103" t="n">
-        <v>1040</v>
+        <v>600</v>
       </c>
       <c r="E103" t="n">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>T8 valley-to-valley cooling cycle</t>
+          <t>pre-vibration deposition/transfer IMU event</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -2436,21 +2564,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>cooling_3</t>
+          <t>vibration_warming</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1040</v>
+        <v>600</v>
       </c>
       <c r="D104" t="n">
-        <v>1152</v>
+        <v>646</v>
       </c>
       <c r="E104" t="n">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>T8 valley-to-valley cooling cycle</t>
+          <t>longest sustained high gyro-y variability segment</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -2467,21 +2595,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>cooling_4</t>
+          <t>transition_to_cooling</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1152</v>
+        <v>646</v>
       </c>
       <c r="D105" t="n">
-        <v>1307</v>
+        <v>794</v>
       </c>
       <c r="E105" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>T8 valley-to-valley cooling cycle</t>
+          <t>post-vibration transition until first T8 valley</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -2498,26 +2626,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>less_periodic_cooling_2</t>
+          <t>cooling_1</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1307</v>
+        <v>794</v>
       </c>
       <c r="D106" t="n">
-        <v>2035</v>
+        <v>891</v>
       </c>
       <c r="E106" t="n">
-        <v>728</v>
+        <v>97</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>after periodic valleys until the last cold T8 minimum</t>
+          <t>T8 valley-to-valley cooling cycle</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -2529,26 +2657,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>transition_2</t>
+          <t>cooling_2</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2035</v>
+        <v>891</v>
       </c>
       <c r="D107" t="n">
-        <v>2074</v>
+        <v>1040</v>
       </c>
       <c r="E107" t="n">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>last cold T8 minimum until sharp acc-z regime change</t>
+          <t>T8 valley-to-valley cooling cycle</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -2560,24 +2688,210 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>demoulding</t>
+          <t>cooling_3</t>
         </is>
       </c>
       <c r="C108" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1152</v>
+      </c>
+      <c r="E108" t="n">
+        <v>112</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>T8 valley-to-valley cooling cycle</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>cooling_4</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1152</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1307</v>
+      </c>
+      <c r="E109" t="n">
+        <v>155</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>T8 valley-to-valley cooling cycle</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1307</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E110" t="n">
+        <v>728</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>after periodic valleys until the last cold T8 minimum</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D111" t="n">
         <v>2074</v>
       </c>
-      <c r="D108" t="n">
+      <c r="E111" t="n">
+        <v>39</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>last cold T8 minimum until sharp acc-z regime change</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>demoulding_twisting</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2074</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2081</v>
+      </c>
+      <c r="E112" t="n">
+        <v>7</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>acc-z plateau drop with acc-x negative parabolic movement</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>demoulding_vibration</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2081</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2137</v>
+      </c>
+      <c r="E113" t="n">
+        <v>56</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>high IMU variability during demoulding vibration/shaking</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>final_demoulding</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2137</v>
+      </c>
+      <c r="D114" t="n">
         <v>2141</v>
       </c>
-      <c r="E108" t="n">
-        <v>67</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>after sharp acc-z regime change</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="E114" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>after twisting/vibration subphases</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
@@ -2917,13 +3231,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP13"/>
+  <dimension ref="A1:EP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
@@ -2947,7 +3261,7 @@
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="22" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
-    <col width="23" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="28" max="28"/>
     <col width="23" customWidth="1" min="29" max="29"/>
     <col width="23" customWidth="1" min="30" max="30"/>
     <col width="24" customWidth="1" min="31" max="31"/>
@@ -2960,13 +3274,13 @@
     <col width="24" customWidth="1" min="38" max="38"/>
     <col width="25" customWidth="1" min="39" max="39"/>
     <col width="23" customWidth="1" min="40" max="40"/>
-    <col width="21" customWidth="1" min="41" max="41"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
     <col width="22" customWidth="1" min="42" max="42"/>
     <col width="23" customWidth="1" min="43" max="43"/>
     <col width="22" customWidth="1" min="44" max="44"/>
     <col width="21" customWidth="1" min="45" max="45"/>
     <col width="24" customWidth="1" min="46" max="46"/>
-    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="21" customWidth="1" min="47" max="47"/>
     <col width="21" customWidth="1" min="48" max="48"/>
     <col width="23" customWidth="1" min="49" max="49"/>
     <col width="27" customWidth="1" min="50" max="50"/>
@@ -2992,7 +3306,7 @@
     <col width="23" customWidth="1" min="70" max="70"/>
     <col width="22" customWidth="1" min="71" max="71"/>
     <col width="23" customWidth="1" min="72" max="72"/>
-    <col width="21" customWidth="1" min="73" max="73"/>
+    <col width="22" customWidth="1" min="73" max="73"/>
     <col width="22" customWidth="1" min="74" max="74"/>
     <col width="22" customWidth="1" min="75" max="75"/>
     <col width="21" customWidth="1" min="76" max="76"/>
@@ -3010,7 +3324,7 @@
     <col width="20" customWidth="1" min="88" max="88"/>
     <col width="21" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="20" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="91" max="91"/>
     <col width="22" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
     <col width="20" customWidth="1" min="94" max="94"/>
@@ -7197,53 +7511,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>demoulding</t>
+          <t>demoulding_twisting</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.01130231457251</v>
+        <v>14.49742265559647</v>
       </c>
       <c r="C13" t="n">
-        <v>3.677666389867866</v>
+        <v>14.43367521011945</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.33363592470465</v>
+        <v>-0.06374744547701283</v>
       </c>
       <c r="E13" t="n">
         <v>14.20034571757199</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>14.25749227231675</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.20034571757199</v>
+        <v>0.05714655474475983</v>
       </c>
       <c r="H13" t="n">
-        <v>15.53041402035055</v>
+        <v>14.82870623734175</v>
       </c>
       <c r="I13" t="n">
         <v>14.7544988175028</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.775915202847747</v>
+        <v>-0.0742074198389453</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1317376874201422</v>
+        <v>-0.4324332827613467</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1451862018451065</v>
+        <v>0.4306960997649636</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2769238892652487</v>
+        <v>0.8631293825263103</v>
       </c>
       <c r="N13" t="n">
         <v>-1.018379720052083</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1897103445870536</v>
+        <v>-0.08220563616071429</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8286693754650298</v>
+        <v>0.9361740838913691</v>
       </c>
       <c r="Q13" t="n">
         <v>0.2397242954799107</v>
@@ -7255,257 +7569,875 @@
         <v>0.7193707057407924</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1151023994125711</v>
+        <v>0.07617369600752434</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2024618852425928</v>
+        <v>0.1052209363566788</v>
       </c>
       <c r="V13" t="n">
-        <v>0.08735948583002165</v>
+        <v>0.02904724034915442</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4812295450520206</v>
+        <v>0.1098489657970348</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5820993324314896</v>
+        <v>0.1575590771362023</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1008697873794689</v>
+        <v>0.04771011133916742</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01126959448228347</v>
+        <v>0.01253711155482701</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.008592761740442595</v>
+        <v>0.004369085139689891</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.002676832741840877</v>
+        <v>-0.008168026415137117</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.1444539388020833</v>
+        <v>0.001408168247767857</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.2064412434895833</v>
+        <v>-0.03071376255580357</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.06198730468750002</v>
+        <v>-0.03212193080357143</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1012776692708333</v>
+        <v>0.02457275390625</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1648021024816176</v>
+        <v>0.03753226143973214</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.06352443321078431</v>
+        <v>0.01295950753348214</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.05728850330784077</v>
+        <v>0.01851910029483202</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.1038901010209172</v>
+        <v>0.03900766086476064</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.04660159771307647</v>
+        <v>0.02048856056992862</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.2886369942310333</v>
+        <v>0.04627222640629541</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.4538691620719058</v>
+        <v>0.1482201269330228</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.1652321678408724</v>
+        <v>0.1019479005267274</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.2567680938443899</v>
+        <v>-0.09403174264090403</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.4065257448241751</v>
+        <v>-0.303638758068582</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.1497576509797852</v>
+        <v>-0.209607015427678</v>
       </c>
       <c r="AR13" t="n">
-        <v>-1.107861328125</v>
+        <v>-1.058197021484375</v>
       </c>
       <c r="AS13" t="n">
-        <v>-1.110547746930804</v>
+        <v>-1.035204206194196</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0.002686418805803559</v>
+        <v>0.0229928152901786</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.9851161411830357</v>
+        <v>0.96290283203125</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9691423688616071</v>
+        <v>0.9316580636160714</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.0159737723214286</v>
+        <v>-0.03124476841517865</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1761245312328704</v>
+        <v>0.07077589391420286</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.285402521591819</v>
+        <v>0.09701509007116607</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.1092779903589486</v>
+        <v>0.02623919615696321</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.784037328503847</v>
+        <v>0.1223441067077776</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.8769106469510897</v>
+        <v>0.4165853543073419</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.09287331844724267</v>
+        <v>0.2942412475995643</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.872421423594157</v>
+        <v>2.855185508728027</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.63624656555203</v>
+        <v>2.736930848318707</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.2361748580421263</v>
+        <v>-0.1182546604093204</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.094004313151042</v>
+        <v>2.790842692057292</v>
       </c>
       <c r="BH13" t="n">
-        <v>1.483612060546875</v>
+        <v>2.557643010066106</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0.6103922526041665</v>
+        <v>-0.2331996819911857</v>
       </c>
       <c r="BJ13" t="n">
-        <v>3.177144368489583</v>
+        <v>2.90399169921875</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.944661458333333</v>
+        <v>2.827634811401367</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.76751708984375</v>
+        <v>-0.07635688781738281</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1259074864862618</v>
+        <v>0.04390776704750006</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.1518625490801041</v>
+        <v>0.04318624485842018</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.02595506259384234</v>
+        <v>-0.000721522189079879</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.16385111524374</v>
+        <v>0.2881960173604484</v>
       </c>
       <c r="BQ13" t="n">
-        <v>9.771337498075601</v>
+        <v>0.4028865948428108</v>
       </c>
       <c r="BR13" t="n">
-        <v>7.607486382831861</v>
+        <v>0.1146905774823624</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.7799816131591797</v>
+        <v>-8.790884335835775</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.867163162534527</v>
+        <v>11.19820891332842</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.08718154937534728</v>
+        <v>19.98909324916419</v>
       </c>
       <c r="BV13" t="n">
         <v>-14.37241617838542</v>
       </c>
       <c r="BW13" t="n">
-        <v>-35.63499450683594</v>
+        <v>0.8444118499755859</v>
       </c>
       <c r="BX13" t="n">
-        <v>-21.26257832845052</v>
+        <v>15.216828028361</v>
       </c>
       <c r="BY13" t="n">
-        <v>36.60744222005209</v>
+        <v>10.39382934570312</v>
       </c>
       <c r="BZ13" t="n">
         <v>17.37663269042969</v>
       </c>
       <c r="CA13" t="n">
-        <v>-19.2308095296224</v>
+        <v>6.982803344726562</v>
       </c>
       <c r="CB13" t="n">
-        <v>1.215024831089745</v>
+        <v>0.7414155434648886</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.316972123579633</v>
+        <v>0.5195591635692463</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.1019472924898879</v>
+        <v>-0.2218563798956423</v>
       </c>
       <c r="CE13" t="n">
         <v>26.59142000089429</v>
       </c>
       <c r="CF13" t="n">
+        <v>7.484639730278748</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-19.10678027061554</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.2814995447794596</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.256102310610273</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.5376018553897326</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>-0.3972676595052083</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.1216227213541667</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.518890380859375</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.1550191243489583</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.3483312270220588</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.5033503513710171</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.03228909205465462</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.03152779941720309</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0.0007612926374515327</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.1193437356268778</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.1334836719062131</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.01413993627933534</v>
+      </c>
+      <c r="EP13" t="inlineStr">
+        <is>
+          <t>accz_mean, accz_std_max, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>demoulding_vibration</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15.00867485258736</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.062123464972064</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-13.9465513876153</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14.84843215741797</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-14.84843215741797</v>
+      </c>
+      <c r="H14" t="n">
+        <v>15.2994612462175</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14.74957189784413</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.5498893483733678</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.01431806049649678</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.02352225683442448</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.03784031733092125</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.1965738932291667</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.1897103445870536</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.006863548642113082</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1647420247395833</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2794886997767857</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1147466750372024</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.203294208885351</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3150056625725148</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.1117114536871638</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.4812295450520206</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.5820993324314896</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1008697873794689</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.01315987602112785</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.01125218250736793</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.001907693513759924</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.1444539388020833</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.2064412434895833</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.06198730468750002</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.1012776692708333</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.1648021024816176</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.06352443321078431</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.1175548099216634</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.163334172971003</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.04577936304933963</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.2886369942310333</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.4538691620719058</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.1652321678408724</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.7164576999724858</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.6569878542049332</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.05946984576755254</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-1.107861328125</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-1.110547746930804</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.002686418805803559</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.05612386067708333</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.18402099609375</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.1278971354166667</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.4385086273258404</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.5080532246784194</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.06954459735257901</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.784037328503847</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.8769106469510897</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.09287331844724267</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.842143469386631</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.65692098108352</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-0.1852224883031104</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.094004313151042</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1.483612060546875</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.6103922526041665</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>3.177144368489583</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4.944661458333333</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.76751708984375</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.2593075201789777</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.5148270463204843</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.2555195261415066</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>2.16385111524374</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>9.771337498075601</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>7.607486382831861</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.7197978496551514</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.6426614839986319</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.07713636565651949</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-5.347412109375</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-1.619796752929688</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>3.727615356445312</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>4.432749430338542</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.855743408203125</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-2.577006022135417</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>2.075586046789703</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>1.582785215130517</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0.4928008316591859</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>22.5282095683739</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>6.10520854242738</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-16.42300102594652</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0.3245222436057196</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.1505842247220246</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.4751064683277442</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>-0.411224365234375</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0.133087158203125</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.27813720703125</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.15850830078125</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>2.234319051106771</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>2.392827351888021</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.05188680804443932</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.06465956043617892</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.0127727523917396</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.2481847208578424</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>8.485398067312611</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>8.237213346454768</v>
+      </c>
+      <c r="EP14" t="inlineStr">
+        <is>
+          <t>T8_mean_C, T8_min_C, accz_max, gyroy_min, gyroy_max, gyroy_std_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>final_demoulding</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>15.4287119505177</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-15.4287119505177</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15.25266533836246</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-15.25266533836246</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15.53041402035055</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-15.53041402035055</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.1729883157639276</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2042745748201625</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3772628905840901</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1.010013834635417</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.07151576450892858</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.938498070126488</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.0024658203125</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8729291643415179</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.8753949846540179</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.06559392053429372</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0957755062072706</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.03018158567297688</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2615593490545352</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.2024618852425928</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.05909746381194242</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.005718905131022136</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.00513986722618735</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.0005790379048347854</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.01410293579101562</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.02025059291294643</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.006147657121930803</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.02061767578125</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.04551914760044643</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.02490147181919643</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.02409795487220774</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.02689893786533508</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.002800982993127341</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.05941739688803158</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.07521430945653504</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.01579691256850346</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.7162978799002511</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.2346245260799633</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.4816733538202878</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-1.00379638671875</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-1.055472237723214</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.05167585100446415</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.9851161411830357</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.9691423688616071</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.0159737723214286</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.1074189482035251</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.111948057390637</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.004529109187111885</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.2040557624812072</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.231237624666706</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.02718186218549873</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.958877245585124</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.466347301707548</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.4925299438775754</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.850657145182292</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.150115966796875</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0.7005411783854165</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>3.151224772135417</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>2.626558191636029</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0.5246665804993871</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.0472483149533426</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.04946471092345637</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.00221639597011377</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.1709387096002497</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.1652052463274597</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-0.005733463272790035</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.581115404764811</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-9.528309391994101</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-18.10942479675891</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.14654541015625</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-35.63499450683594</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-35.78153991699219</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>36.60744222005209</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1.971206665039062</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-34.63623555501302</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.6301560131480808</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>1.22382115738351</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.5936651442354297</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>26.50985891421001</v>
+      </c>
+      <c r="CF15" t="n">
         <v>9.901150423267513</v>
       </c>
-      <c r="CG13" t="n">
-        <v>-16.69026957762678</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>-0.3006326887342665</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>0.1433085578806787</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>0.4439412466149452</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>-0.411224365234375</v>
-      </c>
-      <c r="CL13" t="n">
+      <c r="CG15" t="n">
+        <v>-16.6087084909425</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0.2586042722066244</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.0006311080035041368</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.2592353802101285</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-0.2935892740885417</v>
+      </c>
+      <c r="CL15" t="n">
         <v>-0.330047607421875</v>
       </c>
-      <c r="CM13" t="n">
-        <v>0.0811767578125</v>
-      </c>
-      <c r="CN13" t="n">
+      <c r="CM15" t="n">
+        <v>-0.03645833333333331</v>
+      </c>
+      <c r="CN15" t="n">
         <v>-0.1530253092447917</v>
       </c>
-      <c r="CO13" t="n">
-        <v>2.234319051106771</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>2.387344360351562</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>0.04654933222140449</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>0.046334737625986</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>-0.0002145945954184908</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>0.2481847208578424</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>8.485398067312611</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>8.237213346454768</v>
-      </c>
-      <c r="EP13" t="inlineStr">
-        <is>
-          <t>T8_mean_C, T8_min_C, accz_mean, accz_std_median, gyroy_min, gyroy_max, gyroy_std_max</t>
+      <c r="CO15" t="n">
+        <v>0.128173828125</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.2811991373697916</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.04797070426271448</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.04265045357662846</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0.00532025068608602</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0.1462930595588686</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0.13944277976718</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0.00685027979168859</v>
+      </c>
+      <c r="EP15" t="inlineStr">
+        <is>
+          <t>T8_mean_C, T8_min_C, T8_max_C, accz_mean, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_median, gyroy_std_max</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:EP13"/>
-  <conditionalFormatting sqref="D2:D13">
+  <autoFilter ref="A1:EP15"/>
+  <conditionalFormatting sqref="D2:D15">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7517,7 +8449,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7529,7 +8461,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J13">
+  <conditionalFormatting sqref="J2:J15">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7541,7 +8473,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M13">
+  <conditionalFormatting sqref="M2:M15">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -7553,7 +8485,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P13">
+  <conditionalFormatting sqref="P2:P15">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -7565,7 +8497,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S13">
+  <conditionalFormatting sqref="S2:S15">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -7577,7 +8509,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V13">
+  <conditionalFormatting sqref="V2:V15">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -7589,7 +8521,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y13">
+  <conditionalFormatting sqref="Y2:Y15">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -7601,7 +8533,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AB13">
+  <conditionalFormatting sqref="AB2:AB15">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -7613,7 +8545,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE13">
+  <conditionalFormatting sqref="AE2:AE15">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -7625,7 +8557,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH13">
+  <conditionalFormatting sqref="AH2:AH15">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -7637,7 +8569,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK2:AK13">
+  <conditionalFormatting sqref="AK2:AK15">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -7649,7 +8581,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN13">
+  <conditionalFormatting sqref="AN2:AN15">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -7661,7 +8593,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AQ2:AQ13">
+  <conditionalFormatting sqref="AQ2:AQ15">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -7673,7 +8605,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT2:AT13">
+  <conditionalFormatting sqref="AT2:AT15">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -7685,7 +8617,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AW2:AW13">
+  <conditionalFormatting sqref="AW2:AW15">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -7697,7 +8629,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ2:AZ13">
+  <conditionalFormatting sqref="AZ2:AZ15">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -7709,7 +8641,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC13">
+  <conditionalFormatting sqref="BC2:BC15">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -7721,7 +8653,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF2:BF13">
+  <conditionalFormatting sqref="BF2:BF15">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -7733,7 +8665,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI13">
+  <conditionalFormatting sqref="BI2:BI15">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -7745,7 +8677,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BL2:BL13">
+  <conditionalFormatting sqref="BL2:BL15">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -7757,7 +8689,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO13">
+  <conditionalFormatting sqref="BO2:BO15">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -7769,7 +8701,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BR2:BR13">
+  <conditionalFormatting sqref="BR2:BR15">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -7781,7 +8713,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BU13">
+  <conditionalFormatting sqref="BU2:BU15">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -7793,7 +8725,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX2:BX13">
+  <conditionalFormatting sqref="BX2:BX15">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -7805,7 +8737,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA2:CA13">
+  <conditionalFormatting sqref="CA2:CA15">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -7817,7 +8749,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CD2:CD13">
+  <conditionalFormatting sqref="CD2:CD15">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -7829,7 +8761,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CG2:CG13">
+  <conditionalFormatting sqref="CG2:CG15">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
@@ -7841,7 +8773,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CJ2:CJ13">
+  <conditionalFormatting sqref="CJ2:CJ15">
     <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
@@ -7853,7 +8785,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CM2:CM13">
+  <conditionalFormatting sqref="CM2:CM15">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -7865,7 +8797,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP13">
+  <conditionalFormatting sqref="CP2:CP15">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
@@ -7877,7 +8809,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS13">
+  <conditionalFormatting sqref="CS2:CS15">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -7889,7 +8821,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CV2:CV13">
+  <conditionalFormatting sqref="CV2:CV15">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -7901,7 +8833,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CY2:CY13">
+  <conditionalFormatting sqref="CY2:CY15">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -7913,7 +8845,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DB2:DB13">
+  <conditionalFormatting sqref="DB2:DB15">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -7925,7 +8857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE13">
+  <conditionalFormatting sqref="DE2:DE15">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -7937,7 +8869,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DH2:DH13">
+  <conditionalFormatting sqref="DH2:DH15">
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -7949,7 +8881,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK13">
+  <conditionalFormatting sqref="DK2:DK15">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
@@ -7961,7 +8893,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN13">
+  <conditionalFormatting sqref="DN2:DN15">
     <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
@@ -7973,7 +8905,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DQ2:DQ13">
+  <conditionalFormatting sqref="DQ2:DQ15">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -7985,7 +8917,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DT2:DT13">
+  <conditionalFormatting sqref="DT2:DT15">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -7997,7 +8929,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DW2:DW13">
+  <conditionalFormatting sqref="DW2:DW15">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
@@ -8009,7 +8941,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DZ2:DZ13">
+  <conditionalFormatting sqref="DZ2:DZ15">
     <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
@@ -8021,7 +8953,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EC2:EC13">
+  <conditionalFormatting sqref="EC2:EC15">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
@@ -8033,7 +8965,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EF2:EF13">
+  <conditionalFormatting sqref="EF2:EF15">
     <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
@@ -8045,7 +8977,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EI2:EI13">
+  <conditionalFormatting sqref="EI2:EI15">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -8057,7 +8989,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EL2:EL13">
+  <conditionalFormatting sqref="EL2:EL15">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -8069,7 +9001,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EO2:EO13">
+  <conditionalFormatting sqref="EO2:EO15">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
@@ -8091,7 +9023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:AE29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8102,17 +9034,29 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="28" max="28"/>
+    <col width="23" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8158,57 +9102,117 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>spread_severity</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>spread_color</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>plain_language</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>T2_mean_C</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>T2_vs_zone_mean_C</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>T2_thermal_class</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>T2_color</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>T3_mean_C</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>T3_vs_zone_mean_C</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>T3_thermal_class</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>T3_color</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>T4_mean_C</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>T4_vs_zone_mean_C</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>T4_thermal_class</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>T4_color</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>T5_mean_C</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>T5_vs_zone_mean_C</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>T5_thermal_class</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>T5_color</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>T7_mean_C</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>T7_vs_zone_mean_C</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T7_thermal_class</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>T7_color</t>
         </is>
       </c>
     </row>
@@ -8245,40 +9249,100 @@
       <c r="H2" t="n">
         <v>0.8742187500000007</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>T2 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>15.167578125</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.5641601562500007</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>14.59453125</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>-0.008886718750000355</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
         <v>14.36484375</v>
       </c>
-      <c r="O2" t="n">
+      <c r="U2" t="n">
         <v>-0.2385742187499993</v>
       </c>
-      <c r="P2" t="n">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W2" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
         <v>14.293359375</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Y2" t="n">
         <v>-0.31005859375</v>
       </c>
-      <c r="R2" t="n">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
         <v>14.59677734375</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AC2" t="n">
         <v>-0.006640624999999289</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE2" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -8314,40 +9378,100 @@
       <c r="H3" t="n">
         <v>0.5709228515625</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>#63BE7B</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>T2 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>19.01611328125</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.1637898763020829</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>18.4451904296875</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>-0.4071329752604171</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
         <v>18.91620890299479</v>
       </c>
-      <c r="O3" t="n">
+      <c r="U3" t="n">
         <v>0.06388549804687571</v>
       </c>
-      <c r="P3" t="n">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
         <v>19.00696818033854</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Y3" t="n">
         <v>0.1546447753906257</v>
       </c>
-      <c r="R3" t="n">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
         <v>18.87713623046875</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AC3" t="n">
         <v>0.02481282552083286</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE3" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -8383,40 +9507,100 @@
       <c r="H4" t="n">
         <v>1.245058593750002</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>T5 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>27.79275390625</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.2731445312499936</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>26.85166015625</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>-0.6679492187500067</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
         <v>27.36544921875</v>
       </c>
-      <c r="O4" t="n">
+      <c r="U4" t="n">
         <v>-0.1541601562500041</v>
       </c>
-      <c r="P4" t="n">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W4" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
         <v>28.09671875</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Y4" t="n">
         <v>0.5771093749999956</v>
       </c>
-      <c r="R4" t="n">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AA4" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
         <v>27.49146484375</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AC4" t="n">
         <v>-0.02814453125000682</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE4" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -8452,40 +9636,100 @@
       <c r="H5" t="n">
         <v>0.8856428760593218</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>T5 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>27.98963850635593</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.3380594544491551</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>27.19102555614407</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>-0.4605534957627064</v>
       </c>
-      <c r="N5" t="n">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
         <v>27.32574152542373</v>
       </c>
-      <c r="O5" t="n">
+      <c r="U5" t="n">
         <v>-0.3258375264830455</v>
       </c>
-      <c r="P5" t="n">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
         <v>28.07666843220339</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Y5" t="n">
         <v>0.4250893802966154</v>
       </c>
-      <c r="R5" t="n">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
         <v>27.67482123940678</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AC5" t="n">
         <v>0.02324218750000284</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE5" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -8521,40 +9765,100 @@
       <c r="H6" t="n">
         <v>0.9803059895833321</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>T2 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>27.31231398809524</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.4313151041666643</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>26.33200799851191</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>-0.5489908854166679</v>
       </c>
-      <c r="N6" t="n">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
         <v>26.52632068452381</v>
       </c>
-      <c r="O6" t="n">
+      <c r="U6" t="n">
         <v>-0.3546781994047628</v>
       </c>
-      <c r="P6" t="n">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
         <v>27.23151506696428</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Y6" t="n">
         <v>0.3505161830357117</v>
       </c>
-      <c r="R6" t="n">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
         <v>27.00283668154762</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AC6" t="n">
         <v>0.1218377976190474</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE6" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -8590,40 +9894,100 @@
       <c r="H7" t="n">
         <v>1.398138552295919</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>T2 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>25.80986926020408</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.7528021364795947</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>24.41173070790816</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>-0.6453364158163239</v>
       </c>
-      <c r="N7" t="n">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
         <v>24.64887595663265</v>
       </c>
-      <c r="O7" t="n">
+      <c r="U7" t="n">
         <v>-0.4081911670918323</v>
       </c>
-      <c r="P7" t="n">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>24.90377869897959</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Y7" t="n">
         <v>-0.1532884247448933</v>
       </c>
-      <c r="R7" t="n">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
         <v>25.51108099489796</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AC7" t="n">
         <v>0.4540138711734727</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE7" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -8659,40 +10023,100 @@
       <c r="H8" t="n">
         <v>1.814920176630434</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>T2 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>22.56736865942029</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.9842759284420275</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>20.75244848278986</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>-0.8306442481884062</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
         <v>21.42372905344203</v>
       </c>
-      <c r="O8" t="n">
+      <c r="U8" t="n">
         <v>-0.1593636775362341</v>
       </c>
-      <c r="P8" t="n">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>20.80525362318841</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Y8" t="n">
         <v>-0.7778391077898554</v>
       </c>
-      <c r="R8" t="n">
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="AA8" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
         <v>22.36666383605073</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AC8" t="n">
         <v>0.7835711050724647</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AE8" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -8728,40 +10152,100 @@
       <c r="H9" t="n">
         <v>1.638756793478262</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>T7 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>20.34771286231884</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.7674139492753618</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>18.87812783061594</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>-0.7021710824275367</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
         <v>19.47552932518116</v>
       </c>
-      <c r="O9" t="n">
+      <c r="U9" t="n">
         <v>-0.104769587862318</v>
       </c>
-      <c r="P9" t="n">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
         <v>18.78068387681159</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Y9" t="n">
         <v>-0.7996150362318843</v>
       </c>
-      <c r="R9" t="n">
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="AA9" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
         <v>20.41944067028986</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AC9" t="n">
         <v>0.8391417572463773</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AE9" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -8797,40 +10281,100 @@
       <c r="H10" t="n">
         <v>1.901706861413047</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>T7 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>19.23427592844203</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.7560320425724605</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>17.86638077445652</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>-0.6118631114130437</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
         <v>18.55492810235507</v>
       </c>
-      <c r="O10" t="n">
+      <c r="U10" t="n">
         <v>0.07668421648550705</v>
       </c>
-      <c r="P10" t="n">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>17.41696388134058</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Y10" t="n">
         <v>-1.061280004528989</v>
       </c>
-      <c r="R10" t="n">
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="AA10" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
         <v>19.31867074275362</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AC10" t="n">
         <v>0.8404268568840578</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AE10" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -8866,40 +10410,100 @@
       <c r="H11" t="n">
         <v>2.011099070805647</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>T2 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>16.76053454630399</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.9534987541528235</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>15.46631346034053</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>-0.3407223318106318</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
         <v>15.80788647217608</v>
       </c>
-      <c r="O11" t="n">
+      <c r="U11" t="n">
         <v>0.0008506800249161728</v>
       </c>
-      <c r="P11" t="n">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
         <v>14.74943547549834</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Y11" t="n">
         <v>-1.057600316652824</v>
       </c>
-      <c r="R11" t="n">
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="AA11" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
         <v>16.25100900643688</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AC11" t="n">
         <v>0.4439732142857142</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE11" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8935,40 +10539,100 @@
       <c r="H12" t="n">
         <v>1.391827839176829</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>T2 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>14.49927353277439</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.8461961699695113</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>13.4185165777439</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>-0.2345607850609763</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
         <v>13.30859375</v>
       </c>
-      <c r="O12" t="n">
+      <c r="U12" t="n">
         <v>-0.3444836128048792</v>
       </c>
-      <c r="P12" t="n">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>13.10744569359756</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Y12" t="n">
         <v>-0.5456316692073173</v>
       </c>
-      <c r="R12" t="n">
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="AA12" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
         <v>13.93155725990854</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AC12" t="n">
         <v>0.2784798971036579</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -8979,11 +10643,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>demoulding</t>
+          <t>demoulding_twisting</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.39944118923611</v>
+        <v>14.21041666666667</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -8991,7 +10655,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15.28274197048611</v>
+        <v>15.13020833333333</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -8999,183 +10663,363 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13.92442491319444</v>
+        <v>13.67447916666667</v>
       </c>
       <c r="H13" t="n">
-        <v>1.358317057291666</v>
-      </c>
-      <c r="I13" t="inlineStr">
+        <v>1.455729166666668</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>T2 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>15.28274197048611</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.8833007812500018</v>
-      </c>
       <c r="L13" t="n">
-        <v>14.17510308159722</v>
+        <v>15.13020833333333</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2243381076388875</v>
-      </c>
-      <c r="N13" t="n">
-        <v>14.03700086805556</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-0.3624403211805536</v>
+        <v>0.9197916666666686</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
       <c r="P13" t="n">
-        <v>13.92442491319444</v>
+        <v>13.97721354166667</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.4750162760416643</v>
-      </c>
-      <c r="R13" t="n">
-        <v>14.57793511284722</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.1784939236111125</v>
+        <v>-0.2332031249999993</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>13.87109375</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.3393229166666654</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>13.67447916666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.5359374999999993</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="AA13" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>14.39908854166667</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.1886718750000007</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>reference_2291-4160</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>movement_to_conditioning</t>
+          <t>demoulding_vibration</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.23661221590909</v>
+        <v>14.39102909482759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>15.27720905172414</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>22.62479285037879</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
       <c r="G14" t="n">
-        <v>21.84537760416667</v>
+        <v>13.91594827586207</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7794152462121211</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>T5 is warmest and T4 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>22.12476325757576</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.1118489583333364</v>
+        <v>1.361260775862069</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T5 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L14" t="n">
-        <v>22.38299005681818</v>
+        <v>15.27720905172414</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1463778409090892</v>
-      </c>
-      <c r="N14" t="n">
-        <v>21.84537760416667</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-0.3912346117424264</v>
+        <v>0.8861799568965516</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
       <c r="P14" t="n">
-        <v>22.62479285037879</v>
+        <v>14.1669921875</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3881806344696948</v>
-      </c>
-      <c r="R14" t="n">
-        <v>22.20513731060606</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.03147490530303187</v>
+        <v>-0.2240369073275872</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>14.02693965517241</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.3640894396551726</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>13.91594827586207</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.4750808189655178</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>14.56805630387931</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.1770272090517224</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>reference_2291-4160</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mould_conditioning</t>
+          <t>final_demoulding</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.44869883362676</v>
+        <v>14.602197265625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>22.73446669600939</v>
+        <v>15.437255859375</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>22.15354955252348</v>
+        <v>14.17333984375</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5809171434859124</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>T3 is warmest and T4 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>22.32362272593897</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.1250761076877893</v>
+        <v>1.263916015625</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T5 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L15" t="n">
-        <v>22.73446669600939</v>
+        <v>15.437255859375</v>
       </c>
       <c r="M15" t="n">
-        <v>0.285767862382631</v>
-      </c>
-      <c r="N15" t="n">
-        <v>22.15354955252348</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.2951492811032814</v>
+        <v>0.8350585937500004</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
       <c r="P15" t="n">
-        <v>22.69943423562206</v>
+        <v>14.38232421875</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.250735401995307</v>
-      </c>
-      <c r="R15" t="n">
-        <v>22.33242095803991</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.1162778755868494</v>
+        <v>-0.2198730468749996</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>14.234375</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.3678222656249996</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>14.17333984375</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.4288574218749996</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>14.78369140625</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.1814941406250004</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -9186,65 +11030,125 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deposition_transfer</t>
+          <t>movement_to_conditioning</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.24799262152778</v>
+        <v>22.23661221590909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>28.89122178819444</v>
+        <v>22.62479285037879</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>27.84138093171296</v>
+        <v>21.84537760416667</v>
       </c>
       <c r="H16" t="n">
-        <v>1.049840856481481</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>T3 is warmest and T2 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>27.84138093171296</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.4066116898148167</v>
+        <v>0.7794152462121211</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T5 is warmest and T4 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L16" t="n">
-        <v>28.89122178819444</v>
+        <v>22.12476325757576</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6432291666666643</v>
-      </c>
-      <c r="N16" t="n">
-        <v>28.3255931712963</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.07760054976851904</v>
+        <v>-0.1118489583333364</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
       <c r="P16" t="n">
-        <v>28.19858579282407</v>
+        <v>22.38299005681818</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.04940682870370594</v>
-      </c>
-      <c r="R16" t="n">
-        <v>27.98318142361111</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.2648111979166679</v>
+        <v>0.1463778409090892</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>21.84537760416667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.3912346117424264</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>22.62479285037879</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.3881806344696948</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>22.20513731060606</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.03147490530303187</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -9255,11 +11159,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>vibration_warming</t>
+          <t>mould_conditioning</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28.19467561141304</v>
+        <v>22.44869883362676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9267,53 +11171,113 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>28.41015625</v>
+        <v>22.73446669600939</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>27.99660326086957</v>
+        <v>22.15354955252348</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4135529891304337</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>T3 is warmest and T5 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>28.08763586956522</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.1070397418478244</v>
+        <v>0.5809171434859124</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>#63BE7B</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T3 is warmest and T4 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L17" t="n">
-        <v>28.41015625</v>
+        <v>22.32362272593897</v>
       </c>
       <c r="M17" t="n">
-        <v>0.215480638586957</v>
-      </c>
-      <c r="N17" t="n">
-        <v>28.33793308423913</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.143257472826086</v>
+        <v>-0.1250761076877893</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
       <c r="P17" t="n">
-        <v>27.99660326086957</v>
+        <v>22.73446669600939</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1980723505434767</v>
-      </c>
-      <c r="R17" t="n">
-        <v>28.1410495923913</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.05362601902173836</v>
+        <v>0.285767862382631</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>22.15354955252348</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.2951492811032814</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>22.69943423562206</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.250735401995307</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>22.33242095803991</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.1162778755868494</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -9324,65 +11288,125 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>transition_to_cooling</t>
+          <t>deposition_transfer</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.55716594827586</v>
+        <v>28.24799262152778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>27.77015422952586</v>
+        <v>28.89122178819444</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>27.29754849137931</v>
+        <v>27.84138093171296</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4726057381465516</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>T4 is warmest and T5 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>27.60821322737069</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.05104727909483131</v>
+        <v>1.049840856481481</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T3 is warmest and T2 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L18" t="n">
-        <v>27.67869410021552</v>
+        <v>27.84138093171296</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1215281519396569</v>
-      </c>
-      <c r="N18" t="n">
-        <v>27.77015422952586</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.2129882812500021</v>
+        <v>-0.4066116898148167</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
       <c r="P18" t="n">
-        <v>27.29754849137931</v>
+        <v>28.89122178819444</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2596174568965495</v>
-      </c>
-      <c r="R18" t="n">
-        <v>27.43121969288793</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.1259462553879267</v>
+        <v>0.6432291666666643</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>28.3255931712963</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.07760054976851904</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>28.19858579282407</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.04940682870370594</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>27.98318142361111</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.2648111979166679</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -9393,65 +11417,125 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cooling_1</t>
+          <t>vibration_warming</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25.52827555338542</v>
+        <v>28.19467561141304</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>26.036865234375</v>
+        <v>28.41015625</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>25.24886067708333</v>
+        <v>27.99660326086957</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7880045572916679</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>T2 is warmest and T3 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>26.036865234375</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.5085896809895836</v>
+        <v>0.4135529891304337</v>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>#63BE7B</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T3 is warmest and T5 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L19" t="n">
-        <v>25.24886067708333</v>
+        <v>28.08763586956522</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2794148763020843</v>
-      </c>
-      <c r="N19" t="n">
-        <v>25.42427571614583</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.1039998372395843</v>
+        <v>-0.1070397418478244</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
       <c r="P19" t="n">
-        <v>25.34897867838542</v>
+        <v>28.41015625</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1792968749999986</v>
-      </c>
-      <c r="R19" t="n">
-        <v>25.5823974609375</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.05412190755208357</v>
+        <v>0.215480638586957</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>28.33793308423913</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.143257472826086</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>27.99660326086957</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.1980723505434767</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>28.1410495923913</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.05362601902173836</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -9462,65 +11546,125 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cooling_2</t>
+          <t>transition_to_cooling</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.71220175253378</v>
+        <v>27.55716594827586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>22.29559491131757</v>
+        <v>27.77015422952586</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>20.90987911739865</v>
+        <v>27.29754849137931</v>
       </c>
       <c r="H20" t="n">
-        <v>1.385715793918919</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>T2 is warmest and T4 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>22.29559491131757</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.5833931587837853</v>
+        <v>0.4726057381465516</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>#63BE7B</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T4 is warmest and T5 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L20" t="n">
-        <v>21.28576330236486</v>
+        <v>27.60821322737069</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.42643845016892</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20.90987911739865</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-0.802322635135134</v>
+        <v>0.05104727909483131</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
       <c r="P20" t="n">
-        <v>22.23527238175676</v>
+        <v>27.67869410021552</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5230706292229748</v>
-      </c>
-      <c r="R20" t="n">
-        <v>21.83449904983108</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.1222972972972975</v>
+        <v>0.1215281519396569</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>27.77015422952586</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.2129882812500021</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>27.29754849137931</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.2596174568965495</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>27.43121969288793</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.1259462553879267</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -9531,65 +11675,125 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cooling_3</t>
+          <t>cooling_1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19.36192471590909</v>
+        <v>25.52827555338542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>20.30078125</v>
+        <v>26.036865234375</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>18.09115767045455</v>
+        <v>25.24886067708333</v>
       </c>
       <c r="H21" t="n">
-        <v>2.209623579545454</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>T5 is warmest and T4 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>19.89169034090909</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5297656249999996</v>
+        <v>0.7880045572916679</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T3 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L21" t="n">
-        <v>18.7251953125</v>
+        <v>26.036865234375</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6367294034090918</v>
-      </c>
-      <c r="N21" t="n">
-        <v>18.09115767045455</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-1.270767045454544</v>
+        <v>0.5085896809895836</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
       <c r="P21" t="n">
-        <v>20.30078125</v>
+        <v>25.24886067708333</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.9388565340909096</v>
-      </c>
-      <c r="R21" t="n">
-        <v>19.80079900568182</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.4388742897727269</v>
+        <v>-0.2794148763020843</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>25.42427571614583</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.1039998372395843</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>25.34897867838542</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.1792968749999986</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>25.5823974609375</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.05412190755208357</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -9600,19 +11804,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cooling_4</t>
+          <t>cooling_2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.59992804276316</v>
+        <v>21.71220175253378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19.48482473273026</v>
+        <v>22.29559491131757</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -9620,45 +11824,105 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>17.23269171463816</v>
+        <v>20.90987911739865</v>
       </c>
       <c r="H22" t="n">
-        <v>2.252133018092106</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>T5 is warmest and T4 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>19.14593184621711</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.5460038034539458</v>
+        <v>1.385715793918919</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T4 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L22" t="n">
-        <v>17.85641961348684</v>
+        <v>22.29559491131757</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7435084292763179</v>
-      </c>
-      <c r="N22" t="n">
-        <v>17.23269171463816</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-1.367236328125003</v>
+        <v>0.5833931587837853</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
       <c r="P22" t="n">
-        <v>19.48482473273026</v>
+        <v>21.28576330236486</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8848966899671034</v>
-      </c>
-      <c r="R22" t="n">
-        <v>19.27977230674342</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.6798442639802609</v>
+        <v>-0.42643845016892</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>20.90987911739865</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.802322635135134</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>22.23527238175676</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.5230706292229748</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AA22" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>21.83449904983108</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.1222972972972975</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -9669,19 +11933,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>less_periodic_cooling_2</t>
+          <t>cooling_3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.52933258310249</v>
+        <v>19.36192471590909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16.77396771121884</v>
+        <v>20.30078125</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -9689,45 +11953,105 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>14.14381979310942</v>
+        <v>18.09115767045455</v>
       </c>
       <c r="H23" t="n">
-        <v>2.630147918109419</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>T2 is warmest and T4 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>16.77396771121884</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.244635128116345</v>
+        <v>2.209623579545454</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T5 is warmest and T4 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L23" t="n">
-        <v>14.41952692174515</v>
+        <v>19.89169034090909</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.10980566135734</v>
-      </c>
-      <c r="N23" t="n">
-        <v>14.14381979310942</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-1.385512789993074</v>
+        <v>0.5297656249999996</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
       <c r="P23" t="n">
-        <v>15.66035102146814</v>
+        <v>18.7251953125</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1310184383656505</v>
-      </c>
-      <c r="R23" t="n">
-        <v>16.64899746797091</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.119664884868422</v>
+        <v>-0.6367294034090918</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S23" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>18.09115767045455</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-1.270767045454544</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>20.30078125</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.9388565340909096</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AA23" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>19.80079900568182</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.4388742897727269</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -9738,65 +12062,125 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>transition_2</t>
+          <t>cooling_4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.03994140625</v>
+        <v>18.59992804276316</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>15.203125</v>
+        <v>19.48482473273026</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>13.226953125</v>
+        <v>17.23269171463816</v>
       </c>
       <c r="H24" t="n">
-        <v>1.976171875</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>T2 is warmest and T3 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>15.203125</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.16318359375</v>
+        <v>2.252133018092106</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>T5 is warmest and T4 is coolest in this zone.</t>
+        </is>
       </c>
       <c r="L24" t="n">
-        <v>13.226953125</v>
+        <v>19.14593184621711</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.81298828125</v>
-      </c>
-      <c r="N24" t="n">
-        <v>13.240234375</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-0.7997070312499996</v>
+        <v>0.5460038034539458</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
       <c r="P24" t="n">
-        <v>13.610302734375</v>
+        <v>17.85641961348684</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.4296386718749989</v>
-      </c>
-      <c r="R24" t="n">
-        <v>14.919091796875</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.879150390625</v>
+        <v>-0.7435084292763179</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>17.23269171463816</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1.367236328125003</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>19.48482473273026</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.8848966899671034</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AA24" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>19.27977230674342</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.6798442639802609</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AE24" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -9807,11 +12191,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>demoulding</t>
+          <t>less_periodic_cooling_2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.115252685546875</v>
+        <v>15.52933258310249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9819,7 +12203,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.36798095703125</v>
+        <v>16.77396771121884</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -9827,49 +12211,625 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2.93389892578125</v>
+        <v>14.14381979310942</v>
       </c>
       <c r="H25" t="n">
-        <v>0.43408203125</v>
-      </c>
-      <c r="I25" t="inlineStr">
+        <v>2.630147918109419</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>T2 is warmest and T4 is coolest in this zone.</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>3.36798095703125</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.2527282714843748</v>
-      </c>
       <c r="L25" t="n">
-        <v>2.941314697265625</v>
+        <v>16.77396771121884</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1739379882812502</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.93389892578125</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-0.1813537597656252</v>
+        <v>1.244635128116345</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
       </c>
       <c r="P25" t="n">
-        <v>3.033660888671875</v>
+        <v>14.41952692174515</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.08159179687500018</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.299407958984375</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.1841552734374998</v>
+        <v>-1.10980566135734</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>14.14381979310942</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-1.385512789993074</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>15.66035102146814</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.1310184383656505</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA25" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>16.64899746797091</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.119664884868422</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AE25" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14.03994140625</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>15.203125</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>13.226953125</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.976171875</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T3 is coolest in this zone.</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>15.203125</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.16318359375</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>13.226953125</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.81298828125</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>13.240234375</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.7997070312499996</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>13.610302734375</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.4296386718749989</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA26" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>14.919091796875</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.879150390625</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AE26" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>demoulding_twisting</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>14.20852864583333</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>15.365234375</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>13.37890625</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.986328125</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T4 is coolest in this zone.</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>15.365234375</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.156705729166669</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>13.4091796875</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.7993489583333311</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S27" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>13.37890625</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.8296223958333311</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>13.83072916666667</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-0.377799479166665</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA27" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>15.05859375</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.8500651041666689</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AE27" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>demoulding_vibration</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2.113425925925926</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2.28443287037037</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1.990668402777778</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2937644675925926</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>#63BE7B</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T4 is coolest in this zone.</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>2.28443287037037</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1710069444444442</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1.99609375</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.117332175925926</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>1.990668402777778</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.1227575231481484</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W28" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>2.058702256944445</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-0.0547236689814814</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA28" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.237232349537037</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.1238064236111112</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE28" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>final_demoulding</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>#63BE7B</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T2 is coolest in this zone.</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W29" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AA29" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE29" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S25"/>
+  <autoFilter ref="A1:AE29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9880,7 +12840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9900,7 +12860,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Contours use product sensors: T2, T3, T4, T5, T7. Hotspot delta matrix is included below; full contour data is exported separately.</t>
         </is>
@@ -9913,702 +12873,810 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Comparison contours</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>Hotspot Delta Matrix</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>zone</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="D85" s="1" t="inlineStr">
+      <c r="D103" s="1" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="E85" s="1" t="inlineStr">
+      <c r="E103" s="1" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="G85" s="1" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>cooling_1</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>0.5085896809895836</v>
-      </c>
-      <c r="D86" t="n">
-        <v>-0.2794148763020843</v>
-      </c>
-      <c r="E86" t="n">
-        <v>-0.1039998372395843</v>
-      </c>
-      <c r="F86" t="n">
-        <v>-0.1792968749999986</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0.05412190755208357</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>cooling_2</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>0.5833931587837853</v>
-      </c>
-      <c r="D87" t="n">
-        <v>-0.42643845016892</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-0.802322635135134</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.5230706292229748</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0.1222972972972975</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>cooling_3</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>0.5297656249999996</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-0.6367294034090918</v>
-      </c>
-      <c r="E88" t="n">
-        <v>-1.270767045454544</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.9388565340909096</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0.4388742897727269</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>cooling_4</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>0.5460038034539458</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-0.7435084292763179</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-1.367236328125003</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.8848966899671034</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0.6798442639802609</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>demoulding</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>0.2527282714843748</v>
-      </c>
-      <c r="D90" t="n">
-        <v>-0.1739379882812502</v>
-      </c>
-      <c r="E90" t="n">
-        <v>-0.1813537597656252</v>
-      </c>
-      <c r="F90" t="n">
-        <v>-0.08159179687500018</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0.1841552734374998</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>deposition_transfer</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.4066116898148167</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0.6432291666666643</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0.07760054976851904</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-0.04940682870370594</v>
-      </c>
-      <c r="G91" t="n">
-        <v>-0.2648111979166679</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>less_periodic_cooling_2</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1.244635128116345</v>
-      </c>
-      <c r="D92" t="n">
-        <v>-1.10980566135734</v>
-      </c>
-      <c r="E92" t="n">
-        <v>-1.385512789993074</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.1310184383656505</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1.119664884868422</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>mould_conditioning</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.1250761076877893</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.285767862382631</v>
-      </c>
-      <c r="E93" t="n">
-        <v>-0.2951492811032814</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.250735401995307</v>
-      </c>
-      <c r="G93" t="n">
-        <v>-0.1162778755868494</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>movement_to_conditioning</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.1118489583333364</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0.1463778409090892</v>
-      </c>
-      <c r="E94" t="n">
-        <v>-0.3912346117424264</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0.3881806344696948</v>
-      </c>
-      <c r="G94" t="n">
-        <v>-0.03147490530303187</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>transition_2</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1.16318359375</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-0.81298828125</v>
-      </c>
-      <c r="E95" t="n">
-        <v>-0.7997070312499996</v>
-      </c>
-      <c r="F95" t="n">
-        <v>-0.4296386718749989</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.879150390625</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>transition_to_cooling</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>0.05104727909483131</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.1215281519396569</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.2129882812500021</v>
-      </c>
-      <c r="F96" t="n">
-        <v>-0.2596174568965495</v>
-      </c>
-      <c r="G96" t="n">
-        <v>-0.1259462553879267</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>old-configuration</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>vibration_warming</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.1070397418478244</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0.215480638586957</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0.143257472826086</v>
-      </c>
-      <c r="F97" t="n">
-        <v>-0.1980723505434767</v>
-      </c>
-      <c r="G97" t="n">
-        <v>-0.05362601902173836</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>reference_2291-4160</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>cooling_1</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>0.7528021364795947</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-0.6453364158163239</v>
-      </c>
-      <c r="E98" t="n">
-        <v>-0.4081911670918323</v>
-      </c>
-      <c r="F98" t="n">
-        <v>-0.1532884247448933</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0.4540138711734727</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>reference_2291-4160</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>cooling_2</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>0.9842759284420275</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-0.8306442481884062</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-0.1593636775362341</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-0.7778391077898554</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0.7835711050724647</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>reference_2291-4160</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>cooling_3</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>0.7674139492753618</v>
-      </c>
-      <c r="D100" t="n">
-        <v>-0.7021710824275367</v>
-      </c>
-      <c r="E100" t="n">
-        <v>-0.104769587862318</v>
-      </c>
-      <c r="F100" t="n">
-        <v>-0.7996150362318843</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0.8391417572463773</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>reference_2291-4160</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>cooling_4</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>0.7560320425724605</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-0.6118631114130437</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0.07668421648550705</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-1.061280004528989</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0.8404268568840578</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>reference_2291-4160</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>demoulding</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>0.8833007812500018</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-0.2243381076388875</v>
-      </c>
-      <c r="E102" t="n">
-        <v>-0.3624403211805536</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-0.4750162760416643</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0.1784939236111125</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>reference_2291-4160</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>deposition_transfer</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>0.2731445312499936</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-0.6679492187500067</v>
-      </c>
-      <c r="E103" t="n">
-        <v>-0.1541601562500041</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0.5771093749999956</v>
-      </c>
-      <c r="G103" t="n">
-        <v>-0.02814453125000682</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>reference_2291-4160</t>
+          <t>old-configuration</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>less_periodic_cooling_2</t>
+          <t>cooling_1</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.9534987541528235</v>
+        <v>0.5085896809895836</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.3407223318106318</v>
+        <v>-0.2794148763020843</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0008506800249161728</v>
+        <v>-0.1039998372395843</v>
       </c>
       <c r="F104" t="n">
-        <v>-1.057600316652824</v>
+        <v>-0.1792968749999986</v>
       </c>
       <c r="G104" t="n">
-        <v>0.4439732142857142</v>
+        <v>0.05412190755208357</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>reference_2291-4160</t>
+          <t>old-configuration</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>mould_conditioning</t>
+          <t>cooling_2</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.1637898763020829</v>
+        <v>0.5833931587837853</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.4071329752604171</v>
+        <v>-0.42643845016892</v>
       </c>
       <c r="E105" t="n">
-        <v>0.06388549804687571</v>
+        <v>-0.802322635135134</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1546447753906257</v>
+        <v>0.5230706292229748</v>
       </c>
       <c r="G105" t="n">
-        <v>0.02481282552083286</v>
+        <v>0.1222972972972975</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>reference_2291-4160</t>
+          <t>old-configuration</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>movement_to_conditioning</t>
+          <t>cooling_3</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.5641601562500007</v>
+        <v>0.5297656249999996</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.008886718750000355</v>
+        <v>-0.6367294034090918</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.2385742187499993</v>
+        <v>-1.270767045454544</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.31005859375</v>
+        <v>0.9388565340909096</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.006640624999999289</v>
+        <v>0.4388742897727269</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>reference_2291-4160</t>
+          <t>old-configuration</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>transition_2</t>
+          <t>cooling_4</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.8461961699695113</v>
+        <v>0.5460038034539458</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.2345607850609763</v>
+        <v>-0.7435084292763179</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.3444836128048792</v>
+        <v>-1.367236328125003</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.5456316692073173</v>
+        <v>0.8848966899671034</v>
       </c>
       <c r="G107" t="n">
-        <v>0.2784798971036579</v>
+        <v>0.6798442639802609</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>reference_2291-4160</t>
+          <t>old-configuration</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>transition_to_cooling</t>
+          <t>demoulding_twisting</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.4313151041666643</v>
+        <v>1.156705729166669</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.5489908854166679</v>
+        <v>-0.7993489583333311</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.3546781994047628</v>
+        <v>-0.8296223958333311</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3505161830357117</v>
+        <v>-0.377799479166665</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1218377976190474</v>
+        <v>0.8500651041666689</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>demoulding_vibration</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.1710069444444442</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-0.117332175925926</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-0.1227575231481484</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-0.0547236689814814</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.1238064236111112</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>deposition_transfer</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.4066116898148167</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.6432291666666643</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.07760054976851904</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-0.04940682870370594</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-0.2648111979166679</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>final_demoulding</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1.244635128116345</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-1.10980566135734</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-1.385512789993074</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.1310184383656505</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.119664884868422</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>mould_conditioning</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.1250761076877893</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.285767862382631</v>
+      </c>
+      <c r="E113" t="n">
+        <v>-0.2951492811032814</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.250735401995307</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-0.1162778755868494</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>movement_to_conditioning</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.1118489583333364</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.1463778409090892</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-0.3912346117424264</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.3881806344696948</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-0.03147490530303187</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1.16318359375</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-0.81298828125</v>
+      </c>
+      <c r="E115" t="n">
+        <v>-0.7997070312499996</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-0.4296386718749989</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.879150390625</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>transition_to_cooling</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0.05104727909483131</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.1215281519396569</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.2129882812500021</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-0.2596174568965495</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-0.1259462553879267</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>old-configuration</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>vibration_warming</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.1070397418478244</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.215480638586957</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.143257472826086</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-0.1980723505434767</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-0.05362601902173836</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>reference_2291-4160</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>cooling_1</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7528021364795947</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-0.6453364158163239</v>
+      </c>
+      <c r="E118" t="n">
+        <v>-0.4081911670918323</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-0.1532884247448933</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.4540138711734727</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>cooling_2</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0.9842759284420275</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-0.8306442481884062</v>
+      </c>
+      <c r="E119" t="n">
+        <v>-0.1593636775362341</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-0.7778391077898554</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.7835711050724647</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>cooling_3</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0.7674139492753618</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-0.7021710824275367</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-0.104769587862318</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-0.7996150362318843</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.8391417572463773</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>cooling_4</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7560320425724605</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-0.6118631114130437</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.07668421648550705</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-1.061280004528989</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.8404268568840578</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>demoulding_twisting</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0.9197916666666686</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.2332031249999993</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.3393229166666654</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.5359374999999993</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.1886718750000007</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>demoulding_vibration</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0.8861799568965516</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-0.2240369073275872</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-0.3640894396551726</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-0.4750808189655178</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.1770272090517224</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>deposition_transfer</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0.2731445312499936</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-0.6679492187500067</v>
+      </c>
+      <c r="E124" t="n">
+        <v>-0.1541601562500041</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.5771093749999956</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-0.02814453125000682</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>final_demoulding</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0.8350585937500004</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-0.2198730468749996</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-0.3678222656249996</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-0.4288574218749996</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.1814941406250004</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9534987541528235</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.3407223318106318</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.0008506800249161728</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-1.057600316652824</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.4439732142857142</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>mould_conditioning</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0.1637898763020829</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.4071329752604171</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.06388549804687571</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1546447753906257</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.02481282552083286</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>movement_to_conditioning</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5641601562500007</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-0.008886718750000355</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-0.2385742187499993</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-0.31005859375</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-0.006640624999999289</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0.8461961699695113</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.2345607850609763</v>
+      </c>
+      <c r="E129" t="n">
+        <v>-0.3444836128048792</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-0.5456316692073173</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.2784798971036579</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>transition_to_cooling</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0.4313151041666643</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.5489908854166679</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-0.3546781994047628</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3505161830357117</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.1218377976190474</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
         <is>
           <t>vibration_warming</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="C131" t="n">
         <v>0.3380594544491551</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D131" t="n">
         <v>-0.4605534957627064</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E131" t="n">
         <v>-0.3258375264830455</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F131" t="n">
         <v>0.4250893802966154</v>
       </c>
-      <c r="G109" t="n">
+      <c r="G131" t="n">
         <v>0.02324218750000284</v>
       </c>
     </row>

--- a/outputs/aasted3_run_comparison/summary/aasted3_reference_based_comparison_summary.xlsx
+++ b/outputs/aasted3_run_comparison/summary/aasted3_reference_based_comparison_summary.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensor Coordinates" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanical By Zone" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hotspot Summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contour Overview" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality Comparison" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contour Overview" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read Me'!$A$1:$B$11</definedName>
@@ -1286,7 +1287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reference = reference_2291-4160. Comparison = old-configuration. Raw copies are stored in inputs/aasted3/.</t>
+          <t>Reference = reference_2291-4160. Comparison = 17_3_f_m_aa3-25_06_26-2160-4374s. Raw copies, experimental setup, experimental summary, and temperature-correction coefficients are stored in inputs/aasted3/.</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optional architecture is installed. When a parameter_summary file is placed in inputs/aasted3, the report can mark crystallization onset, detachment onset, and complete/partial ultrasound detachment offsets using positive change points and a pre-deposition reference minus 10% threshold.</t>
+          <t>The architecture reads aa3_trials experimental summary or parameter_summary files from inputs/aasted3. The report marks crystallization onset, detachment onset, and complete/partial ultrasound detachment offsets using T7-corrected ultrasound, positive change points, and a pre-deposition reference minus 10% threshold.</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1454,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>old_configuration.csv</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s.csv</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1471,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1487,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>271.9866759777069</v>
+        <v>345.246253490448</v>
       </c>
     </row>
     <row r="6">
@@ -1501,7 +1502,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1875.362498191601</v>
+        <v>686.7672500697651</v>
       </c>
     </row>
     <row r="7">
@@ -1517,7 +1518,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mould_conditioning: 234.0 s</t>
+          <t>less_periodic_cooling_2: 350.0 s</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1535,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>slightly longer; comparison warmer than reference; T8_mean_C, T8_min_C, T8_max_C, accz_mean, accz_min, accz_max, accz_std_max, gyroy_mean, gyroy_min, gyroy_std_median, gyroy_std_max</t>
+          <t>similar length; comparison cooler than reference; T8_mean_C, T8_min_C, T8_max_C, gyroy_max, gyroy_std_median</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1552,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>main stretched section; comparison warmer than reference; T8_mean_C, T8_min_C, accz_min, accz_std_max, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>similar length; comparison cooler than reference; T8_mean_C, T8_min_C, gyroy_min</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1569,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>similar length; comparison warmer than reference; gyroy_mean, gyroy_min, gyroy_max</t>
+          <t>similar length; comparison cooler than reference; gyroy_std_median</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1586,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>similar length; comparison warmer than reference; accz_min, gyroy_min, gyroy_std_max</t>
+          <t>similar length; comparison cooler than reference; accz_min</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1603,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>similar length; similar mean product temperature; accz_std_max, gyroy_min, gyroy_std_median, gyroy_std_max</t>
+          <t>similar length; similar mean product temperature; gyroy_min, gyroy_std_max</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1620,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>similar length; comparison warmer than reference; gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>similar length; similar mean product temperature; gyroy_min</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1637,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>similar length; similar mean product temperature; gyroy_min, gyroy_std_max</t>
+          <t>slightly longer; comparison cooler than reference; gyroy_min, gyroy_std_max</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1654,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>similar length; similar mean product temperature; T8_min_C, accz_std_max, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>main stretched section; similar mean product temperature; accz_std_max, gyroy_std_max</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2467,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2478,10 +2479,10 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="E101" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -2497,7 +2498,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2506,13 +2507,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D102" t="n">
-        <v>493</v>
+        <v>214</v>
       </c>
       <c r="E102" t="n">
-        <v>426</v>
+        <v>188</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -2528,7 +2529,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2537,13 +2538,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>493</v>
+        <v>214</v>
       </c>
       <c r="D103" t="n">
-        <v>600</v>
+        <v>315</v>
       </c>
       <c r="E103" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -2559,7 +2560,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2568,13 +2569,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>600</v>
+        <v>315</v>
       </c>
       <c r="D104" t="n">
-        <v>646</v>
+        <v>374</v>
       </c>
       <c r="E104" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -2590,7 +2591,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2599,13 +2600,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>646</v>
+        <v>374</v>
       </c>
       <c r="D105" t="n">
-        <v>794</v>
+        <v>519</v>
       </c>
       <c r="E105" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -2621,7 +2622,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2630,13 +2631,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>794</v>
+        <v>519</v>
       </c>
       <c r="D106" t="n">
-        <v>891</v>
+        <v>617</v>
       </c>
       <c r="E106" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -2652,7 +2653,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2661,13 +2662,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>891</v>
+        <v>617</v>
       </c>
       <c r="D107" t="n">
-        <v>1040</v>
+        <v>793</v>
       </c>
       <c r="E107" t="n">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -2683,7 +2684,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2692,13 +2693,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1040</v>
+        <v>793</v>
       </c>
       <c r="D108" t="n">
-        <v>1152</v>
+        <v>900</v>
       </c>
       <c r="E108" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -2714,7 +2715,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2723,13 +2724,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1152</v>
+        <v>900</v>
       </c>
       <c r="D109" t="n">
-        <v>1307</v>
+        <v>1024</v>
       </c>
       <c r="E109" t="n">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -2745,7 +2746,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2754,13 +2755,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1307</v>
+        <v>1024</v>
       </c>
       <c r="D110" t="n">
-        <v>2035</v>
+        <v>1976</v>
       </c>
       <c r="E110" t="n">
-        <v>728</v>
+        <v>952</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -2776,7 +2777,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2785,13 +2786,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2035</v>
+        <v>1976</v>
       </c>
       <c r="D111" t="n">
-        <v>2074</v>
+        <v>2118</v>
       </c>
       <c r="E111" t="n">
-        <v>39</v>
+        <v>142</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -2807,7 +2808,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2816,13 +2817,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2074</v>
+        <v>2118</v>
       </c>
       <c r="D112" t="n">
-        <v>2081</v>
+        <v>2126</v>
       </c>
       <c r="E112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -2838,7 +2839,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2847,13 +2848,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2081</v>
+        <v>2126</v>
       </c>
       <c r="D113" t="n">
-        <v>2137</v>
+        <v>2190</v>
       </c>
       <c r="E113" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -2869,7 +2870,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2878,13 +2879,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2137</v>
+        <v>2190</v>
       </c>
       <c r="D114" t="n">
-        <v>2141</v>
+        <v>2214</v>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3237,7 +3238,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
@@ -3245,47 +3246,47 @@
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
     <col width="27" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
     <col width="24" customWidth="1" min="22" max="22"/>
     <col width="24" customWidth="1" min="23" max="23"/>
     <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
     <col width="22" customWidth="1" min="26" max="26"/>
-    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
     <col width="24" customWidth="1" min="28" max="28"/>
     <col width="23" customWidth="1" min="29" max="29"/>
-    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="30" max="30"/>
     <col width="24" customWidth="1" min="31" max="31"/>
     <col width="21" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
-    <col width="23" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="34" max="34"/>
     <col width="27" customWidth="1" min="35" max="35"/>
     <col width="28" customWidth="1" min="36" max="36"/>
     <col width="24" customWidth="1" min="37" max="37"/>
     <col width="24" customWidth="1" min="38" max="38"/>
     <col width="25" customWidth="1" min="39" max="39"/>
-    <col width="23" customWidth="1" min="40" max="40"/>
+    <col width="24" customWidth="1" min="40" max="40"/>
     <col width="22" customWidth="1" min="41" max="41"/>
     <col width="22" customWidth="1" min="42" max="42"/>
     <col width="23" customWidth="1" min="43" max="43"/>
     <col width="22" customWidth="1" min="44" max="44"/>
-    <col width="21" customWidth="1" min="45" max="45"/>
-    <col width="24" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="45" max="45"/>
+    <col width="23" customWidth="1" min="46" max="46"/>
     <col width="21" customWidth="1" min="47" max="47"/>
     <col width="21" customWidth="1" min="48" max="48"/>
-    <col width="23" customWidth="1" min="49" max="49"/>
+    <col width="24" customWidth="1" min="49" max="49"/>
     <col width="27" customWidth="1" min="50" max="50"/>
     <col width="28" customWidth="1" min="51" max="51"/>
-    <col width="23" customWidth="1" min="52" max="52"/>
+    <col width="24" customWidth="1" min="52" max="52"/>
     <col width="24" customWidth="1" min="53" max="53"/>
     <col width="25" customWidth="1" min="54" max="54"/>
     <col width="22" customWidth="1" min="55" max="55"/>
@@ -3294,22 +3295,22 @@
     <col width="23" customWidth="1" min="58" max="58"/>
     <col width="21" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
-    <col width="21" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
     <col width="21" customWidth="1" min="62" max="62"/>
     <col width="22" customWidth="1" min="63" max="63"/>
-    <col width="22" customWidth="1" min="64" max="64"/>
+    <col width="23" customWidth="1" min="64" max="64"/>
     <col width="28" customWidth="1" min="65" max="65"/>
     <col width="29" customWidth="1" min="66" max="66"/>
     <col width="24" customWidth="1" min="67" max="67"/>
     <col width="25" customWidth="1" min="68" max="68"/>
     <col width="26" customWidth="1" min="69" max="69"/>
-    <col width="23" customWidth="1" min="70" max="70"/>
+    <col width="22" customWidth="1" min="70" max="70"/>
     <col width="22" customWidth="1" min="71" max="71"/>
     <col width="23" customWidth="1" min="72" max="72"/>
     <col width="22" customWidth="1" min="73" max="73"/>
     <col width="22" customWidth="1" min="74" max="74"/>
     <col width="22" customWidth="1" min="75" max="75"/>
-    <col width="21" customWidth="1" min="76" max="76"/>
+    <col width="22" customWidth="1" min="76" max="76"/>
     <col width="21" customWidth="1" min="77" max="77"/>
     <col width="22" customWidth="1" min="78" max="78"/>
     <col width="21" customWidth="1" min="79" max="79"/>
@@ -3318,16 +3319,16 @@
     <col width="24" customWidth="1" min="82" max="82"/>
     <col width="25" customWidth="1" min="83" max="83"/>
     <col width="26" customWidth="1" min="84" max="84"/>
-    <col width="21" customWidth="1" min="85" max="85"/>
+    <col width="22" customWidth="1" min="85" max="85"/>
     <col width="22" customWidth="1" min="86" max="86"/>
     <col width="23" customWidth="1" min="87" max="87"/>
-    <col width="20" customWidth="1" min="88" max="88"/>
+    <col width="22" customWidth="1" min="88" max="88"/>
     <col width="21" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
     <col width="22" customWidth="1" min="91" max="91"/>
     <col width="22" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="20" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
     <col width="28" customWidth="1" min="95" max="95"/>
     <col width="29" customWidth="1" min="96" max="96"/>
     <col width="24" customWidth="1" min="97" max="97"/>
@@ -4124,302 +4125,302 @@
         <v>15.52460098971224</v>
       </c>
       <c r="C2" t="n">
-        <v>22.33202883022977</v>
+        <v>12.17148218067509</v>
       </c>
       <c r="D2" t="n">
-        <v>6.80742784051753</v>
+        <v>-3.353118809037158</v>
       </c>
       <c r="E2" t="n">
         <v>15.34018936099057</v>
       </c>
       <c r="F2" t="n">
-        <v>22.287109375</v>
+        <v>11.6064453125</v>
       </c>
       <c r="G2" t="n">
-        <v>6.946920014009432</v>
+        <v>-3.733744048490568</v>
       </c>
       <c r="H2" t="n">
         <v>16.07242573881686</v>
       </c>
       <c r="I2" t="n">
-        <v>22.35410688403682</v>
+        <v>12.63943860574593</v>
       </c>
       <c r="J2" t="n">
-        <v>6.281681145219963</v>
+        <v>-3.432987133070924</v>
       </c>
       <c r="K2" t="n">
         <v>-0.5368004368373326</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.02622721195430614</v>
+        <v>-0.4964356334665304</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5105732248830265</v>
+        <v>0.04036480337080217</v>
       </c>
       <c r="N2" t="n">
         <v>-1.048880440848214</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.02773175920758928</v>
+        <v>-1.051378522600446</v>
       </c>
       <c r="P2" t="n">
-        <v>1.021148681640625</v>
+        <v>-0.002498081752232206</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01713943481445312</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02455793108258928</v>
+        <v>0.07291085379464286</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.04169736589704241</v>
+        <v>0.05577141898018974</v>
       </c>
       <c r="T2" t="n">
         <v>0.03877181949361025</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002516657829139598</v>
+        <v>0.03406954677465622</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.03625516166447065</v>
+        <v>-0.004702272718954029</v>
       </c>
       <c r="W2" t="n">
         <v>0.2551015997630952</v>
       </c>
       <c r="X2" t="n">
-        <v>0.009927087581051796</v>
+        <v>0.2115907788366657</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2451745121820434</v>
+        <v>-0.04351082092642947</v>
       </c>
       <c r="Z2" t="n">
         <v>0.008378801618303571</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01827846000972965</v>
+        <v>0.006986249038596558</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.009899658391426083</v>
+        <v>-0.001392552579707013</v>
       </c>
       <c r="AC2" t="n">
         <v>-0.00726318359375</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0172119140625</v>
+        <v>-0.005575997488839286</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.02447509765625</v>
+        <v>0.001687186104910714</v>
       </c>
       <c r="AF2" t="n">
         <v>0.01769205729166667</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.02025059291294643</v>
+        <v>0.01741681780133928</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.002558535621279761</v>
+        <v>-0.0002752394903273829</v>
       </c>
       <c r="AI2" t="n">
         <v>0.01270874710605859</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001605488666143564</v>
+        <v>0.01227780160038133</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.01110325843991502</v>
+        <v>-0.0004309455056772573</v>
       </c>
       <c r="AL2" t="n">
         <v>0.03208759519736847</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.003258361761001178</v>
+        <v>0.04311653689490094</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.02882923343636729</v>
+        <v>0.01102894169753248</v>
       </c>
       <c r="AO2" t="n">
         <v>0.4479989115397135</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.06109563009634</v>
+        <v>0.488598848381086</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.509094541636054</v>
+        <v>0.04059993684137247</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.09227294921875</v>
       </c>
       <c r="AS2" t="n">
-        <v>-1.064653669084821</v>
+        <v>-0.08636474609375</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0.9723807198660714</v>
+        <v>0.005908203124999997</v>
       </c>
       <c r="AU2" t="n">
         <v>0.9688197544642857</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.05596923828125</v>
+        <v>0.9704015395220589</v>
       </c>
       <c r="AW2" t="n">
-        <v>-2.024788992745536</v>
+        <v>0.001581785057773177</v>
       </c>
       <c r="AX2" t="n">
         <v>0.0458989215249313</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.006430887205384256</v>
+        <v>0.03616904674949482</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.03946803431954705</v>
+        <v>-0.009729874775436478</v>
       </c>
       <c r="BA2" t="n">
         <v>0.2646710061930599</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.01283206979648683</v>
+        <v>0.3425790454249703</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.2518389363965731</v>
+        <v>0.07790803923191031</v>
       </c>
       <c r="BD2" t="n">
         <v>2.883698488871257</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.87591338863188</v>
+        <v>2.862196464137947</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.007785100239376952</v>
+        <v>-0.02150202473330953</v>
       </c>
       <c r="BG2" t="n">
         <v>2.698628743489583</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.844265208524816</v>
+        <v>2.70660400390625</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1456364650352326</v>
+        <v>0.007975260416666519</v>
       </c>
       <c r="BJ2" t="n">
         <v>2.927419026692708</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.91595458984375</v>
+        <v>2.917556762695312</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.01146443684895848</v>
+        <v>-0.009862263997395981</v>
       </c>
       <c r="BM2" t="n">
         <v>0.06479490562920771</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.02162807297479108</v>
+        <v>0.07060315781695839</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.04316683265441663</v>
+        <v>0.005808252187750676</v>
       </c>
       <c r="BP2" t="n">
         <v>0.2769825001807807</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.04301985310944212</v>
+        <v>0.3023043363422901</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.2339626470713386</v>
+        <v>0.0253218361615094</v>
       </c>
       <c r="BS2" t="n">
         <v>-0.7421609115600586</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.491703783556254</v>
+        <v>-0.7367571086019425</v>
       </c>
       <c r="BU2" t="n">
-        <v>2.233864695116313</v>
+        <v>0.005403802958116044</v>
       </c>
       <c r="BV2" t="n">
         <v>-41.26698811848959</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.461181640625</v>
+        <v>-42.80251895680147</v>
       </c>
       <c r="BX2" t="n">
-        <v>42.72816975911459</v>
+        <v>-1.535530838311885</v>
       </c>
       <c r="BY2" t="n">
         <v>1.67779541015625</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.52313232421875</v>
+        <v>2.676256965188419</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.1546630859375</v>
+        <v>0.9984615550321689</v>
       </c>
       <c r="CB2" t="n">
         <v>0.2466633309816629</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.01993700566461322</v>
+        <v>0.1311973814847347</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.2267263253170497</v>
+        <v>-0.1154659494969283</v>
       </c>
       <c r="CE2" t="n">
         <v>26.72129171373545</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.03809367172169988</v>
+        <v>28.71015347730762</v>
       </c>
       <c r="CG2" t="n">
-        <v>-26.68319804201375</v>
+        <v>1.988861763572178</v>
       </c>
       <c r="CH2" t="n">
         <v>-0.3591134262084962</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.2459380695092387</v>
+        <v>-0.2389428170324937</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.6050514957177349</v>
+        <v>0.1201706091760025</v>
       </c>
       <c r="CK2" t="n">
         <v>-0.4436238606770833</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.07992448477909483</v>
+        <v>-0.3003917020909926</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.5235483454561781</v>
+        <v>0.1432321585860907</v>
       </c>
       <c r="CN2" t="n">
         <v>-0.330047607421875</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.2709242876838235</v>
+        <v>-0.1938629150390625</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.6009718951056986</v>
+        <v>0.1361846923828125</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.02734986543226808</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.01495361328125</v>
+        <v>0.03015986044448223</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0.01239625215101807</v>
+        <v>0.002809995012214149</v>
       </c>
       <c r="CT2" t="n">
         <v>0.05932288036451382</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.4709544782293714</v>
+        <v>0.07049816385342469</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.4116315978648576</v>
+        <v>0.01117528348891088</v>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>T8_mean_C, T8_min_C, T8_max_C, accz_mean, accz_min, accz_max, accz_std_max, gyroy_mean, gyroy_min, gyroy_std_median, gyroy_std_max</t>
+          <t>T8_mean_C, T8_min_C, T8_max_C, gyroy_max, gyroy_std_median</t>
         </is>
       </c>
     </row>
@@ -4433,302 +4434,302 @@
         <v>24.70050931450471</v>
       </c>
       <c r="C3" t="n">
-        <v>23.12464288708671</v>
+        <v>22.86865304613514</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.575866427418006</v>
+        <v>-1.831856268369574</v>
       </c>
       <c r="E3" t="n">
         <v>16.28937526710904</v>
       </c>
       <c r="F3" t="n">
-        <v>20.04769854360752</v>
+        <v>12.81191273703851</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75832327649848</v>
+        <v>-3.477462530070534</v>
       </c>
       <c r="H3" t="n">
         <v>32.74151417326573</v>
       </c>
       <c r="I3" t="n">
-        <v>31.9408539396871</v>
+        <v>32.41555034643766</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.8006602335786361</v>
+        <v>-0.3259638268280796</v>
       </c>
       <c r="K3" t="n">
         <v>-0.05427554107847667</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1862017065442487</v>
+        <v>-0.05271965416193743</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.131926165465772</v>
+        <v>0.001555886916539247</v>
       </c>
       <c r="N3" t="n">
         <v>-1.037504069010417</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.082340785435268</v>
+        <v>-1.026236397879464</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0448367164248511</v>
+        <v>0.01126767113095251</v>
       </c>
       <c r="Q3" t="n">
         <v>0.007926432291666667</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9926578297334558</v>
+        <v>0.01209368024553571</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9847313974417892</v>
+        <v>0.004167247953869047</v>
       </c>
       <c r="T3" t="n">
         <v>0.03638577802277736</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03299578241521656</v>
+        <v>0.02717760341988716</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0033899956075608</v>
+        <v>-0.009208174602890196</v>
       </c>
       <c r="W3" t="n">
         <v>0.1890359756520396</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5462395519351303</v>
+        <v>0.2466001761065763</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3572035762830906</v>
+        <v>0.05756420045453664</v>
       </c>
       <c r="Z3" t="n">
         <v>0.003649319012959798</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.01436160460617242</v>
+        <v>0.003781855830040038</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.01801092361913222</v>
+        <v>0.0001325368170802398</v>
       </c>
       <c r="AC3" t="n">
         <v>-0.064404296875</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.3233139935661765</v>
+        <v>-0.01208932059151786</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.2589096966911765</v>
+        <v>0.05231497628348215</v>
       </c>
       <c r="AF3" t="n">
         <v>0.02252197265625</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.8273664202008929</v>
+        <v>0.01317487444196429</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.8048444475446429</v>
+        <v>-0.009347098214285714</v>
       </c>
       <c r="AI3" t="n">
         <v>0.00892050379412972</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01069582711076294</v>
+        <v>0.008460785693043073</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.001775323316633217</v>
+        <v>-0.0004597181010866473</v>
       </c>
       <c r="AL3" t="n">
         <v>0.1754773316142838</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.3814337792396966</v>
+        <v>0.05795542724613938</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.2059564476254128</v>
+        <v>-0.1175219043681444</v>
       </c>
       <c r="AO3" t="n">
         <v>0.9334113332203456</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6354914671569223</v>
+        <v>0.9368507948030041</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.2979198660634234</v>
+        <v>0.00343946158265851</v>
       </c>
       <c r="AR3" t="n">
         <v>-0.02106119791666667</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1.067483084542411</v>
+        <v>-0.02690778459821428</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1.046421886625744</v>
+        <v>-0.005846586681547618</v>
       </c>
       <c r="AU3" t="n">
         <v>1.002925618489583</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.12188720703125</v>
+        <v>1.002724783761161</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1189615885416666</v>
+        <v>-0.0002008347284225831</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0344609939392355</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.03260140116998068</v>
+        <v>0.03511376923404315</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.001859592769254827</v>
+        <v>0.0006527752948076448</v>
       </c>
       <c r="BA3" t="n">
         <v>0.2695349696990631</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.5735845791771802</v>
+        <v>0.2409813935524709</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.3040496094781171</v>
+        <v>-0.02855357614659224</v>
       </c>
       <c r="BD3" t="n">
         <v>2.936941440900167</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.126553809938235</v>
+        <v>2.897912176287027</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1896123690380676</v>
+        <v>-0.03902926461314005</v>
       </c>
       <c r="BG3" t="n">
         <v>2.868601481119792</v>
       </c>
       <c r="BH3" t="n">
-        <v>-55.22422790527344</v>
+        <v>2.760810852050781</v>
       </c>
       <c r="BI3" t="n">
-        <v>-58.09282938639323</v>
+        <v>-0.1077906290690103</v>
       </c>
       <c r="BJ3" t="n">
         <v>3.047866821289062</v>
       </c>
       <c r="BK3" t="n">
-        <v>57.28462219238281</v>
+        <v>3.010349273681641</v>
       </c>
       <c r="BL3" t="n">
-        <v>54.23675537109375</v>
+        <v>-0.03751754760742188</v>
       </c>
       <c r="BM3" t="n">
         <v>0.03326386676918849</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.04712155002593012</v>
+        <v>0.03496846303283182</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.01385768325674163</v>
+        <v>0.001704596263643325</v>
       </c>
       <c r="BP3" t="n">
         <v>0.1866180012112513</v>
       </c>
       <c r="BQ3" t="n">
-        <v>41.19791299108901</v>
+        <v>0.1940653001145076</v>
       </c>
       <c r="BR3" t="n">
-        <v>41.01129498987775</v>
+        <v>0.007447298903256377</v>
       </c>
       <c r="BS3" t="n">
         <v>1.417432697614034</v>
       </c>
       <c r="BT3" t="n">
-        <v>2.190627949883767</v>
+        <v>1.233660100159255</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.773195252269733</v>
+        <v>-0.1837725974547788</v>
       </c>
       <c r="BV3" t="n">
         <v>0.4625651041666667</v>
       </c>
       <c r="BW3" t="n">
-        <v>-65.51979064941406</v>
+        <v>-0.0763702392578125</v>
       </c>
       <c r="BX3" t="n">
-        <v>-65.98235575358073</v>
+        <v>-0.5389353434244792</v>
       </c>
       <c r="BY3" t="n">
         <v>41.49727376302084</v>
       </c>
       <c r="BZ3" t="n">
-        <v>95.91087341308594</v>
+        <v>40.20706176757812</v>
       </c>
       <c r="CA3" t="n">
-        <v>54.4135996500651</v>
+        <v>-1.290211995442711</v>
       </c>
       <c r="CB3" t="n">
         <v>0.04885023437722506</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.05637214130170413</v>
+        <v>0.03622821211188733</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.007521906924479065</v>
+        <v>-0.01262202226533773</v>
       </c>
       <c r="CE3" t="n">
         <v>24.6942022006408</v>
       </c>
       <c r="CF3" t="n">
-        <v>107.2983308506786</v>
+        <v>24.69569678322329</v>
       </c>
       <c r="CG3" t="n">
-        <v>82.60412865003782</v>
+        <v>0.001494582582484583</v>
       </c>
       <c r="CH3" t="n">
         <v>-0.4075844844182332</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.6873460735971678</v>
+        <v>-0.3252163125139316</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.094930558015401</v>
+        <v>0.08236817190430157</v>
       </c>
       <c r="CK3" t="n">
         <v>-0.480010986328125</v>
       </c>
       <c r="CL3" t="n">
-        <v>-44.34280395507812</v>
+        <v>-0.4213714599609375</v>
       </c>
       <c r="CM3" t="n">
-        <v>-43.86279296875</v>
+        <v>0.0586395263671875</v>
       </c>
       <c r="CN3" t="n">
         <v>-0.3145243326822917</v>
       </c>
       <c r="CO3" t="n">
-        <v>50.8978271484375</v>
+        <v>-0.2109527587890625</v>
       </c>
       <c r="CP3" t="n">
-        <v>51.21235148111979</v>
+        <v>0.1035715738932292</v>
       </c>
       <c r="CQ3" t="n">
         <v>0.01848796089647603</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.02082442051415789</v>
+        <v>0.01800006583552081</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.002336459617681856</v>
+        <v>-0.0004878950609552152</v>
       </c>
       <c r="CT3" t="n">
         <v>0.06849243894935984</v>
       </c>
       <c r="CU3" t="n">
-        <v>46.02315512033991</v>
+        <v>0.07985545520029418</v>
       </c>
       <c r="CV3" t="n">
-        <v>45.95466268139055</v>
+        <v>0.01136301625093433</v>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>T8_mean_C, T8_min_C, accz_min, accz_std_max, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>T8_mean_C, T8_min_C, gyroy_min</t>
         </is>
       </c>
     </row>
@@ -4742,302 +4743,302 @@
         <v>29.33283350277162</v>
       </c>
       <c r="C4" t="n">
-        <v>29.03948788964039</v>
+        <v>28.70742044213338</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2933456131312333</v>
+        <v>-0.6254130606382482</v>
       </c>
       <c r="E4" t="n">
         <v>26.07253458246615</v>
       </c>
       <c r="F4" t="n">
-        <v>26.06373267801023</v>
+        <v>25.40236256792754</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.008801904455918219</v>
+        <v>-0.6701720145386076</v>
       </c>
       <c r="H4" t="n">
         <v>31.36661119991474</v>
       </c>
       <c r="I4" t="n">
-        <v>30.69791098922071</v>
+        <v>31.06475354554538</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6687002106940341</v>
+        <v>-0.3018576543693676</v>
       </c>
       <c r="K4" t="n">
         <v>0.2501788500965798</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.313723102865175</v>
+        <v>0.2499063907817688</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5639019529617548</v>
+        <v>-0.0002724593148109855</v>
       </c>
       <c r="N4" t="n">
         <v>-0.1009562174479167</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.061370849609375</v>
+        <v>-0.09030689912683823</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9604146321614584</v>
+        <v>0.01064931832107843</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9924723307291666</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04360089983258929</v>
+        <v>0.9905831473214286</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9488714308965773</v>
+        <v>-0.001889183407738027</v>
       </c>
       <c r="T4" t="n">
         <v>0.06086300539911352</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05689553294419233</v>
+        <v>0.05444279016573063</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.003967472454921184</v>
+        <v>-0.006420215233382889</v>
       </c>
       <c r="W4" t="n">
         <v>0.2418208775248952</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2773265730588341</v>
+        <v>0.2561068283028413</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03550569553393884</v>
+        <v>0.01428595077794609</v>
       </c>
       <c r="Z4" t="n">
         <v>0.007544795714147928</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008816258868091403</v>
+        <v>0.007791535291210268</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001271463153943475</v>
+        <v>0.0002467395770623399</v>
       </c>
       <c r="AC4" t="n">
         <v>-0.008797200520833333</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.01387376051682692</v>
+        <v>-0.010772705078125</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.005076559995993591</v>
+        <v>-0.001975504557291667</v>
       </c>
       <c r="AF4" t="n">
         <v>0.051123046875</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.03519439697265625</v>
+        <v>0.02932303292410714</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.01592864990234375</v>
+        <v>-0.02180001395089286</v>
       </c>
       <c r="AI4" t="n">
         <v>0.01519262453570233</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01307438920674186</v>
+        <v>0.01516866208830672</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.00211823532896047</v>
+        <v>-2.396244739561251e-05</v>
       </c>
       <c r="AL4" t="n">
         <v>0.08389927892537999</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.05291974901836871</v>
+        <v>0.05417171411440788</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03097952990701128</v>
+        <v>-0.02972756481097211</v>
       </c>
       <c r="AO4" t="n">
         <v>0.4855458738942626</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4839371874929151</v>
+        <v>0.4895450322748661</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.001608686401347426</v>
+        <v>0.003999158380603496</v>
       </c>
       <c r="AR4" t="n">
         <v>-1.086747233072917</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1.075382777622768</v>
+        <v>-1.070011683872768</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01136445545014886</v>
+        <v>0.01673554920014886</v>
       </c>
       <c r="AU4" t="n">
         <v>1.035614013671875</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.9874267578125</v>
+        <v>1.007476806640625</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.048187255859375</v>
+        <v>-0.02813720703125</v>
       </c>
       <c r="AX4" t="n">
         <v>0.05183596825624944</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.04525963755913362</v>
+        <v>0.05875494724980591</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.006576330697115822</v>
+        <v>0.006918978993556472</v>
       </c>
       <c r="BA4" t="n">
         <v>0.1986695070531082</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.2264054258190671</v>
+        <v>0.2550446158729747</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.02773591876595899</v>
+        <v>0.05637510881986657</v>
       </c>
       <c r="BD4" t="n">
         <v>3.059401270783978</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.015456094060484</v>
+        <v>3.022832834272094</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.04394517672349352</v>
+        <v>-0.03656843651188346</v>
       </c>
       <c r="BG4" t="n">
         <v>2.789382934570312</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.536631266276042</v>
+        <v>2.797927856445312</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0.252751668294271</v>
+        <v>0.008544921875</v>
       </c>
       <c r="BJ4" t="n">
         <v>3.405685424804688</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.281695048014323</v>
+        <v>3.339462280273438</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.1239903767903647</v>
+        <v>-0.06622314453125</v>
       </c>
       <c r="BM4" t="n">
         <v>0.0556866719114913</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.05403786370612487</v>
+        <v>0.06371335437783443</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.001648808205366434</v>
+        <v>0.008026682466343131</v>
       </c>
       <c r="BP4" t="n">
         <v>0.2873394097577233</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.3263217622090975</v>
+        <v>0.5278286468931033</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.03898235245137416</v>
+        <v>0.24048923713538</v>
       </c>
       <c r="BS4" t="n">
         <v>1.144826223820816</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.770918267633671</v>
+        <v>1.054064787925218</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.6260920438128554</v>
+        <v>-0.09076143589559793</v>
       </c>
       <c r="BV4" t="n">
         <v>-29.13764953613281</v>
       </c>
       <c r="BW4" t="n">
-        <v>-52.76756286621094</v>
+        <v>-28.64418029785156</v>
       </c>
       <c r="BX4" t="n">
-        <v>-23.62991333007812</v>
+        <v>0.49346923828125</v>
       </c>
       <c r="BY4" t="n">
         <v>52.65665690104166</v>
       </c>
       <c r="BZ4" t="n">
-        <v>31.92471822102864</v>
+        <v>51.55418395996094</v>
       </c>
       <c r="CA4" t="n">
-        <v>-20.73193868001302</v>
+        <v>-1.102472941080727</v>
       </c>
       <c r="CB4" t="n">
         <v>0.2945459374931652</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.2723370010664009</v>
+        <v>0.4039331428055738</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0.02220893642676425</v>
+        <v>0.1093872053124086</v>
       </c>
       <c r="CE4" t="n">
         <v>27.82924092061192</v>
       </c>
       <c r="CF4" t="n">
-        <v>27.28394128794848</v>
+        <v>26.35058935021543</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.5452996326634398</v>
+        <v>-1.47865157039649</v>
       </c>
       <c r="CH4" t="n">
         <v>-0.4574032065309124</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.2151727525027294</v>
+        <v>-0.3995559964812173</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.6725759590336418</v>
+        <v>0.05784721004969506</v>
       </c>
       <c r="CK4" t="n">
         <v>-0.623565673828125</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.2691650390625</v>
+        <v>-0.54046630859375</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.354400634765625</v>
+        <v>0.083099365234375</v>
       </c>
       <c r="CN4" t="n">
         <v>-0.3433990478515625</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.44647216796875</v>
+        <v>-0.2643585205078125</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.7898712158203125</v>
+        <v>0.07904052734375</v>
       </c>
       <c r="CQ4" t="n">
         <v>0.03294570117197831</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.03015270723200239</v>
+        <v>0.03190549183641234</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0.002792993939975928</v>
+        <v>-0.001040209335565971</v>
       </c>
       <c r="CT4" t="n">
         <v>0.1170714717892871</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.2358298655282861</v>
+        <v>0.1482991234458819</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.118758393738999</v>
+        <v>0.03122765165659479</v>
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>gyroy_mean, gyroy_min, gyroy_max</t>
+          <t>gyroy_std_median</t>
         </is>
       </c>
     </row>
@@ -5051,302 +5052,302 @@
         <v>26.27487304622931</v>
       </c>
       <c r="C5" t="n">
-        <v>26.29715315243612</v>
+        <v>25.67420376531461</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02228010620681076</v>
+        <v>-0.6006692809146976</v>
       </c>
       <c r="E5" t="n">
         <v>23.35192837386867</v>
       </c>
       <c r="F5" t="n">
-        <v>22.60439002377358</v>
+        <v>22.77630900171562</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7475383500950876</v>
+        <v>-0.5756193721530529</v>
       </c>
       <c r="H5" t="n">
         <v>27.70391447981227</v>
       </c>
       <c r="I5" t="n">
-        <v>27.72697878612859</v>
+        <v>27.25255106555293</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02306430631631784</v>
+        <v>-0.4513634142593368</v>
       </c>
       <c r="K5" t="n">
         <v>-0.04410977650990774</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.04029672673402863</v>
+        <v>-0.03550489941660668</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003813049775879103</v>
+        <v>0.008604877093301058</v>
       </c>
       <c r="N5" t="n">
         <v>-0.3970947265625</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4489702497209822</v>
+        <v>-0.4145333426339285</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.05187552315848215</v>
+        <v>-0.01743861607142855</v>
       </c>
       <c r="Q5" t="n">
         <v>0.3271484375</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5728628976004464</v>
+        <v>0.3086357116699219</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2457144601004464</v>
+        <v>-0.01851272583007812</v>
       </c>
       <c r="T5" t="n">
         <v>0.2777774537554547</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3022152880036155</v>
+        <v>0.3205172204168586</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02443783424816082</v>
+        <v>0.04273976666140389</v>
       </c>
       <c r="W5" t="n">
         <v>0.7321182187780035</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8913700036817463</v>
+        <v>0.858538364379414</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1592517849037428</v>
+        <v>0.1264201456014105</v>
       </c>
       <c r="Z5" t="n">
         <v>0.02820479957969277</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01482146608936322</v>
+        <v>0.01713846597825305</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.01338333349032955</v>
+        <v>-0.01106633360143972</v>
       </c>
       <c r="AC5" t="n">
         <v>-0.1122262137276786</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.2938052906709559</v>
+        <v>-0.1109690946691176</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.1815790769432773</v>
+        <v>0.001257119058560935</v>
       </c>
       <c r="AF5" t="n">
         <v>0.2889811197916667</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2323957170758928</v>
+        <v>0.1813616071428572</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.05658540271577384</v>
+        <v>-0.1076195126488095</v>
       </c>
       <c r="AI5" t="n">
         <v>0.1723562024781092</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.147892221052437</v>
+        <v>0.1560841025821295</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02446398142567219</v>
+        <v>-0.01627209989597977</v>
       </c>
       <c r="AL5" t="n">
         <v>0.4176022833368329</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.4600999349609411</v>
+        <v>0.4211893335965746</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.04249765162410823</v>
+        <v>0.003587050259741764</v>
       </c>
       <c r="AO5" t="n">
         <v>0.5903527134747925</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.6203194993400953</v>
+        <v>0.5795118333046041</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.02996678586530288</v>
+        <v>-0.01084088017018836</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.1653529575892857</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.2987455480238971</v>
+        <v>-0.08887154715401786</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.1333925904346114</v>
+        <v>0.07648141043526786</v>
       </c>
       <c r="AU5" t="n">
         <v>1.129976399739583</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.073390415736607</v>
+        <v>1.205605643136161</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.0565859840029761</v>
+        <v>0.07562924339657751</v>
       </c>
       <c r="AX5" t="n">
         <v>0.5759892082408165</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.5816952614758941</v>
+        <v>0.6073535170855575</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.005706053235077668</v>
+        <v>0.03136430884474106</v>
       </c>
       <c r="BA5" t="n">
         <v>1.01492990425375</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.260600127627699</v>
+        <v>1.146848311754441</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.2456702233739489</v>
+        <v>0.1319184075006916</v>
       </c>
       <c r="BD5" t="n">
         <v>3.160245464120433</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.066914420500683</v>
+        <v>3.116558894067574</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.09333104361975009</v>
+        <v>-0.0436865700528597</v>
       </c>
       <c r="BG5" t="n">
         <v>2.350387573242188</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.385676457331731</v>
+        <v>2.618751525878906</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.03528888408954334</v>
+        <v>0.2683639526367188</v>
       </c>
       <c r="BJ5" t="n">
         <v>3.858530680338542</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.567316391888787</v>
+        <v>3.729991912841797</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.2912142884497548</v>
+        <v>-0.1285387674967446</v>
       </c>
       <c r="BM5" t="n">
         <v>0.7715556682964702</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.2118105511323345</v>
+        <v>0.7397130579171165</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.5597451171641357</v>
+        <v>-0.03184261037935365</v>
       </c>
       <c r="BP5" t="n">
         <v>7.862638968640897</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.115811119814829</v>
+        <v>5.34029372447486</v>
       </c>
       <c r="BR5" t="n">
-        <v>-4.746827848826067</v>
+        <v>-2.522345244166037</v>
       </c>
       <c r="BS5" t="n">
         <v>1.340757338872878</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.776885301582464</v>
+        <v>1.157127625033735</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.4361279627095853</v>
+        <v>-0.1836297138391429</v>
       </c>
       <c r="BV5" t="n">
         <v>-0.551788330078125</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.1987950942095587</v>
+        <v>-0.5273640950520834</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.3529932358685663</v>
+        <v>0.02442423502604163</v>
       </c>
       <c r="BY5" t="n">
         <v>3.723983764648438</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.49010995718149</v>
+        <v>3.338643391927083</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.7661261925330525</v>
+        <v>-0.385340372721354</v>
       </c>
       <c r="CB5" t="n">
         <v>2.149889152497679</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.099022653573709</v>
+        <v>2.777920999717442</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.05086649892397022</v>
+        <v>0.6280318472197632</v>
       </c>
       <c r="CE5" t="n">
         <v>13.94649791700223</v>
       </c>
       <c r="CF5" t="n">
-        <v>8.541705421153475</v>
+        <v>13.86144829415063</v>
       </c>
       <c r="CG5" t="n">
-        <v>-5.40479249584876</v>
+        <v>-0.08504962285160644</v>
       </c>
       <c r="CH5" t="n">
         <v>-0.4274989108105639</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.2266373412887078</v>
+        <v>-0.438354825770824</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.6541362520992717</v>
+        <v>-0.01085591496026006</v>
       </c>
       <c r="CK5" t="n">
         <v>-0.817962646484375</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.2312469482421875</v>
+        <v>-1.072921752929688</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.5867156982421875</v>
+        <v>-0.2549591064453125</v>
       </c>
       <c r="CN5" t="n">
         <v>-0.0464630126953125</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.6040191650390625</v>
+        <v>0.07049560546875</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.650482177734375</v>
+        <v>0.1169586181640625</v>
       </c>
       <c r="CQ5" t="n">
         <v>0.1046348277573617</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.08409884279583989</v>
+        <v>0.1020941425113425</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.02053598496152177</v>
+        <v>-0.002540685246019164</v>
       </c>
       <c r="CT5" t="n">
         <v>0.6433001736981472</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.3838181216800131</v>
+        <v>0.3435099751502918</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.2594820520181341</v>
+        <v>-0.2997901985478554</v>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>accz_min, gyroy_min, gyroy_std_max</t>
+          <t>accz_min</t>
         </is>
       </c>
     </row>
@@ -5360,302 +5361,302 @@
         <v>22.55086840662369</v>
       </c>
       <c r="C6" t="n">
-        <v>22.4148898960505</v>
+        <v>21.97497159681689</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1359785105731852</v>
+        <v>-0.5758968098067996</v>
       </c>
       <c r="E6" t="n">
         <v>19.61936564506168</v>
       </c>
       <c r="F6" t="n">
-        <v>20.40581979974169</v>
+        <v>18.98415865869614</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7864541546800048</v>
+        <v>-0.6352069863655387</v>
       </c>
       <c r="H6" t="n">
         <v>23.97816999783493</v>
       </c>
       <c r="I6" t="n">
-        <v>23.67547710535883</v>
+        <v>23.47204516221995</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3026928924760917</v>
+        <v>-0.5061248356149726</v>
       </c>
       <c r="K6" t="n">
         <v>-0.03798876053247696</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.03533871746038806</v>
+        <v>-0.03482877430898366</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002650043072088902</v>
+        <v>0.003159986223493304</v>
       </c>
       <c r="N6" t="n">
         <v>-0.06876220703124999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.11907958984375</v>
+        <v>-0.06441824776785714</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.05031738281250001</v>
+        <v>0.004343959263392858</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.0003987630208333333</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.01172310965401786</v>
+        <v>0.001661028180803571</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.01132434663318452</v>
+        <v>0.002059791201636905</v>
       </c>
       <c r="T6" t="n">
         <v>0.04672970298579943</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03375343654977193</v>
+        <v>0.04207129335325369</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.01297626643602749</v>
+        <v>-0.004658409632545733</v>
       </c>
       <c r="W6" t="n">
         <v>0.1071074520472561</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07332047364408752</v>
+        <v>0.06696354584625777</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.03378697840316855</v>
+        <v>-0.04014390620099829</v>
       </c>
       <c r="Z6" t="n">
         <v>0.01075538733066657</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001158344836894414</v>
+        <v>0.01106462410826335</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.01063955284697712</v>
+        <v>0.000309236777596783</v>
       </c>
       <c r="AC6" t="n">
         <v>0.003810337611607143</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.008892352764423076</v>
+        <v>0.002541678292410714</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.01270269037603022</v>
+        <v>-0.001268659319196429</v>
       </c>
       <c r="AF6" t="n">
         <v>0.0167724609375</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.01837158203125</v>
+        <v>0.03028215680803572</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.001599121093749999</v>
+        <v>0.01350969587053572</v>
       </c>
       <c r="AI6" t="n">
         <v>0.008255943143066932</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.005347117395997514</v>
+        <v>0.009546124048205609</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.002908825747069418</v>
+        <v>0.001290180905138678</v>
       </c>
       <c r="AL6" t="n">
         <v>0.03627543319162506</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.02041023571685495</v>
+        <v>0.04008312173233591</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.01586519747477011</v>
+        <v>0.003807688540710848</v>
       </c>
       <c r="AO6" t="n">
         <v>0.9406028034922842</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.935967586085404</v>
+        <v>0.9424050378172697</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.004635217406880221</v>
+        <v>0.001802234324985497</v>
       </c>
       <c r="AR6" t="n">
         <v>0.897979736328125</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.908416748046875</v>
+        <v>0.9069780622209821</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.01043701171875</v>
+        <v>0.008998325892857095</v>
       </c>
       <c r="AU6" t="n">
         <v>0.9748779296875</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.9758770282451923</v>
+        <v>0.9718279157366071</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0009990985576923128</v>
+        <v>-0.003050013950892883</v>
       </c>
       <c r="AX6" t="n">
         <v>0.04417926639954546</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.03269971911168738</v>
+        <v>0.04335982624210842</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.01147954728785808</v>
+        <v>-0.0008194401574370402</v>
       </c>
       <c r="BA6" t="n">
         <v>0.1773595817674142</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1047282750216218</v>
+        <v>0.1653174643986417</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.07263130674579246</v>
+        <v>-0.0120421173687725</v>
       </c>
       <c r="BD6" t="n">
         <v>3.186943897834191</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.044568566140395</v>
+        <v>3.126028882639773</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.1423753316937955</v>
+        <v>-0.06091501519441822</v>
       </c>
       <c r="BG6" t="n">
         <v>3.07745361328125</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.999267578125</v>
+        <v>3.039321899414062</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.07818603515625</v>
+        <v>-0.0381317138671875</v>
       </c>
       <c r="BJ6" t="n">
         <v>3.335154215494792</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.115834554036458</v>
+        <v>3.211822509765625</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.219319661458333</v>
+        <v>-0.1233317057291665</v>
       </c>
       <c r="BM6" t="n">
         <v>0.03399209918638069</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.02977637105755405</v>
+        <v>0.03254519904977722</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.004215728128826642</v>
+        <v>-0.001446900136603473</v>
       </c>
       <c r="BP6" t="n">
         <v>0.3198940040805111</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1845916871973962</v>
+        <v>0.2209298314018331</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.1353023168831149</v>
+        <v>-0.09896417267867799</v>
       </c>
       <c r="BS6" t="n">
         <v>1.342341838738857</v>
       </c>
       <c r="BT6" t="n">
-        <v>1.748856511626153</v>
+        <v>1.190712003644816</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.4065146728872957</v>
+        <v>-0.151629835094041</v>
       </c>
       <c r="BV6" t="n">
         <v>0.091217041015625</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.5954742431640625</v>
+        <v>-0.5709075927734375</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.5042572021484375</v>
+        <v>-0.6621246337890625</v>
       </c>
       <c r="BY6" t="n">
         <v>2.645294189453125</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.673425674438477</v>
+        <v>2.54510498046875</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.02813148498535156</v>
+        <v>-0.100189208984375</v>
       </c>
       <c r="CB6" t="n">
         <v>0.08424161326249768</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.02618349104404665</v>
+        <v>0.05882702711154499</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.05805812221845104</v>
+        <v>-0.0254145861509527</v>
       </c>
       <c r="CE6" t="n">
         <v>3.420764077268906</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.08372591002952</v>
+        <v>4.658788195652564</v>
       </c>
       <c r="CG6" t="n">
-        <v>-1.337038167239386</v>
+        <v>1.238024118383658</v>
       </c>
       <c r="CH6" t="n">
         <v>-0.3424840462513459</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.2228309430369014</v>
+        <v>-0.3989396942838851</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.5653149892882473</v>
+        <v>-0.05645564803253916</v>
       </c>
       <c r="CK6" t="n">
         <v>-0.3907877604166667</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.1853179931640625</v>
+        <v>-0.4299163818359375</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.5761057535807292</v>
+        <v>-0.03912862141927081</v>
       </c>
       <c r="CN6" t="n">
         <v>-0.2995707194010417</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.3034703871783088</v>
+        <v>-0.3337860107421875</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.6030411065793505</v>
+        <v>-0.03421529134114581</v>
       </c>
       <c r="CQ6" t="n">
         <v>0.04205851117668701</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.05177690759328561</v>
+        <v>0.03694867329500973</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.009718396416598593</v>
+        <v>-0.005109837881677286</v>
       </c>
       <c r="CT6" t="n">
         <v>0.06710507101158</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.08285324131053315</v>
+        <v>0.06337499110215</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.01574817029895315</v>
+        <v>-0.003730079909430001</v>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>accz_std_max, gyroy_min, gyroy_std_median, gyroy_std_max</t>
+          <t>gyroy_min, gyroy_std_max</t>
         </is>
       </c>
     </row>
@@ -5669,302 +5670,302 @@
         <v>18.86930651240748</v>
       </c>
       <c r="C7" t="n">
-        <v>19.6095490270898</v>
+        <v>18.52027516461937</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7402425146823219</v>
+        <v>-0.3490313477881095</v>
       </c>
       <c r="E7" t="n">
         <v>14.76981486810349</v>
       </c>
       <c r="F7" t="n">
-        <v>15.07939511894781</v>
+        <v>14.85397460980112</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3095802508443235</v>
+        <v>0.08415974169762919</v>
       </c>
       <c r="H7" t="n">
         <v>20.52646496592924</v>
       </c>
       <c r="I7" t="n">
-        <v>21.0788775852417</v>
+        <v>20.04913491829697</v>
       </c>
       <c r="J7" t="n">
-        <v>0.552412619312463</v>
+        <v>-0.4773300476322611</v>
       </c>
       <c r="K7" t="n">
         <v>-0.03971628132195825</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.03136946056814108</v>
+        <v>-0.03838882586412971</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008346820753817166</v>
+        <v>0.001327455457828544</v>
       </c>
       <c r="N7" t="n">
         <v>-0.08839111328125</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.05661446707589286</v>
+        <v>-0.05603745404411765</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03177664620535715</v>
+        <v>0.03235365923713236</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.02077229817708333</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008209228515625</v>
+        <v>-0.02084786551339286</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02898152669270833</v>
+        <v>-7.556733630952397e-05</v>
       </c>
       <c r="T7" t="n">
         <v>0.02638174171659131</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02156053016171558</v>
+        <v>0.02604356073604119</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.004821211554875731</v>
+        <v>-0.0003381809805501207</v>
       </c>
       <c r="W7" t="n">
         <v>0.05046444098388737</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0378871501255362</v>
+        <v>0.0452705661946899</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.01257729085835117</v>
+        <v>-0.005193874789197465</v>
       </c>
       <c r="Z7" t="n">
         <v>0.009348840911455351</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0002972190477558779</v>
+        <v>0.009277366124813433</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.00964605995921123</v>
+        <v>-7.147478664191846e-05</v>
       </c>
       <c r="AC7" t="n">
         <v>0.00384521484375</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.00860126201923077</v>
+        <v>0.003980364118303571</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.01244647686298077</v>
+        <v>0.0001351492745535711</v>
       </c>
       <c r="AF7" t="n">
         <v>0.01560465494791667</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.007281135110294118</v>
+        <v>0.0167236328125</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.008323519837622549</v>
+        <v>0.001118977864583334</v>
       </c>
       <c r="AI7" t="n">
         <v>0.004259029270117343</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.003778913623159779</v>
+        <v>0.004233781205543137</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0004801156469575632</v>
+        <v>-2.524806457420564e-05</v>
       </c>
       <c r="AL7" t="n">
         <v>0.01557564689684287</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.01733430949602273</v>
+        <v>0.0154940957244737</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.00175866259917986</v>
+        <v>-8.155117236916323e-05</v>
       </c>
       <c r="AO7" t="n">
         <v>0.9419387255125846</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.9366707991652153</v>
+        <v>0.9438677374718575</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.005267926347369278</v>
+        <v>0.001929011959272864</v>
       </c>
       <c r="AR7" t="n">
         <v>0.9039347330729167</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.9067711463341346</v>
+        <v>0.9188276018415179</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.002836413261217863</v>
+        <v>0.01489286876860119</v>
       </c>
       <c r="AU7" t="n">
         <v>0.9687761579241071</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.9719566932091346</v>
+        <v>0.9620157877604166</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.003180535285027486</v>
+        <v>-0.006760370163690466</v>
       </c>
       <c r="AX7" t="n">
         <v>0.02454215629180911</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.02685181189950401</v>
+        <v>0.02345510306861034</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.002309655607694902</v>
+        <v>-0.001087053223198766</v>
       </c>
       <c r="BA7" t="n">
         <v>0.07276922476450014</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.07959373486212172</v>
+        <v>0.1035014311595208</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.006824510097621583</v>
+        <v>0.03073220639502067</v>
       </c>
       <c r="BD7" t="n">
         <v>3.182311135479528</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.026604342634728</v>
+        <v>3.124590463528027</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1557067928447995</v>
+        <v>-0.05772067195150132</v>
       </c>
       <c r="BG7" t="n">
         <v>3.112345377604167</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.869334501378677</v>
+        <v>3.068695068359375</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.2430108762254899</v>
+        <v>-0.04365030924479152</v>
       </c>
       <c r="BJ7" t="n">
         <v>3.390981038411458</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.148269653320312</v>
+        <v>3.285589218139648</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.242711385091146</v>
+        <v>-0.10539182027181</v>
       </c>
       <c r="BM7" t="n">
         <v>0.02673269767843421</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.02869114315713148</v>
+        <v>0.02675497729421825</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001958445478697272</v>
+        <v>2.227961578404186e-05</v>
       </c>
       <c r="BP7" t="n">
         <v>0.3147434936082267</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.2168615132503336</v>
+        <v>0.2879807177706336</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.09788198035789308</v>
+        <v>-0.02676277583759307</v>
       </c>
       <c r="BS7" t="n">
         <v>1.322847378559601</v>
       </c>
       <c r="BT7" t="n">
-        <v>1.713002873509434</v>
+        <v>1.192265143761268</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.3901554949498331</v>
+        <v>-0.1305822347983334</v>
       </c>
       <c r="BV7" t="n">
         <v>-0.5912017822265624</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.9508738798253676</v>
+        <v>0.184783935546875</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.54207566205193</v>
+        <v>0.7759857177734374</v>
       </c>
       <c r="BY7" t="n">
         <v>2.783864339192708</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.931074876051682</v>
+        <v>1.814371744791667</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.147210536858974</v>
+        <v>-0.9694925944010417</v>
       </c>
       <c r="CB7" t="n">
         <v>0.02346747031490767</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.02679228853442933</v>
+        <v>0.02464288367996408</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.003324818219521665</v>
+        <v>0.001175413365056409</v>
       </c>
       <c r="CE7" t="n">
         <v>6.647560990587892</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.245034417430444</v>
+        <v>7.340182163519817</v>
       </c>
       <c r="CG7" t="n">
-        <v>-3.402526573157448</v>
+        <v>0.6926211729319247</v>
       </c>
       <c r="CH7" t="n">
         <v>-0.3007201007288745</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.2516773011521047</v>
+        <v>-0.3652810618888199</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.5523974018809792</v>
+        <v>-0.06456096115994542</v>
       </c>
       <c r="CK7" t="n">
         <v>-0.432159423828125</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.09016149184283088</v>
+        <v>-0.466552734375</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.5223209156709558</v>
+        <v>-0.034393310546875</v>
       </c>
       <c r="CN7" t="n">
         <v>-0.2188212076822917</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.298004150390625</v>
+        <v>-0.2899932861328125</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.5168253580729166</v>
+        <v>-0.07117207845052084</v>
       </c>
       <c r="CQ7" t="n">
         <v>0.0742465177446809</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.06519306895586363</v>
+        <v>0.06134749957334251</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.009053448788817267</v>
+        <v>-0.01289901817133839</v>
       </c>
       <c r="CT7" t="n">
         <v>0.1353714038935403</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.09818887347571177</v>
+        <v>0.1056857125806994</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0.03718253041782855</v>
+        <v>-0.02968569131284088</v>
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>gyroy_min</t>
         </is>
       </c>
     </row>
@@ -5978,298 +5979,298 @@
         <v>14.94143829589093</v>
       </c>
       <c r="C8" t="n">
-        <v>14.56664001784816</v>
+        <v>15.01198335725824</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3747982780427623</v>
+        <v>0.07054506136731042</v>
       </c>
       <c r="E8" t="n">
         <v>11.62435635929374</v>
       </c>
       <c r="F8" t="n">
-        <v>12.62135602739823</v>
+        <v>11.27478279891552</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9969996681044879</v>
+        <v>-0.3495735603782233</v>
       </c>
       <c r="H8" t="n">
         <v>16.29093361737037</v>
       </c>
       <c r="I8" t="n">
-        <v>15.67941159451611</v>
+        <v>16.33840926890201</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6115220228542526</v>
+        <v>0.04747565153164501</v>
       </c>
       <c r="K8" t="n">
         <v>-0.03330706694659332</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.03765165133668704</v>
+        <v>-0.03169752673613939</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.00434458439009372</v>
+        <v>0.001609540210453932</v>
       </c>
       <c r="N8" t="n">
         <v>-0.05662027994791666</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0662372295673077</v>
+        <v>-0.05250767299107143</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.009616949619391031</v>
+        <v>0.004112606956845233</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.0001871744791666667</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.004708426339285714</v>
+        <v>0.006849016462053571</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.004521251860119048</v>
+        <v>0.007036190941220237</v>
       </c>
       <c r="T8" t="n">
         <v>0.0236101494653442</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01905818062002168</v>
+        <v>0.0186546922494316</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.004551968845322524</v>
+        <v>-0.004955457215912604</v>
       </c>
       <c r="W8" t="n">
         <v>0.05714820098157523</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06241303241487501</v>
+        <v>0.06318408548992828</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005264831433299783</v>
+        <v>0.006035884508353052</v>
       </c>
       <c r="Z8" t="n">
         <v>0.008452891916370003</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.002135215587599639</v>
+        <v>0.008474885635445689</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.01058810750396964</v>
+        <v>2.199371907568581e-05</v>
       </c>
       <c r="AC8" t="n">
         <v>0.0016357421875</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.01291329520089286</v>
+        <v>-0.0009329659598214286</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.01454903738839286</v>
+        <v>-0.002568708147321429</v>
       </c>
       <c r="AF8" t="n">
         <v>0.01962890625</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.01365152994791667</v>
+        <v>0.01985931396484375</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.005977376302083335</v>
+        <v>0.0002304077148437486</v>
       </c>
       <c r="AI8" t="n">
         <v>0.005036446155883667</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004275801342346263</v>
+        <v>0.004226025324523385</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.0007606448135374045</v>
+        <v>-0.0008104208313602819</v>
       </c>
       <c r="AL8" t="n">
         <v>0.02455148079051056</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.02042449058075216</v>
+        <v>0.01997659260668615</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.004126990209758402</v>
+        <v>-0.004574888183824413</v>
       </c>
       <c r="AO8" t="n">
         <v>0.943651310786931</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.9359411638968699</v>
+        <v>0.9457294049665346</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.007710146890061109</v>
+        <v>0.002078094179603585</v>
       </c>
       <c r="AR8" t="n">
         <v>0.9149169921875</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.9032156808035714</v>
+        <v>0.9258384704589844</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0.0117013113839286</v>
+        <v>0.01092147827148438</v>
       </c>
       <c r="AU8" t="n">
         <v>0.9873087565104167</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9708208356584821</v>
+        <v>0.9924235026041667</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.01648792085193462</v>
+        <v>0.005114746093749956</v>
       </c>
       <c r="AX8" t="n">
         <v>0.02332897441945894</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.02418212651025067</v>
+        <v>0.0177545449694903</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0008531520907917312</v>
+        <v>-0.005574429449968634</v>
       </c>
       <c r="BA8" t="n">
         <v>0.1225773427473577</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.09497724809193277</v>
+        <v>0.126523965041166</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0.0276000946554249</v>
+        <v>0.003946622293808336</v>
       </c>
       <c r="BD8" t="n">
         <v>3.096716468729084</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.900894547659528</v>
+        <v>3.046549154375414</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.1958219210695562</v>
+        <v>-0.05016731435366983</v>
       </c>
       <c r="BG8" t="n">
         <v>2.959818522135417</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.719563802083333</v>
+        <v>2.89202880859375</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0.240254720052083</v>
+        <v>-0.06778971354166652</v>
       </c>
       <c r="BJ8" t="n">
         <v>3.3436279296875</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.201141357421875</v>
+        <v>3.2513427734375</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0.142486572265625</v>
+        <v>-0.09228515625</v>
       </c>
       <c r="BM8" t="n">
         <v>0.02880333314036244</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.03203213174175696</v>
+        <v>0.02769111490968575</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.003228798601394522</v>
+        <v>-0.001112218230676688</v>
       </c>
       <c r="BP8" t="n">
         <v>0.2670196883771547</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.2645136943853766</v>
+        <v>0.2694151387537235</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0.002505993991778088</v>
+        <v>0.002395450376568742</v>
       </c>
       <c r="BS8" t="n">
         <v>1.176921271484756</v>
       </c>
       <c r="BT8" t="n">
-        <v>1.493394981868313</v>
+        <v>1.054910792786457</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.3164737103835573</v>
+        <v>-0.1220104786982983</v>
       </c>
       <c r="BV8" t="n">
         <v>-0.09452819824218762</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.1201273600260417</v>
+        <v>0.013885498046875</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.2146555582682293</v>
+        <v>0.1084136962890626</v>
       </c>
       <c r="BY8" t="n">
         <v>3.408426920572917</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.944264729817708</v>
+        <v>2.724761962890625</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.535837809244792</v>
+        <v>-0.6836649576822915</v>
       </c>
       <c r="CB8" t="n">
         <v>0.03112052335302486</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.02723946575566247</v>
+        <v>0.02439187949422751</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0.003881057597362392</v>
+        <v>-0.006728643858797352</v>
       </c>
       <c r="CE8" t="n">
         <v>9.07233647587671</v>
       </c>
       <c r="CF8" t="n">
-        <v>5.865770410718853</v>
+        <v>4.866209491670103</v>
       </c>
       <c r="CG8" t="n">
-        <v>-3.206566065157857</v>
+        <v>-4.206126984206607</v>
       </c>
       <c r="CH8" t="n">
         <v>-0.232924987438728</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.2892292318437031</v>
+        <v>-0.2972764471885455</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.5221542192824311</v>
+        <v>-0.06435145974981749</v>
       </c>
       <c r="CK8" t="n">
         <v>-0.4520975748697917</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.010467529296875</v>
+        <v>-0.4286702473958333</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.4416300455729167</v>
+        <v>0.02342732747395837</v>
       </c>
       <c r="CN8" t="n">
         <v>0.005340576171875</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.6114959716796875</v>
+        <v>-0.06553201114430147</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.6061553955078125</v>
+        <v>-0.07087258731617647</v>
       </c>
       <c r="CQ8" t="n">
         <v>0.1086149511100198</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.09951038658189833</v>
+        <v>0.06942559414593737</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0.009104564528121459</v>
+        <v>-0.03918935696408242</v>
       </c>
       <c r="CT8" t="n">
         <v>0.1591444827183698</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.1598941511403252</v>
+        <v>0.1447763816633835</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0007496684219554239</v>
+        <v>-0.01436810105498632</v>
       </c>
       <c r="EP8" t="inlineStr">
         <is>
@@ -6287,302 +6288,302 @@
         <v>13.83326063226469</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95007283868499</v>
+        <v>14.34601046541521</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1168122064203025</v>
+        <v>0.5127498331505222</v>
       </c>
       <c r="E9" t="n">
         <v>10.98029442975796</v>
       </c>
       <c r="F9" t="n">
-        <v>12.65276005018413</v>
+        <v>11.48701719632026</v>
       </c>
       <c r="G9" t="n">
-        <v>1.672465620426168</v>
+        <v>0.5067227665622962</v>
       </c>
       <c r="H9" t="n">
         <v>15.30857202525175</v>
       </c>
       <c r="I9" t="n">
-        <v>15.20285283042407</v>
+        <v>15.48631991302608</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1057191948276763</v>
+        <v>0.177747887774327</v>
       </c>
       <c r="K9" t="n">
         <v>-0.03719316222857981</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0329582687151168</v>
+        <v>-0.0362365304776712</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004234893513463012</v>
+        <v>0.0009566317509086056</v>
       </c>
       <c r="N9" t="n">
         <v>-0.08525797526041666</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06367710658482142</v>
+        <v>-0.04851481119791667</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02158086867559524</v>
+        <v>0.03674316406249999</v>
       </c>
       <c r="Q9" t="n">
         <v>0.0004109700520833333</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0011962890625</v>
+        <v>-0.003827776227678571</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0007853190104166667</v>
+        <v>-0.004238746279761904</v>
       </c>
       <c r="T9" t="n">
         <v>0.01947610962840841</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01752898497682866</v>
+        <v>0.0106966365685618</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.001947124651579743</v>
+        <v>-0.00877947305984661</v>
       </c>
       <c r="W9" t="n">
         <v>0.04995497282592934</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05810264395740967</v>
+        <v>0.03617690894934331</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.008147671131480336</v>
+        <v>-0.01377806387658603</v>
       </c>
       <c r="Z9" t="n">
         <v>0.007963853678712903</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.001991544820198907</v>
+        <v>0.008650759068227969</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.00995539849891181</v>
+        <v>0.0006869053895150658</v>
       </c>
       <c r="AC9" t="n">
         <v>-0.007564290364583334</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.007707868303571429</v>
+        <v>0.000339508056640625</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.0001435779389880954</v>
+        <v>0.007903798421223959</v>
       </c>
       <c r="AF9" t="n">
         <v>0.0208740234375</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01018415178571429</v>
+        <v>0.02121843610491072</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.01068987165178571</v>
+        <v>0.0003444126674107158</v>
       </c>
       <c r="AI9" t="n">
         <v>0.004646793859509393</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.003841494829003475</v>
+        <v>0.003409507201168104</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.0008052990305059179</v>
+        <v>-0.001237286658341289</v>
       </c>
       <c r="AL9" t="n">
         <v>0.03017511941716322</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.03232117907058291</v>
+        <v>0.01854703280875322</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.002146059653419685</v>
+        <v>-0.01162808660841</v>
       </c>
       <c r="AO9" t="n">
         <v>0.9425747375692959</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.9362846549565206</v>
+        <v>0.9461849509478847</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.006290082612775305</v>
+        <v>0.0036102133785888</v>
       </c>
       <c r="AR9" t="n">
         <v>0.9027579171316964</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.9011666434151786</v>
+        <v>0.9291599818638393</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.001591273716517794</v>
+        <v>0.0264020647321429</v>
       </c>
       <c r="AU9" t="n">
         <v>0.9630301339285714</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.9529825846354166</v>
+        <v>0.9646402994791666</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.01004754929315477</v>
+        <v>0.001610165550595233</v>
       </c>
       <c r="AX9" t="n">
         <v>0.01605324462269583</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01827474818511866</v>
+        <v>0.01008972748473597</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.00222150356242283</v>
+        <v>-0.005963517137959855</v>
       </c>
       <c r="BA9" t="n">
         <v>0.1513588382979006</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.09666877462266454</v>
+        <v>0.09122384839440421</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.0546900636752361</v>
+        <v>-0.06013498990349643</v>
       </c>
       <c r="BD9" t="n">
         <v>2.996147603496139</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.74057003981465</v>
+        <v>2.96791064341801</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.2555775636814897</v>
+        <v>-0.02823696007812915</v>
       </c>
       <c r="BG9" t="n">
         <v>2.763926188151042</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.59124755859375</v>
+        <v>2.73651123046875</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0.1726786295572915</v>
+        <v>-0.02741495768229152</v>
       </c>
       <c r="BJ9" t="n">
         <v>3.233718872070312</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.843856811523438</v>
+        <v>3.168563842773438</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0.389862060546875</v>
+        <v>-0.065155029296875</v>
       </c>
       <c r="BM9" t="n">
         <v>0.02857852419494233</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.02849778993350898</v>
+        <v>0.02479156823609809</v>
       </c>
       <c r="BO9" t="n">
-        <v>-8.073426143335311e-05</v>
+        <v>-0.003786955958844245</v>
       </c>
       <c r="BP9" t="n">
         <v>0.8263520066205692</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.2126644193158656</v>
+        <v>0.2982350883140516</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0.6136875873047035</v>
+        <v>-0.5281169183065175</v>
       </c>
       <c r="BS9" t="n">
         <v>1.001740930225927</v>
       </c>
       <c r="BT9" t="n">
-        <v>1.213994533092508</v>
+        <v>0.890049607270022</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.2122536028665809</v>
+        <v>-0.1116913229559052</v>
       </c>
       <c r="BV9" t="n">
         <v>-1.105570475260417</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0.4913330078125</v>
+        <v>-1.364517211914062</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.6142374674479167</v>
+        <v>-0.2589467366536458</v>
       </c>
       <c r="BY9" t="n">
         <v>2.072072347005208</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.527902456430288</v>
+        <v>2.13322639465332</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.45583010942508</v>
+        <v>0.06115404764811183</v>
       </c>
       <c r="CB9" t="n">
         <v>0.02682928526625366</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.02497120417338136</v>
+        <v>0.0250550639832631</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0.001858081092872301</v>
+        <v>-0.001774221282990561</v>
       </c>
       <c r="CE9" t="n">
         <v>10.70805126946162</v>
       </c>
       <c r="CF9" t="n">
-        <v>4.969140487153683</v>
+        <v>4.599198522753772</v>
       </c>
       <c r="CG9" t="n">
-        <v>-5.738910782307939</v>
+        <v>-6.10885274670785</v>
       </c>
       <c r="CH9" t="n">
         <v>-0.2320905963020146</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.2483894137441799</v>
+        <v>-0.290428890938654</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.4804800100461945</v>
+        <v>-0.05833829463663939</v>
       </c>
       <c r="CK9" t="n">
         <v>-0.330047607421875</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.144195556640625</v>
+        <v>-0.3914642333984375</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.4742431640625</v>
+        <v>-0.0614166259765625</v>
       </c>
       <c r="CN9" t="n">
         <v>-0.09769694010416667</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.3562164306640625</v>
+        <v>-0.2058614095052083</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.4539133707682292</v>
+        <v>-0.1081644694010417</v>
       </c>
       <c r="CQ9" t="n">
         <v>0.1057622158728014</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.115639103903637</v>
+        <v>0.06511990934253804</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.009876888030835557</v>
+        <v>-0.04064230653026339</v>
       </c>
       <c r="CT9" t="n">
         <v>0.293463696844701</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.1599557394829663</v>
+        <v>0.1132938273047584</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0.1335079573617347</v>
+        <v>-0.1801698695399425</v>
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>T8_min_C, accz_std_max, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>accz_std_max, gyroy_std_max</t>
         </is>
       </c>
     </row>
@@ -6596,302 +6597,302 @@
         <v>13.017440836056</v>
       </c>
       <c r="C10" t="n">
-        <v>13.7298892288471</v>
+        <v>14.47109849883414</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7124483927910941</v>
+        <v>1.453657662778141</v>
       </c>
       <c r="E10" t="n">
         <v>10.09522473829066</v>
       </c>
       <c r="F10" t="n">
-        <v>11.88398398714774</v>
+        <v>12.27494456020747</v>
       </c>
       <c r="G10" t="n">
-        <v>1.788759248857081</v>
+        <v>2.179719821916814</v>
       </c>
       <c r="H10" t="n">
         <v>13.99520229375056</v>
       </c>
       <c r="I10" t="n">
-        <v>14.66134058270546</v>
+        <v>15.24886041243957</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6661382889548992</v>
+        <v>1.253658118689016</v>
       </c>
       <c r="K10" t="n">
         <v>-0.03315936714177786</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0365459927258474</v>
+        <v>-0.0321075482475263</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.003386625584069533</v>
+        <v>0.001051818894251565</v>
       </c>
       <c r="N10" t="n">
         <v>-0.07406005859375001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06649576822916667</v>
+        <v>-0.07638985770089286</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007564290364583337</v>
+        <v>-0.002329799107142858</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.005832672119140625</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01061293658088235</v>
+        <v>-8.138020833333333e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01644560870002298</v>
+        <v>0.005751291910807292</v>
       </c>
       <c r="T10" t="n">
         <v>0.01510489669116456</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01295296158282232</v>
+        <v>0.01326864114215124</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.002151935108342239</v>
+        <v>-0.001836255549013319</v>
       </c>
       <c r="W10" t="n">
         <v>0.03676449488438729</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05097870817587867</v>
+        <v>0.06022030369010742</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01421421329149138</v>
+        <v>0.02345580880572012</v>
       </c>
       <c r="Z10" t="n">
         <v>0.008578431835052558</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.001916418829839305</v>
+        <v>0.01011601064000194</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.01049485066489186</v>
+        <v>0.001537578804949386</v>
       </c>
       <c r="AC10" t="n">
         <v>0.001106770833333333</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.010009765625</v>
+        <v>0.005610874720982143</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01111653645833333</v>
+        <v>0.004504103887648809</v>
       </c>
       <c r="AF10" t="n">
         <v>0.01914760044642857</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002410888671875</v>
+        <v>0.01857376098632812</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.01673671177455357</v>
+        <v>-0.0005738394601004469</v>
       </c>
       <c r="AI10" t="n">
         <v>0.003674844040791312</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002990072404355133</v>
+        <v>0.003527503212267413</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.0006847716364361787</v>
+        <v>-0.0001473408285238989</v>
       </c>
       <c r="AL10" t="n">
         <v>0.02279290727336419</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.01699959296159637</v>
+        <v>0.01634874093187463</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.005793314311767824</v>
+        <v>-0.006444166341489567</v>
       </c>
       <c r="AO10" t="n">
         <v>0.9449058044693869</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.9373550248580094</v>
+        <v>0.9449174632871642</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.007550779611377512</v>
+        <v>1.165881777731581e-05</v>
       </c>
       <c r="AR10" t="n">
         <v>0.9144490559895834</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.904052734375</v>
+        <v>0.8966456821986607</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.01039632161458337</v>
+        <v>-0.01780337379092267</v>
       </c>
       <c r="AU10" t="n">
         <v>1.0168701171875</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.9623453776041667</v>
+        <v>0.9611672794117647</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.05452473958333337</v>
+        <v>-0.05570283777573537</v>
       </c>
       <c r="AX10" t="n">
         <v>0.0131511338444699</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.01404737125929091</v>
+        <v>0.0104005072678456</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0008962374148210085</v>
+        <v>-0.002750626576624299</v>
       </c>
       <c r="BA10" t="n">
         <v>0.09823391713523243</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.06888935201145452</v>
+        <v>0.1128384124486645</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.02934456512377791</v>
+        <v>0.01460449531343205</v>
       </c>
       <c r="BD10" t="n">
         <v>2.955067601369981</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.672649135685351</v>
+        <v>2.936321943674163</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.2824184656846298</v>
+        <v>-0.01874565769581826</v>
       </c>
       <c r="BG10" t="n">
         <v>2.761077880859375</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.553989186006434</v>
+        <v>2.709096272786458</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0.2070886948529411</v>
+        <v>-0.05198160807291652</v>
       </c>
       <c r="BJ10" t="n">
         <v>3.1881103515625</v>
       </c>
       <c r="BK10" t="n">
-        <v>2.763926188151042</v>
+        <v>3.147201538085938</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.4241841634114585</v>
+        <v>-0.0409088134765625</v>
       </c>
       <c r="BM10" t="n">
         <v>0.0259876290957315</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.02684650251973113</v>
+        <v>0.02499662217914249</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0008588734239996232</v>
+        <v>-0.0009910069165890156</v>
       </c>
       <c r="BP10" t="n">
         <v>0.3169974555225946</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.2161794166251224</v>
+        <v>1.283014044047492</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0.1008180388974722</v>
+        <v>0.9660165885248979</v>
       </c>
       <c r="BS10" t="n">
         <v>0.9077637041386086</v>
       </c>
       <c r="BT10" t="n">
-        <v>1.075494071774744</v>
+        <v>0.8230860398175521</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.1677303676361355</v>
+        <v>-0.0846776643210565</v>
       </c>
       <c r="BV10" t="n">
         <v>-1.792831420898438</v>
       </c>
       <c r="BW10" t="n">
-        <v>-0.629119873046875</v>
+        <v>-3.715972900390626</v>
       </c>
       <c r="BX10" t="n">
-        <v>1.163711547851562</v>
+        <v>-1.923141479492188</v>
       </c>
       <c r="BY10" t="n">
         <v>3.013153076171875</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.339141845703125</v>
+        <v>2.31781005859375</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.32598876953125</v>
+        <v>-0.695343017578125</v>
       </c>
       <c r="CB10" t="n">
         <v>0.02468975552314372</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.02163579903934808</v>
+        <v>0.0230969857585273</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0.003053956483795636</v>
+        <v>-0.001592769764616416</v>
       </c>
       <c r="CE10" t="n">
         <v>7.92764406735245</v>
       </c>
       <c r="CF10" t="n">
-        <v>8.044096422125818</v>
+        <v>11.30509411730393</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.1164523547733687</v>
+        <v>3.377450049951477</v>
       </c>
       <c r="CH10" t="n">
         <v>-0.2150055519977019</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.24454170783465</v>
+        <v>-0.2927387202857455</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.4595472598323519</v>
+        <v>-0.07773316828804355</v>
       </c>
       <c r="CK10" t="n">
         <v>-0.3090413411458333</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.1451380112591912</v>
+        <v>-0.3748372395833333</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.4541793524050245</v>
+        <v>-0.0657958984375</v>
       </c>
       <c r="CN10" t="n">
         <v>-0.0400543212890625</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.3893280029296875</v>
+        <v>-0.139068603515625</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.42938232421875</v>
+        <v>-0.0990142822265625</v>
       </c>
       <c r="CQ10" t="n">
         <v>0.2436406447870407</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1082716492386266</v>
+        <v>0.1143943829356537</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0.1353689955484141</v>
+        <v>-0.129246261851387</v>
       </c>
       <c r="CT10" t="n">
         <v>0.3406873217410825</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.1560612717078025</v>
+        <v>0.2777510392545559</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0.18462605003328</v>
+        <v>-0.06293628248652661</v>
       </c>
       <c r="EP10" t="inlineStr">
         <is>
-          <t>T8_min_C, gyroy_min</t>
+          <t>T8_mean_C, T8_min_C, T8_max_C, gyroy_min, gyroy_std_max</t>
         </is>
       </c>
     </row>
@@ -6905,298 +6906,303 @@
         <v>11.55586104010554</v>
       </c>
       <c r="C11" t="n">
-        <v>12.50712012238481</v>
+        <v>11.63740786183397</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9512590822792628</v>
+        <v>0.08154682172842698</v>
       </c>
       <c r="E11" t="n">
         <v>9.362656759147562</v>
       </c>
       <c r="F11" t="n">
-        <v>9.441918829415249</v>
+        <v>9.225856060297495</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07926207026768672</v>
+        <v>-0.1368006988500667</v>
       </c>
       <c r="H11" t="n">
         <v>13.74257026291506</v>
       </c>
       <c r="I11" t="n">
-        <v>14.43168349152044</v>
+        <v>14.80063692523175</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6891132286053736</v>
+        <v>1.058066662316682</v>
       </c>
       <c r="K11" t="n">
         <v>-0.03682929345571343</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.02977655516283909</v>
+        <v>-0.03608686268280344</v>
       </c>
       <c r="M11" t="n">
-        <v>0.007052738292874346</v>
+        <v>0.0007424307729099952</v>
       </c>
       <c r="N11" t="n">
         <v>-0.07115827287946429</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.06823294503348214</v>
+        <v>-0.06965419224330358</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002925327845982151</v>
+        <v>0.001504080636160712</v>
       </c>
       <c r="Q11" t="n">
         <v>0.0001749674479166667</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03244916130514706</v>
+        <v>-0.003282819475446429</v>
       </c>
       <c r="S11" t="n">
-        <v>0.03227419385723039</v>
+        <v>-0.003457786923363095</v>
       </c>
       <c r="T11" t="n">
         <v>0.01614998022265537</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01573426495893889</v>
+        <v>0.01539206552079316</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0004157152637164797</v>
+        <v>-0.0007579147018622161</v>
       </c>
       <c r="W11" t="n">
         <v>0.06625656600505225</v>
       </c>
       <c r="X11" t="n">
-        <v>0.08019304153952124</v>
+        <v>0.06133148428201416</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01393647553446899</v>
+        <v>-0.004925081723038092</v>
       </c>
       <c r="Z11" t="n">
         <v>0.009701185604940264</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.0006087504722513255</v>
+        <v>0.009668047954352079</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.01030993607719159</v>
+        <v>-3.313765058818481e-05</v>
       </c>
       <c r="AC11" t="n">
         <v>0.001114908854166667</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.01377599379595588</v>
+        <v>0.000373391544117647</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01489090265012255</v>
+        <v>-0.0007415173100490196</v>
       </c>
       <c r="AF11" t="n">
         <v>0.02183024088541667</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.014801025390625</v>
+        <v>0.019866943359375</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.007029215494791668</v>
+        <v>-0.001963297526041668</v>
       </c>
       <c r="AI11" t="n">
         <v>0.005421388042918182</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.00401853368766074</v>
+        <v>0.00503890512803752</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.001402854355257442</v>
+        <v>-0.0003824829148806625</v>
       </c>
       <c r="AL11" t="n">
         <v>0.02115496477423926</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.04986425542228088</v>
+        <v>0.02584038819981902</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.02870929064804162</v>
+        <v>0.004685423425579757</v>
       </c>
       <c r="AO11" t="n">
         <v>0.9451382097658778</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.9389342273817892</v>
+        <v>0.9452982028017622</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.006203982384088591</v>
+        <v>0.0001599930358844315</v>
       </c>
       <c r="AR11" t="n">
         <v>0.8904581705729167</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.8902839211856618</v>
+        <v>0.8891398111979166</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0.0001742493872548545</v>
+        <v>-0.001318359375000022</v>
       </c>
       <c r="AU11" t="n">
         <v>0.9965250651041667</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.98162841796875</v>
+        <v>0.9848991842830882</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.01489664713541672</v>
+        <v>-0.01162588082107852</v>
       </c>
       <c r="AX11" t="n">
         <v>0.01636039057408493</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.01817118277416295</v>
+        <v>0.01617091657511461</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.001810792200078022</v>
+        <v>-0.0001894739989703222</v>
       </c>
       <c r="BA11" t="n">
         <v>0.1228251283583157</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.1421947711768318</v>
+        <v>0.117455359260071</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.01936964281851608</v>
+        <v>-0.00536976909824477</v>
       </c>
       <c r="BD11" t="n">
         <v>2.921606427896666</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.612991673032757</v>
+        <v>2.916496130281466</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.3086147548639091</v>
+        <v>-0.005110297615199766</v>
       </c>
       <c r="BG11" t="n">
         <v>2.755452473958333</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.4609375</v>
+        <v>2.799530029296875</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0.2945149739583335</v>
+        <v>0.04407755533854152</v>
       </c>
       <c r="BJ11" t="n">
         <v>3.163686116536458</v>
       </c>
       <c r="BK11" t="n">
-        <v>2.750966389973958</v>
+        <v>3.047898236443014</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.4127197265625</v>
+        <v>-0.115787880093444</v>
       </c>
       <c r="BM11" t="n">
         <v>0.02821615450289448</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.02730893706614661</v>
+        <v>0.02737577721373148</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0.0009072174367478654</v>
+        <v>-0.000840377289162992</v>
       </c>
       <c r="BP11" t="n">
         <v>0.2977753911025356</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.2487728264852526</v>
+        <v>0.2938549095406255</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0.04900256461728295</v>
+        <v>-0.00392048156191005</v>
       </c>
       <c r="BS11" t="n">
         <v>0.8008448931734464</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.8515668553982848</v>
+        <v>0.7618490899545683</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.05072196222483838</v>
+        <v>-0.03899580321887808</v>
       </c>
       <c r="BV11" t="n">
         <v>-1.092147827148437</v>
       </c>
       <c r="BW11" t="n">
-        <v>-1.415315515854779</v>
+        <v>-1.1279296875</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.3231676887063422</v>
+        <v>-0.03578186035156272</v>
       </c>
       <c r="BY11" t="n">
         <v>3.008346557617188</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.126907348632812</v>
+        <v>2.657470703125</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.118560791015625</v>
+        <v>-0.3508758544921875</v>
       </c>
       <c r="CB11" t="n">
         <v>0.02675604522289794</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.02268911010018926</v>
+        <v>0.02600988241051815</v>
       </c>
       <c r="CD11" t="n">
-        <v>-0.004066935122708674</v>
+        <v>-0.00074616281237979</v>
       </c>
       <c r="CE11" t="n">
         <v>9.231255543719943</v>
       </c>
       <c r="CF11" t="n">
-        <v>8.126761773213371</v>
+        <v>6.894075288289839</v>
       </c>
       <c r="CG11" t="n">
-        <v>-1.104493770506572</v>
+        <v>-2.337180255430104</v>
       </c>
       <c r="CH11" t="n">
         <v>-0.1938063072817292</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.2280058320190448</v>
+        <v>-0.2517122777997942</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.4218121393007739</v>
+        <v>-0.05790597051806504</v>
       </c>
       <c r="CK11" t="n">
         <v>-0.447113037109375</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0592803955078125</v>
+        <v>-0.447540283203125</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.5063934326171875</v>
+        <v>-0.00042724609375</v>
       </c>
       <c r="CN11" t="n">
         <v>0.02336502075195312</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.36102294921875</v>
+        <v>-0.1233673095703125</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.3376579284667969</v>
+        <v>-0.1467323303222656</v>
       </c>
       <c r="CQ11" t="n">
         <v>0.09084957679089894</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.08518383189197129</v>
+        <v>0.08178230283213114</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0.005665744898927655</v>
+        <v>-0.009067273958767802</v>
       </c>
       <c r="CT11" t="n">
         <v>0.2566262532675626</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.1532984148979251</v>
+        <v>0.2749166006745193</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0.1033278383696375</v>
+        <v>0.01829034740695668</v>
+      </c>
+      <c r="EP11" t="inlineStr">
+        <is>
+          <t>T8_max_C</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -7209,302 +7215,302 @@
         <v>12.50863754249298</v>
       </c>
       <c r="C12" t="n">
-        <v>12.07775679259262</v>
+        <v>12.23905339055616</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4308807499003606</v>
+        <v>-0.2695841519368258</v>
       </c>
       <c r="E12" t="n">
         <v>9.546358296789753</v>
       </c>
       <c r="F12" t="n">
-        <v>9.624668010134966</v>
+        <v>9.546776422750712</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07830971334521308</v>
+        <v>0.0004181259609588039</v>
       </c>
       <c r="H12" t="n">
         <v>14.18969982282669</v>
       </c>
       <c r="I12" t="n">
-        <v>14.26501666004845</v>
+        <v>14.33795599984073</v>
       </c>
       <c r="J12" t="n">
-        <v>0.07531683722175941</v>
+        <v>0.1482561770140389</v>
       </c>
       <c r="K12" t="n">
         <v>-0.03557111452905368</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.03369038359462355</v>
+        <v>-0.03376243815442437</v>
       </c>
       <c r="M12" t="n">
-        <v>0.001880730934430135</v>
+        <v>0.001808676374629309</v>
       </c>
       <c r="N12" t="n">
         <v>-0.1288533528645833</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.09140886579241071</v>
+        <v>-0.1254141671316964</v>
       </c>
       <c r="P12" t="n">
-        <v>0.03744448707217261</v>
+        <v>0.003439185732886901</v>
       </c>
       <c r="Q12" t="n">
         <v>0.04752349853515625</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04076712472098214</v>
+        <v>0.06634957449776786</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.006756373814174106</v>
+        <v>0.01882607596261161</v>
       </c>
       <c r="T12" t="n">
         <v>0.02942570715252378</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02147835697794105</v>
+        <v>0.02052112269176707</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.007947350174582729</v>
+        <v>-0.008904584460756711</v>
       </c>
       <c r="W12" t="n">
         <v>0.0926843185508394</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1229191691895879</v>
+        <v>0.1142505838371591</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03023485063874853</v>
+        <v>0.02156626528631968</v>
       </c>
       <c r="Z12" t="n">
         <v>0.007016526594125165</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.001109303929724056</v>
+        <v>0.007552387089385211</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.008125830523849221</v>
+        <v>0.0005358604952600456</v>
       </c>
       <c r="AC12" t="n">
         <v>-0.00356292724609375</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.016815185546875</v>
+        <v>-0.004891531808035714</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.01325225830078125</v>
+        <v>-0.001328604561941964</v>
       </c>
       <c r="AF12" t="n">
         <v>0.01831868489583333</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.007533482142857143</v>
+        <v>0.01728372012867647</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.01078520275297619</v>
+        <v>-0.001034964767156862</v>
       </c>
       <c r="AI12" t="n">
         <v>0.0094188216575278</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.008205075799712492</v>
+        <v>0.006572661457605837</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.001213745857815309</v>
+        <v>-0.002846160199921964</v>
       </c>
       <c r="AL12" t="n">
         <v>0.03365795460488248</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.04803308830858125</v>
+        <v>0.03058507120382814</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01437513370369876</v>
+        <v>-0.003072883401054338</v>
       </c>
       <c r="AO12" t="n">
         <v>0.9456508518646121</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.9398903078686907</v>
+        <v>0.9469110644201379</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.005760543995921408</v>
+        <v>0.001260212555525886</v>
       </c>
       <c r="AR12" t="n">
         <v>0.9043131510416667</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.9081508091517857</v>
+        <v>0.9204842703683036</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.003837658110119047</v>
+        <v>0.01617111932663695</v>
       </c>
       <c r="AU12" t="n">
         <v>0.9903279622395833</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.991845703125</v>
+        <v>0.9713963099888393</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.001517740885416674</v>
+        <v>-0.018931652250744</v>
       </c>
       <c r="AX12" t="n">
         <v>0.03891405582841959</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.03112179268867234</v>
+        <v>0.02606001166741466</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.007792263139747249</v>
+        <v>-0.01285404416100492</v>
       </c>
       <c r="BA12" t="n">
         <v>0.1508458719054339</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.1398287540241667</v>
+        <v>0.09557272091341663</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.01101711788126722</v>
+        <v>-0.05527315099201731</v>
       </c>
       <c r="BD12" t="n">
         <v>2.899106725916132</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.610195286893407</v>
+        <v>2.875423427184394</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.288911439022725</v>
+        <v>-0.02368329873173813</v>
       </c>
       <c r="BG12" t="n">
         <v>2.647786458333333</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.371082305908203</v>
+        <v>2.583770751953125</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.2767041524251304</v>
+        <v>-0.06401570638020848</v>
       </c>
       <c r="BJ12" t="n">
         <v>3.207550048828125</v>
       </c>
       <c r="BK12" t="n">
-        <v>2.762680053710938</v>
+        <v>3.205350988051471</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0.4448699951171875</v>
+        <v>-0.002199060776654438</v>
       </c>
       <c r="BM12" t="n">
         <v>0.05862217100905814</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0506404651229586</v>
+        <v>0.04691658931751597</v>
       </c>
       <c r="BO12" t="n">
-        <v>-0.007981705886099547</v>
+        <v>-0.01170558169154218</v>
       </c>
       <c r="BP12" t="n">
         <v>0.55927027735668</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.3104693186633718</v>
+        <v>0.5980094799279858</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0.2488009586933082</v>
+        <v>0.03873920257130581</v>
       </c>
       <c r="BS12" t="n">
         <v>0.7264109474044662</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.7994880845133382</v>
+        <v>0.6624220518223408</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.07307713710887198</v>
+        <v>-0.06398889558212539</v>
       </c>
       <c r="BV12" t="n">
         <v>-2.088699340820312</v>
       </c>
       <c r="BW12" t="n">
-        <v>-2.624893188476562</v>
+        <v>-4.097824096679688</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.53619384765625</v>
+        <v>-2.009124755859375</v>
       </c>
       <c r="BY12" t="n">
         <v>4.131184895833333</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.222636503331802</v>
+        <v>5.209732055664062</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.09145160749846859</v>
+        <v>1.078547159830729</v>
       </c>
       <c r="CB12" t="n">
         <v>0.4065220235739825</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.2002844024758982</v>
+        <v>0.1929320377927696</v>
       </c>
       <c r="CD12" t="n">
-        <v>-0.2062376210980843</v>
+        <v>-0.2135899857812129</v>
       </c>
       <c r="CE12" t="n">
         <v>9.099894052670733</v>
       </c>
       <c r="CF12" t="n">
-        <v>9.505600627972697</v>
+        <v>6.043672457561111</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.4057065753019646</v>
+        <v>-3.056221595109622</v>
       </c>
       <c r="CH12" t="n">
         <v>-0.2032250713657688</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.2093294153386905</v>
+        <v>-0.2778321772043945</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.4125544867044594</v>
+        <v>-0.07460710583862562</v>
       </c>
       <c r="CK12" t="n">
         <v>-0.4378604888916016</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.09432279146634616</v>
+        <v>-0.5721956140854779</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.5321832803579477</v>
+        <v>-0.1343351251938764</v>
       </c>
       <c r="CN12" t="n">
         <v>0.0229644775390625</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.340728759765625</v>
+        <v>0.0101470947265625</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.3177642822265625</v>
+        <v>-0.0128173828125</v>
       </c>
       <c r="CQ12" t="n">
         <v>0.0550323135806574</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.054845163141433</v>
+        <v>0.04141827851178537</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.0001871504392243969</v>
+        <v>-0.01361403506887203</v>
       </c>
       <c r="CT12" t="n">
         <v>0.6831852372761843</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.2405372425282533</v>
+        <v>0.3317200269322847</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0.442647994747931</v>
+        <v>-0.3514652103438996</v>
       </c>
       <c r="EP12" t="inlineStr">
         <is>
-          <t>gyroy_std_median</t>
+          <t>accz_std_max, gyroy_min, gyroy_std_median</t>
         </is>
       </c>
     </row>
@@ -7518,302 +7524,302 @@
         <v>14.49742265559647</v>
       </c>
       <c r="C13" t="n">
-        <v>14.43367521011945</v>
+        <v>14.57989615543127</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06374744547701283</v>
+        <v>0.0824734998348049</v>
       </c>
       <c r="E13" t="n">
         <v>14.20034571757199</v>
       </c>
       <c r="F13" t="n">
-        <v>14.25749227231675</v>
+        <v>14.33496130661866</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05714655474475983</v>
+        <v>0.1346155890466729</v>
       </c>
       <c r="H13" t="n">
         <v>14.82870623734175</v>
       </c>
       <c r="I13" t="n">
-        <v>14.7544988175028</v>
+        <v>14.90092496154234</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0742074198389453</v>
+        <v>0.07221872420059228</v>
       </c>
       <c r="K13" t="n">
         <v>-0.4324332827613467</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4306960997649636</v>
+        <v>-0.4658273702580579</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8631293825263103</v>
+        <v>-0.03339408749671119</v>
       </c>
       <c r="N13" t="n">
         <v>-1.018379720052083</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.08220563616071429</v>
+        <v>-1.031725202287946</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9361740838913691</v>
+        <v>-0.01334548223586296</v>
       </c>
       <c r="Q13" t="n">
         <v>0.2397242954799107</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9590950012207031</v>
+        <v>0.2232235179227941</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7193707057407924</v>
+        <v>-0.0165007775571166</v>
       </c>
       <c r="T13" t="n">
         <v>0.07617369600752434</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1052209363566788</v>
+        <v>0.07255389870644162</v>
       </c>
       <c r="V13" t="n">
-        <v>0.02904724034915442</v>
+        <v>-0.003619797301082722</v>
       </c>
       <c r="W13" t="n">
         <v>0.1098489657970348</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1575590771362023</v>
+        <v>0.1526940942752432</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.04771011133916742</v>
+        <v>0.04284512847820834</v>
       </c>
       <c r="Z13" t="n">
         <v>0.01253711155482701</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.004369085139689891</v>
+        <v>0.01220423984913182</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.008168026415137117</v>
+        <v>-0.00033287170569519</v>
       </c>
       <c r="AC13" t="n">
         <v>0.001408168247767857</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.03071376255580357</v>
+        <v>0.001582554408482143</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.03212193080357143</v>
+        <v>0.0001743861607142855</v>
       </c>
       <c r="AF13" t="n">
         <v>0.02457275390625</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.03753226143973214</v>
+        <v>0.03030831473214286</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01295950753348214</v>
+        <v>0.005735560825892855</v>
       </c>
       <c r="AI13" t="n">
         <v>0.01851910029483202</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.03900766086476064</v>
+        <v>0.01499670809498644</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.02048856056992862</v>
+        <v>-0.00352239219984558</v>
       </c>
       <c r="AL13" t="n">
         <v>0.04627222640629541</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.1482201269330228</v>
+        <v>0.06377804602719717</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.1019479005267274</v>
+        <v>0.01750581962090176</v>
       </c>
       <c r="AO13" t="n">
         <v>-0.09403174264090403</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.303638758068582</v>
+        <v>-0.05903519833104693</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.209607015427678</v>
+        <v>0.0349965443098571</v>
       </c>
       <c r="AR13" t="n">
         <v>-1.058197021484375</v>
       </c>
       <c r="AS13" t="n">
-        <v>-1.035204206194196</v>
+        <v>-1.086225237165179</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0229928152901786</v>
+        <v>-0.0280282156808036</v>
       </c>
       <c r="AU13" t="n">
         <v>0.96290283203125</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9316580636160714</v>
+        <v>0.9505833217075893</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.03124476841517865</v>
+        <v>-0.01231951032366074</v>
       </c>
       <c r="AX13" t="n">
         <v>0.07077589391420286</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.09701509007116607</v>
+        <v>0.06431582511793874</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02623919615696321</v>
+        <v>-0.006460068796264123</v>
       </c>
       <c r="BA13" t="n">
         <v>0.1223441067077776</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.4165853543073419</v>
+        <v>0.1292875369181282</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.2942412475995643</v>
+        <v>0.006943430210350585</v>
       </c>
       <c r="BD13" t="n">
         <v>2.855185508728027</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.736930848318707</v>
+        <v>2.856608170390964</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.1182546604093204</v>
+        <v>0.001422661662937141</v>
       </c>
       <c r="BG13" t="n">
         <v>2.790842692057292</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.557643010066106</v>
+        <v>2.76641845703125</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0.2331996819911857</v>
+        <v>-0.02442423502604152</v>
       </c>
       <c r="BJ13" t="n">
         <v>2.90399169921875</v>
       </c>
       <c r="BK13" t="n">
-        <v>2.827634811401367</v>
+        <v>2.907598158892463</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0.07635688781738281</v>
+        <v>0.003606459673713314</v>
       </c>
       <c r="BM13" t="n">
         <v>0.04390776704750006</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.04318624485842018</v>
+        <v>0.03831725628005993</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0.000721522189079879</v>
+        <v>-0.005590510767440125</v>
       </c>
       <c r="BP13" t="n">
         <v>0.2881960173604484</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.4028865948428108</v>
+        <v>0.2485838198627757</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.1146905774823624</v>
+        <v>-0.03961219749767264</v>
       </c>
       <c r="BS13" t="n">
         <v>-8.790884335835775</v>
       </c>
       <c r="BT13" t="n">
-        <v>11.19820891332842</v>
+        <v>-8.225628560844411</v>
       </c>
       <c r="BU13" t="n">
-        <v>19.98909324916419</v>
+        <v>0.565255774991364</v>
       </c>
       <c r="BV13" t="n">
         <v>-14.37241617838542</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.8444118499755859</v>
+        <v>-13.56952442842371</v>
       </c>
       <c r="BX13" t="n">
-        <v>15.216828028361</v>
+        <v>0.8028917499617023</v>
       </c>
       <c r="BY13" t="n">
         <v>10.39382934570312</v>
       </c>
       <c r="BZ13" t="n">
-        <v>17.37663269042969</v>
+        <v>22.87155151367188</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.982803344726562</v>
+        <v>12.47772216796875</v>
       </c>
       <c r="CB13" t="n">
         <v>0.7414155434648886</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5195591635692463</v>
+        <v>0.7595986873470373</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.2218563798956423</v>
+        <v>0.0181831438821487</v>
       </c>
       <c r="CE13" t="n">
         <v>26.59142000089429</v>
       </c>
       <c r="CF13" t="n">
-        <v>7.484639730278748</v>
+        <v>14.27047510308392</v>
       </c>
       <c r="CG13" t="n">
-        <v>-19.10678027061554</v>
+        <v>-12.32094489781037</v>
       </c>
       <c r="CH13" t="n">
         <v>-0.2814995447794596</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.256102310610273</v>
+        <v>-0.3549864634193257</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.5376018553897326</v>
+        <v>-0.07348691863986606</v>
       </c>
       <c r="CK13" t="n">
         <v>-0.3972676595052083</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.1216227213541667</v>
+        <v>-0.4651641845703125</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.518890380859375</v>
+        <v>-0.06789652506510419</v>
       </c>
       <c r="CN13" t="n">
         <v>-0.1550191243489583</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.3483312270220588</v>
+        <v>-0.2579498291015625</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.5033503513710171</v>
+        <v>-0.1029307047526042</v>
       </c>
       <c r="CQ13" t="n">
         <v>0.03228909205465462</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.03152779941720309</v>
+        <v>0.03078279425360615</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0.0007612926374515327</v>
+        <v>-0.001506297801048474</v>
       </c>
       <c r="CT13" t="n">
         <v>0.1193437356268778</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.1334836719062131</v>
+        <v>0.09702610779281909</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.01413993627933534</v>
+        <v>-0.02231762783405868</v>
       </c>
       <c r="EP13" t="inlineStr">
         <is>
-          <t>accz_mean, accz_std_max, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>gyroy_max, gyroy_std_max</t>
         </is>
       </c>
     </row>
@@ -7827,302 +7833,302 @@
         <v>15.00867485258736</v>
       </c>
       <c r="C14" t="n">
-        <v>1.062123464972064</v>
+        <v>15.0636389720506</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.9465513876153</v>
+        <v>0.05496411946323576</v>
       </c>
       <c r="E14" t="n">
         <v>14.84843215741797</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>14.91090609116976</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.84843215741797</v>
+        <v>0.06247393375178234</v>
       </c>
       <c r="H14" t="n">
         <v>15.2994612462175</v>
       </c>
       <c r="I14" t="n">
-        <v>14.74957189784413</v>
+        <v>15.38495564031458</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5498893483733678</v>
+        <v>0.0854943940970756</v>
       </c>
       <c r="K14" t="n">
         <v>-0.01431806049649678</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02352225683442448</v>
+        <v>-0.007047379311259319</v>
       </c>
       <c r="M14" t="n">
-        <v>0.03784031733092125</v>
+        <v>0.007270681185237458</v>
       </c>
       <c r="N14" t="n">
         <v>-0.1965738932291667</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1897103445870536</v>
+        <v>-0.1819223257211539</v>
       </c>
       <c r="P14" t="n">
-        <v>0.006863548642113082</v>
+        <v>0.0146515675080128</v>
       </c>
       <c r="Q14" t="n">
         <v>0.1647420247395833</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2794886997767857</v>
+        <v>0.1435834099264706</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1147466750372024</v>
+        <v>-0.02115861481311274</v>
       </c>
       <c r="T14" t="n">
         <v>0.203294208885351</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3150056625725148</v>
+        <v>0.2077459042838134</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1117114536871638</v>
+        <v>0.00445169539846238</v>
       </c>
       <c r="W14" t="n">
         <v>0.4812295450520206</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5820993324314896</v>
+        <v>0.533165550005871</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1008697873794689</v>
+        <v>0.05193600495385031</v>
       </c>
       <c r="Z14" t="n">
         <v>0.01315987602112785</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01125218250736793</v>
+        <v>0.01149446762612753</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.001907693513759924</v>
+        <v>-0.001665408395000319</v>
       </c>
       <c r="AC14" t="n">
         <v>-0.1444539388020833</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.2064412434895833</v>
+        <v>-0.1208170572916667</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.06198730468750002</v>
+        <v>0.02363688151041665</v>
       </c>
       <c r="AF14" t="n">
         <v>0.1012776692708333</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.1648021024816176</v>
+        <v>0.11114501953125</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.06352443321078431</v>
+        <v>0.009867350260416671</v>
       </c>
       <c r="AI14" t="n">
         <v>0.1175548099216634</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.163334172971003</v>
+        <v>0.1474957808114054</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.04577936304933963</v>
+        <v>0.02994097088974199</v>
       </c>
       <c r="AL14" t="n">
         <v>0.2886369942310333</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4538691620719058</v>
+        <v>0.3671750302234273</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.1652321678408724</v>
+        <v>0.07853803599239401</v>
       </c>
       <c r="AO14" t="n">
         <v>-0.7164576999724858</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.6569878542049332</v>
+        <v>-0.66364443466999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.05946984576755254</v>
+        <v>0.05281326530249575</v>
       </c>
       <c r="AR14" t="n">
         <v>-1.107861328125</v>
       </c>
       <c r="AS14" t="n">
-        <v>-1.110547746930804</v>
+        <v>-1.106029510498047</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0.002686418805803559</v>
+        <v>0.001831817626953169</v>
       </c>
       <c r="AU14" t="n">
         <v>0.05612386067708333</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.18402099609375</v>
+        <v>0.02498779296875</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1278971354166667</v>
+        <v>-0.03113606770833333</v>
       </c>
       <c r="AX14" t="n">
         <v>0.4385086273258404</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.5080532246784194</v>
+        <v>0.4518777743675808</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.06954459735257901</v>
+        <v>0.01336914704174036</v>
       </c>
       <c r="BA14" t="n">
         <v>0.784037328503847</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.8769106469510897</v>
+        <v>0.6854932875816518</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.09287331844724267</v>
+        <v>-0.09854404092219515</v>
       </c>
       <c r="BD14" t="n">
         <v>2.842143469386631</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.65692098108352</v>
+        <v>2.906491349633499</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.1852224883031104</v>
+        <v>0.06434788024686799</v>
       </c>
       <c r="BG14" t="n">
         <v>2.094004313151042</v>
       </c>
       <c r="BH14" t="n">
-        <v>1.483612060546875</v>
+        <v>2.207794189453125</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0.6103922526041665</v>
+        <v>0.1137898763020835</v>
       </c>
       <c r="BJ14" t="n">
         <v>3.177144368489583</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.944661458333333</v>
+        <v>3.745381673177083</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.76751708984375</v>
+        <v>0.5682373046875</v>
       </c>
       <c r="BM14" t="n">
         <v>0.2593075201789777</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.5148270463204843</v>
+        <v>0.3137792939613483</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.2555195261415066</v>
+        <v>0.05447177378237067</v>
       </c>
       <c r="BP14" t="n">
         <v>2.16385111524374</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9.771337498075601</v>
+        <v>3.607127781504353</v>
       </c>
       <c r="BR14" t="n">
-        <v>7.607486382831861</v>
+        <v>1.443276666260612</v>
       </c>
       <c r="BS14" t="n">
         <v>0.7197978496551514</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.6426614839986319</v>
+        <v>0.6576498910069476</v>
       </c>
       <c r="BU14" t="n">
-        <v>-0.07713636565651949</v>
+        <v>-0.06214795864820377</v>
       </c>
       <c r="BV14" t="n">
         <v>-5.347412109375</v>
       </c>
       <c r="BW14" t="n">
-        <v>-1.619796752929688</v>
+        <v>-12.00721740722656</v>
       </c>
       <c r="BX14" t="n">
-        <v>3.727615356445312</v>
+        <v>-6.659805297851562</v>
       </c>
       <c r="BY14" t="n">
         <v>4.432749430338542</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.855743408203125</v>
+        <v>4.295425415039062</v>
       </c>
       <c r="CA14" t="n">
-        <v>-2.577006022135417</v>
+        <v>-0.1373240152994795</v>
       </c>
       <c r="CB14" t="n">
         <v>2.075586046789703</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.582785215130517</v>
+        <v>2.348050099042565</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0.4928008316591859</v>
+        <v>0.2724640522528614</v>
       </c>
       <c r="CE14" t="n">
         <v>22.5282095683739</v>
       </c>
       <c r="CF14" t="n">
-        <v>6.10520854242738</v>
+        <v>16.36214649476295</v>
       </c>
       <c r="CG14" t="n">
-        <v>-16.42300102594652</v>
+        <v>-6.16606307361095</v>
       </c>
       <c r="CH14" t="n">
         <v>-0.3245222436057196</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.1505842247220246</v>
+        <v>-0.409525631455109</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.4751064683277442</v>
+        <v>-0.08500338784938932</v>
       </c>
       <c r="CK14" t="n">
         <v>-0.411224365234375</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0.133087158203125</v>
+        <v>-0.6723785400390625</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.27813720703125</v>
+        <v>-0.2611541748046875</v>
       </c>
       <c r="CN14" t="n">
         <v>-0.15850830078125</v>
       </c>
       <c r="CO14" t="n">
-        <v>2.234319051106771</v>
+        <v>-0.10467529296875</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.392827351888021</v>
+        <v>0.0538330078125</v>
       </c>
       <c r="CQ14" t="n">
         <v>0.05188680804443932</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.06465956043617892</v>
+        <v>0.06001466780091593</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0127727523917396</v>
+        <v>0.008127859756476612</v>
       </c>
       <c r="CT14" t="n">
         <v>0.2481847208578424</v>
       </c>
       <c r="CU14" t="n">
-        <v>8.485398067312611</v>
+        <v>0.9006105452290204</v>
       </c>
       <c r="CV14" t="n">
-        <v>8.237213346454768</v>
+        <v>0.652425824371178</v>
       </c>
       <c r="EP14" t="inlineStr">
         <is>
-          <t>T8_mean_C, T8_min_C, accz_max, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>gyroy_min</t>
         </is>
       </c>
     </row>
@@ -8136,302 +8142,302 @@
         <v>15.4287119505177</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>15.46375402150244</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.4287119505177</v>
+        <v>0.03504207098473699</v>
       </c>
       <c r="E15" t="n">
         <v>15.25266533836246</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>15.34852062091185</v>
       </c>
       <c r="G15" t="n">
-        <v>-15.25266533836246</v>
+        <v>0.0958552825493868</v>
       </c>
       <c r="H15" t="n">
         <v>15.53041402035055</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>15.60608951446174</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.53041402035055</v>
+        <v>0.07567549411118613</v>
       </c>
       <c r="K15" t="n">
         <v>-0.1729883157639276</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2042745748201625</v>
+        <v>-0.1155774419753253</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3772628905840901</v>
+        <v>0.05741087378860237</v>
       </c>
       <c r="N15" t="n">
         <v>-1.010013834635417</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.07151576450892858</v>
+        <v>-0.9929924011230469</v>
       </c>
       <c r="P15" t="n">
-        <v>0.938498070126488</v>
+        <v>0.01702143351236973</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.0024658203125</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8729291643415179</v>
+        <v>0.002702985491071429</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8753949846540179</v>
+        <v>0.005168805803571428</v>
       </c>
       <c r="T15" t="n">
         <v>0.06559392053429372</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0957755062072706</v>
+        <v>0.06841448798129092</v>
       </c>
       <c r="V15" t="n">
-        <v>0.03018158567297688</v>
+        <v>0.002820567446997199</v>
       </c>
       <c r="W15" t="n">
         <v>0.2615593490545352</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2024618852425928</v>
+        <v>0.1911926275151775</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.05909746381194242</v>
+        <v>-0.07036672153935769</v>
       </c>
       <c r="Z15" t="n">
         <v>0.005718905131022136</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.00513986722618735</v>
+        <v>0.009160398351235027</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.0005790379048347854</v>
+        <v>0.003441493220212892</v>
       </c>
       <c r="AC15" t="n">
         <v>-0.01410293579101562</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.02025059291294643</v>
+        <v>-0.01828874860491072</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.006147657121930803</v>
+        <v>-0.004185812813895091</v>
       </c>
       <c r="AF15" t="n">
         <v>0.02061767578125</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.04551914760044643</v>
+        <v>0.04203527113970588</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.02490147181919643</v>
+        <v>0.02141759535845588</v>
       </c>
       <c r="AI15" t="n">
         <v>0.02409795487220774</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02689893786533508</v>
+        <v>0.02800632761982278</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.002800982993127341</v>
+        <v>0.003908372747615046</v>
       </c>
       <c r="AL15" t="n">
         <v>0.05941739688803158</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.07521430945653504</v>
+        <v>0.09447299682686004</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.01579691256850346</v>
+        <v>0.03505559993882846</v>
       </c>
       <c r="AO15" t="n">
         <v>0.7162978799002511</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.2346245260799633</v>
+        <v>0.7929145063787234</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.4816733538202878</v>
+        <v>0.07661662647847234</v>
       </c>
       <c r="AR15" t="n">
         <v>-1.00379638671875</v>
       </c>
       <c r="AS15" t="n">
-        <v>-1.055472237723214</v>
+        <v>-0.9757908412388393</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0.05167585100446415</v>
+        <v>0.02800554547991074</v>
       </c>
       <c r="AU15" t="n">
         <v>0.9851161411830357</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.9691423688616071</v>
+        <v>0.9761891084558824</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.0159737723214286</v>
+        <v>-0.008927032727153339</v>
       </c>
       <c r="AX15" t="n">
         <v>0.1074189482035251</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.111948057390637</v>
+        <v>0.1100273888058151</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.004529109187111885</v>
+        <v>0.002608440602289971</v>
       </c>
       <c r="BA15" t="n">
         <v>0.2040557624812072</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.231237624666706</v>
+        <v>0.2341080891194139</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.02718186218549873</v>
+        <v>0.03005232663820667</v>
       </c>
       <c r="BD15" t="n">
         <v>2.958877245585124</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.466347301707548</v>
+        <v>2.748544992185106</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.4925299438775754</v>
+        <v>-0.2103322534000172</v>
       </c>
       <c r="BG15" t="n">
         <v>2.850657145182292</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.150115966796875</v>
+        <v>-0.1751708984374999</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0.7005411783854165</v>
+        <v>-3.025828043619792</v>
       </c>
       <c r="BJ15" t="n">
         <v>3.151224772135417</v>
       </c>
       <c r="BK15" t="n">
-        <v>2.626558191636029</v>
+        <v>3.082046508789062</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0.5246665804993871</v>
+        <v>-0.06917826334635402</v>
       </c>
       <c r="BM15" t="n">
         <v>0.0472483149533426</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.04946471092345637</v>
+        <v>0.0535845770688586</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.00221639597011377</v>
+        <v>0.006336262115516002</v>
       </c>
       <c r="BP15" t="n">
         <v>0.1709387096002497</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.1652052463274597</v>
+        <v>5.113438392693603</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0.005733463272790035</v>
+        <v>4.942499683093353</v>
       </c>
       <c r="BS15" t="n">
         <v>8.581115404764811</v>
       </c>
       <c r="BT15" t="n">
-        <v>-9.528309391994101</v>
+        <v>5.232033052631453</v>
       </c>
       <c r="BU15" t="n">
-        <v>-18.10942479675891</v>
+        <v>-3.349082352133357</v>
       </c>
       <c r="BV15" t="n">
         <v>0.14654541015625</v>
       </c>
       <c r="BW15" t="n">
-        <v>-35.63499450683594</v>
+        <v>-0.24139404296875</v>
       </c>
       <c r="BX15" t="n">
-        <v>-35.78153991699219</v>
+        <v>-0.387939453125</v>
       </c>
       <c r="BY15" t="n">
         <v>36.60744222005209</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.971206665039062</v>
+        <v>42.71659851074219</v>
       </c>
       <c r="CA15" t="n">
-        <v>-34.63623555501302</v>
+        <v>6.109156290690102</v>
       </c>
       <c r="CB15" t="n">
         <v>0.6301560131480808</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.22382115738351</v>
+        <v>0.04518949507882374</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.5936651442354297</v>
+        <v>-0.584966518069257</v>
       </c>
       <c r="CE15" t="n">
         <v>26.50985891421001</v>
       </c>
       <c r="CF15" t="n">
-        <v>9.901150423267513</v>
+        <v>25.68433487032907</v>
       </c>
       <c r="CG15" t="n">
-        <v>-16.6087084909425</v>
+        <v>-0.8255240438809395</v>
       </c>
       <c r="CH15" t="n">
         <v>-0.2586042722066244</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0006311080035041368</v>
+        <v>-0.3441208783318015</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.2592353802101285</v>
+        <v>-0.08551660612517714</v>
       </c>
       <c r="CK15" t="n">
         <v>-0.2935892740885417</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0.330047607421875</v>
+        <v>-0.3887939453125</v>
       </c>
       <c r="CM15" t="n">
-        <v>-0.03645833333333331</v>
+        <v>-0.09520467122395831</v>
       </c>
       <c r="CN15" t="n">
         <v>-0.1530253092447917</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.128173828125</v>
+        <v>-0.2184295654296875</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.2811991373697916</v>
+        <v>-0.06540425618489584</v>
       </c>
       <c r="CQ15" t="n">
         <v>0.04797070426271448</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.04265045357662846</v>
+        <v>0.0578195519518185</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0.00532025068608602</v>
+        <v>0.009848847689104018</v>
       </c>
       <c r="CT15" t="n">
         <v>0.1462930595588686</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.13944277976718</v>
+        <v>0.5609847574031893</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0.00685027979168859</v>
+        <v>0.4146916978443208</v>
       </c>
       <c r="EP15" t="inlineStr">
         <is>
-          <t>T8_mean_C, T8_min_C, T8_max_C, accz_mean, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_median, gyroy_std_max</t>
+          <t>gyroy_mean, gyroy_min, gyroy_std_median</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9032,7 @@
   <dimension ref="A1:AE29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -9038,7 +9044,7 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="38" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
@@ -9050,7 +9056,7 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="19" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="19" customWidth="1" min="28" max="28"/>
@@ -11025,7 +11031,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11034,47 +11040,47 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.23661221590909</v>
+        <v>10.3505859375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22.62479285037879</v>
+        <v>10.48610276442308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>21.84537760416667</v>
+        <v>10.09435096153846</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7794152462121211</v>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>#FFEB84</t>
+        <v>0.391751802884615</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>#63BE7B</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>T5 is warmest and T4 is coolest in this zone.</t>
+          <t>T3 is warmest and T2 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>22.12476325757576</v>
+        <v>10.09435096153846</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1118489583333364</v>
+        <v>-0.2562349759615401</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -11087,10 +11093,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>22.38299005681818</v>
+        <v>10.48610276442308</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1463778409090892</v>
+        <v>0.1355168269230749</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -11103,10 +11109,10 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>21.84537760416667</v>
+        <v>10.38168569711539</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3912346117424264</v>
+        <v>0.03109975961538325</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -11119,10 +11125,10 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>22.62479285037879</v>
+        <v>10.46762319711539</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.3881806344696948</v>
+        <v>0.1170372596153832</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -11135,10 +11141,10 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>22.20513731060606</v>
+        <v>10.32316706730769</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.03147490530303187</v>
+        <v>-0.02741887019231015</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -11154,7 +11160,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11163,111 +11169,111 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.44869883362676</v>
+        <v>15.83922456781915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>22.73446669600939</v>
+        <v>16.4478162400266</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>22.15354955252348</v>
+        <v>15.30934175531915</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5809171434859124</v>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>#63BE7B</t>
+        <v>1.138474484707448</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>T3 is warmest and T4 is coolest in this zone.</t>
+          <t>T5 is warmest and T2 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>22.32362272593897</v>
+        <v>15.30934175531915</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1250761076877893</v>
+        <v>-0.5298828125000004</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>15.49720536901596</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.3420191988031931</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>22.73446669600939</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.285767862382631</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="n">
+        <v>16.1718438331117</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.3326192652925517</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="T17" t="n">
-        <v>22.15354955252348</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.2951492811032814</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
       <c r="X17" t="n">
-        <v>22.69943423562206</v>
+        <v>16.4478162400266</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.250735401995307</v>
+        <v>0.6085916722074476</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AA17" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>22.33242095803991</v>
+        <v>15.76991564162234</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1162778755868494</v>
+        <v>-0.0693089261968094</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -11283,7 +11289,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11292,47 +11298,47 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28.24799262152778</v>
+        <v>26.46574609375</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>27.3671484375</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>28.89122178819444</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
       <c r="G18" t="n">
-        <v>27.84138093171296</v>
+        <v>25.7880859375</v>
       </c>
       <c r="H18" t="n">
-        <v>1.049840856481481</v>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>#FFEB84</t>
+        <v>1.579062499999999</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>T3 is warmest and T2 is coolest in this zone.</t>
+          <t>T5 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.84138093171296</v>
+        <v>26.42771484375</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4066116898148167</v>
+        <v>-0.03803124999999952</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -11345,58 +11351,58 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>28.89122178819444</v>
+        <v>25.7880859375</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6432291666666643</v>
+        <v>-0.6776601562499991</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>26.453671875</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.01207421874999781</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>27.3671484375</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.9014023437500001</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>hotspot</t>
         </is>
       </c>
-      <c r="S18" s="6" t="inlineStr">
+      <c r="AA18" s="6" t="inlineStr">
         <is>
           <t>#F8696B</t>
         </is>
       </c>
-      <c r="T18" t="n">
-        <v>28.3255931712963</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.07760054976851904</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="X18" t="n">
-        <v>28.19858579282407</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-0.04940682870370594</v>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AA18" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
       <c r="AB18" t="n">
-        <v>27.98318142361111</v>
+        <v>26.292109375</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.2648111979166679</v>
+        <v>-0.1736367187500001</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -11412,7 +11418,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11421,47 +11427,47 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.19467561141304</v>
+        <v>27.06162760416667</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27.64466145833333</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>28.41015625</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
       <c r="G19" t="n">
-        <v>27.99660326086957</v>
+        <v>26.51373697916667</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4135529891304337</v>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>#63BE7B</t>
+        <v>1.130924479166669</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>T3 is warmest and T5 is coolest in this zone.</t>
+          <t>T5 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.08763586956522</v>
+        <v>27.13792317708333</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1070397418478244</v>
+        <v>0.076295572916667</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -11474,58 +11480,58 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>28.41015625</v>
+        <v>26.51373697916667</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.215480638586957</v>
+        <v>-0.5478906250000009</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>26.91458333333333</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.1470442708333337</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="T19" t="n">
-        <v>28.33793308423913</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.143257472826086</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
       <c r="X19" t="n">
-        <v>27.99660326086957</v>
+        <v>27.64466145833333</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.1980723505434767</v>
+        <v>0.5830338541666684</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AA19" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="AA19" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>28.1410495923913</v>
+        <v>27.09723307291667</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.05362601902173836</v>
+        <v>0.03560546874999915</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -11541,7 +11547,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11550,47 +11556,47 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.55716594827586</v>
+        <v>26.68500434027778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>27.77015422952586</v>
+        <v>27.11028374565972</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>27.29754849137931</v>
+        <v>26.18088107638889</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4726057381465516</v>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>#63BE7B</t>
+        <v>0.9294026692708321</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>T4 is warmest and T5 is coolest in this zone.</t>
+          <t>T5 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>27.60821322737069</v>
+        <v>26.97638617621528</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05104727909483131</v>
+        <v>0.2913818359374964</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -11603,58 +11609,58 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>27.67869410021552</v>
+        <v>26.18088107638889</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1215281519396569</v>
+        <v>-0.5041232638888928</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>26.42420789930556</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.260796440972225</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="T20" t="n">
-        <v>27.77015422952586</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.2129882812500021</v>
-      </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="n">
+        <v>27.11028374565972</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4252794053819393</v>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="W20" s="7" t="inlineStr">
+      <c r="AA20" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="X20" t="n">
-        <v>27.29754849137931</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>-0.2596174568965495</v>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AA20" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
       <c r="AB20" t="n">
-        <v>27.43121969288793</v>
+        <v>26.73326280381944</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.1259462553879267</v>
+        <v>0.04825846354166075</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -11670,7 +11676,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11679,7 +11685,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.52827555338542</v>
+        <v>24.62400350765306</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -11687,7 +11693,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>26.036865234375</v>
+        <v>25.35172193877551</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -11695,10 +11701,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>25.24886067708333</v>
+        <v>23.9987643494898</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7880045572916679</v>
+        <v>1.352957589285715</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -11716,10 +11722,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>26.036865234375</v>
+        <v>25.35172193877551</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5085896809895836</v>
+        <v>0.7277184311224509</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -11732,58 +11738,58 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>25.24886067708333</v>
+        <v>23.9987643494898</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2794148763020843</v>
+        <v>-0.6252391581632644</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>24.32790577168367</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.2960977359693864</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="W21" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="T21" t="n">
-        <v>25.42427571614583</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.1039998372395843</v>
-      </c>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="n">
+        <v>24.44174505739796</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.1822584502551017</v>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="W21" s="7" t="inlineStr">
+      <c r="AA21" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="X21" t="n">
-        <v>25.34897867838542</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>-0.1792968749999986</v>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AA21" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
       <c r="AB21" t="n">
-        <v>25.5823974609375</v>
+        <v>24.99988042091837</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.05412190755208357</v>
+        <v>0.375876913265305</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -11799,7 +11805,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11808,7 +11814,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.71220175253378</v>
+        <v>21.05263893821023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -11816,39 +11822,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>22.29559491131757</v>
+        <v>21.95192649147727</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>20.90987911739865</v>
+        <v>20.27727716619318</v>
       </c>
       <c r="H22" t="n">
-        <v>1.385715793918919</v>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>#FFEB84</t>
+        <v>1.67464932528409</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>T2 is warmest and T4 is coolest in this zone.</t>
+          <t>T2 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>22.29559491131757</v>
+        <v>21.95192649147727</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5833931587837853</v>
+        <v>0.8992875532670439</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -11861,74 +11867,74 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>21.28576330236486</v>
+        <v>20.27727716619318</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.42643845016892</v>
+        <v>-0.775361772017046</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>coolspot</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>#4472C4</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>20.95330255681818</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.09933638139204604</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="T22" t="n">
-        <v>20.90987911739865</v>
-      </c>
-      <c r="U22" t="n">
-        <v>-0.802322635135134</v>
-      </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="n">
+        <v>20.3026123046875</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.7500266335227295</v>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>coolspot</t>
         </is>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="AA22" s="9" t="inlineStr">
         <is>
           <t>#4472C4</t>
         </is>
       </c>
-      <c r="X22" t="n">
-        <v>22.23527238175676</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.5230706292229748</v>
-      </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AB22" t="n">
+        <v>21.778076171875</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.7254372336647705</v>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>hotspot</t>
         </is>
       </c>
-      <c r="AA22" s="6" t="inlineStr">
+      <c r="AE22" s="6" t="inlineStr">
         <is>
           <t>#F8696B</t>
-        </is>
-      </c>
-      <c r="AB22" t="n">
-        <v>21.83449904983108</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.1222972972972975</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AE22" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11937,26 +11943,26 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19.36192471590909</v>
+        <v>19.18578920717593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20.30078125</v>
+        <v>19.98220486111111</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>18.09115767045455</v>
+        <v>18.44093605324074</v>
       </c>
       <c r="H23" t="n">
-        <v>2.209623579545454</v>
+        <v>1.54126880787037</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -11970,14 +11976,14 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>T5 is warmest and T4 is coolest in this zone.</t>
+          <t>T7 is warmest and T3 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>19.89169034090909</v>
+        <v>19.87210648148148</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5297656249999996</v>
+        <v>0.686317274305555</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -11990,10 +11996,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>18.7251953125</v>
+        <v>18.44093605324074</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.6367294034090918</v>
+        <v>-0.7448531539351855</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -12006,58 +12012,58 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>18.09115767045455</v>
+        <v>19.13789424189815</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.270767045454544</v>
+        <v>-0.04789496527777715</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>18.49580439814815</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-0.6899848090277771</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>coolspot</t>
         </is>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="AA23" s="9" t="inlineStr">
         <is>
           <t>#4472C4</t>
         </is>
       </c>
-      <c r="X23" t="n">
-        <v>20.30078125</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.9388565340909096</v>
-      </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AB23" t="n">
+        <v>19.98220486111111</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.7964156539351848</v>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>hotspot</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
+      <c r="AE23" s="6" t="inlineStr">
         <is>
           <t>#F8696B</t>
-        </is>
-      </c>
-      <c r="AB23" t="n">
-        <v>19.80079900568182</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.4388742897727269</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AE23" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -12066,26 +12072,26 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.59992804276316</v>
+        <v>19.01766318044355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>19.84611265120968</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>19.48482473273026</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
       <c r="G24" t="n">
-        <v>17.23269171463816</v>
+        <v>18.22352255544355</v>
       </c>
       <c r="H24" t="n">
-        <v>2.252133018092106</v>
+        <v>1.622590095766128</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -12099,14 +12105,14 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>T5 is warmest and T4 is coolest in this zone.</t>
+          <t>T7 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>19.14593184621711</v>
+        <v>19.67872668850806</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5460038034539458</v>
+        <v>0.6610635080645153</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -12119,10 +12125,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>17.85641961348684</v>
+        <v>18.35751638104839</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.7435084292763179</v>
+        <v>-0.6601467993951609</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -12135,42 +12141,42 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>17.23269171463816</v>
+        <v>18.98243762600806</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.367236328125003</v>
+        <v>-0.0352255544354847</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>18.22352255544355</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-0.7941406250000007</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>coolspot</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="AA24" s="9" t="inlineStr">
         <is>
           <t>#4472C4</t>
         </is>
       </c>
-      <c r="X24" t="n">
-        <v>19.48482473273026</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.8848966899671034</v>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>hotspot</t>
-        </is>
-      </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>#F8696B</t>
-        </is>
-      </c>
       <c r="AB24" t="n">
-        <v>19.27977230674342</v>
+        <v>19.84611265120968</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.6798442639802609</v>
+        <v>0.8284494707661274</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -12186,7 +12192,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12195,7 +12201,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.52933258310249</v>
+        <v>15.54945099133403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -12203,18 +12209,18 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>16.77396771121884</v>
+        <v>16.41107741924895</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>14.14381979310942</v>
+        <v>14.73225979845063</v>
       </c>
       <c r="H25" t="n">
-        <v>2.630147918109419</v>
+        <v>1.67881762079832</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -12228,14 +12234,14 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>T2 is warmest and T4 is coolest in this zone.</t>
+          <t>T2 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>16.77396771121884</v>
+        <v>16.41107741924895</v>
       </c>
       <c r="M25" t="n">
-        <v>1.244635128116345</v>
+        <v>0.8616264279149188</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -12248,74 +12254,74 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>14.41952692174515</v>
+        <v>15.19958803834034</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.10980566135734</v>
+        <v>-0.3498629529936963</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>15.45544331013656</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.0940076811974766</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>14.73225979845063</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-0.817191192883401</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>coolspot</t>
         </is>
       </c>
-      <c r="S25" s="9" t="inlineStr">
+      <c r="AA25" s="9" t="inlineStr">
         <is>
           <t>#4472C4</t>
         </is>
       </c>
-      <c r="T25" t="n">
-        <v>14.14381979310942</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-1.385512789993074</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>coolspot</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>#4472C4</t>
-        </is>
-      </c>
-      <c r="X25" t="n">
-        <v>15.66035102146814</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.1310184383656505</v>
-      </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AB25" t="n">
+        <v>15.9488863904937</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.3994353991596657</v>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="AA25" s="7" t="inlineStr">
+      <c r="AE25" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="AB25" t="n">
-        <v>16.64899746797091</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.119664884868422</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>hotspot</t>
-        </is>
-      </c>
-      <c r="AE25" s="6" t="inlineStr">
-        <is>
-          <t>#F8696B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12324,7 +12330,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14.03994140625</v>
+        <v>13.32757482394366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -12332,87 +12338,87 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>15.203125</v>
+        <v>14.01825209066901</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>13.226953125</v>
+        <v>12.93784386003521</v>
       </c>
       <c r="H26" t="n">
-        <v>1.976171875</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
+        <v>1.080408230633802</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T4 is coolest in this zone.</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>14.01825209066901</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.6906772667253538</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>#F8696B</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>T2 is warmest and T3 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>15.203125</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.16318359375</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>hotspot</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>#F8696B</t>
-        </is>
-      </c>
       <c r="P26" t="n">
-        <v>13.226953125</v>
+        <v>13.26171875</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.81298828125</v>
+        <v>-0.06585607394366022</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>coolspot</t>
-        </is>
-      </c>
-      <c r="S26" s="9" t="inlineStr">
-        <is>
-          <t>#4472C4</t>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>13.240234375</v>
+        <v>12.93784386003521</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7997070312499996</v>
+        <v>-0.3897309639084483</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>coolspot</t>
-        </is>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>#4472C4</t>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>13.610302734375</v>
+        <v>12.95212092869718</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.4296386718749989</v>
+        <v>-0.3754538952464763</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -12425,26 +12431,26 @@
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>14.919091796875</v>
+        <v>13.4679384903169</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.879150390625</v>
+        <v>0.1403636663732417</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>hotspot</t>
-        </is>
-      </c>
-      <c r="AE26" s="6" t="inlineStr">
-        <is>
-          <t>#F8696B</t>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE26" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -12453,7 +12459,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.20852864583333</v>
+        <v>13.884716796875</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -12461,87 +12467,87 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15.365234375</v>
+        <v>14.614990234375</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>13.37890625</v>
+        <v>13.44921875</v>
       </c>
       <c r="H27" t="n">
-        <v>1.986328125</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
+        <v>1.165771484375</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2 is warmest and T5 is coolest in this zone.</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>14.614990234375</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.7302734374999993</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>#F8696B</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>T2 is warmest and T4 is coolest in this zone.</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>15.365234375</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.156705729166669</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>hotspot</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>#F8696B</t>
-        </is>
-      </c>
       <c r="P27" t="n">
-        <v>13.4091796875</v>
+        <v>13.8203125</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.7993489583333311</v>
+        <v>-0.06440429687500071</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>coolspot</t>
-        </is>
-      </c>
-      <c r="S27" s="9" t="inlineStr">
-        <is>
-          <t>#4472C4</t>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>13.37890625</v>
+        <v>13.5830078125</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8296223958333311</v>
+        <v>-0.3017089843750007</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>coolspot</t>
-        </is>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>#4472C4</t>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>13.83072916666667</v>
+        <v>13.44921875</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.377799479166665</v>
+        <v>-0.4354980468750007</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -12554,26 +12560,26 @@
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>15.05859375</v>
+        <v>13.9560546875</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.8500651041666689</v>
+        <v>0.07133789062499929</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>hotspot</t>
-        </is>
-      </c>
-      <c r="AE27" s="6" t="inlineStr">
-        <is>
-          <t>#F8696B</t>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AE27" s="7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12582,7 +12588,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.113425925925926</v>
+        <v>14.15682942708333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -12590,103 +12596,103 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.28443287037037</v>
+        <v>14.8212890625</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1.990668402777778</v>
+        <v>13.75045572916667</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2937644675925926</v>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>#63BE7B</t>
+        <v>1.070833333333333</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>T2 is warmest and T4 is coolest in this zone.</t>
+          <t>T2 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28443287037037</v>
+        <v>14.8212890625</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1710069444444442</v>
+        <v>0.6644596354166659</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>14.09332682291667</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.06350260416666664</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="P28" t="n">
-        <v>1.99609375</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-0.117332175925926</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="n">
+        <v>13.87932942708333</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.2775000000000016</v>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="W28" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="T28" t="n">
-        <v>1.990668402777778</v>
-      </c>
-      <c r="U28" t="n">
-        <v>-0.1227575231481484</v>
-      </c>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="n">
+        <v>13.75045572916667</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-0.406373697916667</v>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="W28" s="7" t="inlineStr">
+      <c r="AA28" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="X28" t="n">
-        <v>2.058702256944445</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>-0.0547236689814814</v>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AA28" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
       <c r="AB28" t="n">
-        <v>2.237232349537037</v>
+        <v>14.23974609375</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.1238064236111112</v>
+        <v>0.08291666666666586</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -12702,7 +12708,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12711,7 +12717,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>14.44357096354167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -12719,103 +12725,103 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>15.046875</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>14.08349609375</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>#63BE7B</t>
+        <v>0.96337890625</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>#FFEB84</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>T2 is warmest and T2 is coolest in this zone.</t>
+          <t>T2 is warmest and T5 is coolest in this zone.</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>15.046875</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.6033040364583311</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t>hotspot</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>#F8696B</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>14.37972005208333</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.06385091145833499</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="n">
+        <v>14.16609700520833</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-0.277473958333335</v>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="W29" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="n">
+        <v>14.08349609375</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.3600748697916689</v>
+      </c>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
       </c>
-      <c r="W29" s="7" t="inlineStr">
+      <c r="AA29" s="7" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="AA29" s="7" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>14.54166666666667</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>0.09809570312499716</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -12835,6 +12841,1218 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Quality-linked parameter comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>quality_0_not_good_1_good</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>chocolate</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>protocol_duration_s</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>viscosity_ratio_mean_rx1rx2</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>crystallization_onset_minus_deposition_mean_s</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>detachment_onset_minus_deposition_mean_s</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_minus_deposition_mean_s</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>complete_detachment_channels</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>complete_before_demoulding_channels</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>mean_change_points_until_offset_or_last</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>mean_product_delta_vs_reference_C</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>mean_hotspot_spread_C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Milk</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1869</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3752599114208275</v>
+      </c>
+      <c r="G3" t="n">
+        <v>344</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1144</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1470.29220187664</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rx1Tx1, Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Rx1Tx1, Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.342393165207788</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>New Cooling Configuration</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Milk</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2214</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.363644774310466</v>
+      </c>
+      <c r="G4" t="n">
+        <v>343</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1171</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1788.490580201149</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rx1Tx1, Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Rx1Tx1, Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.8018543671750219</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.23716366640188</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>comparison_minus_reference</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>viscosity_ratio_mean_rx1rx2: -0.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>comparison_minus_reference</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>crystallization_onset_minus_deposition_mean_s: -1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>comparison_minus_reference</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>detachment_onset_minus_deposition_mean_s: 27.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>comparison_minus_reference</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>detachment_offset_minus_deposition_mean_s: 318.198</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>comparison_minus_reference</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean_change_points_until_offset_or_last: 0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>comparison_minus_reference</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mean_hotspot_spread_C: -0.105</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>T7-corrected ultrasound viscosity ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>signal_column</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>deposition_s</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>pre_deposition_window_s</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>post_deposition_window_s</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>pre_deposition_us_level</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>post_50s_us_level</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>viscosity_ratio_channel</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>viscosity_ratio_mean_rx1rx2</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rx1Tx1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rx1Tx1_tc</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>286</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>336.0-341.0</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9886593692731603</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3397804961059535</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3436780216382841</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3752599114208275</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>median(T-corrected US 50-55 s after deposition) / median(T-corrected US 5 s before deposition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rx2Tx2_tc</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>286</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>336.0-341.0</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8195161085032753</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3334134096986497</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.406841801203371</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3752599114208275</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>median(T-corrected US 50-55 s after deposition) / median(T-corrected US 5 s before deposition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rx1Tx1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Rx1Tx1_tc</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>284</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>334.0-339.0</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9854422053609572</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3148687546001829</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3195202650010812</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.363644774310466</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>median(T-corrected US 50-55 s after deposition) / median(T-corrected US 5 s before deposition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Rx2Tx2_tc</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>284</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>334.0-339.0</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8087176470762016</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3297702155989941</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4077692836198509</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.363644774310466</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>median(T-corrected US 50-55 s after deposition) / median(T-corrected US 5 s before deposition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Detachment homogeneity</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>channels_evaluated</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>channels_complete</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>complete_channels</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>both_primary_channels_complete</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>all_complete_before_demoulding</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>detachment_onset_spread_s</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_spread_s</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>detachment_duration_spread_s</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>mean_change_points_until_offset_or_last</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>homogeneity_reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Rx1Tx1, Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.980263471603394</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.980263471603394</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>homogeneous complete detachment</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Rx1Tx1, Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.000029802322388</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.000029802322388</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>homogeneous complete detachment</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Per-channel detachment decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>signal_column</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>signal_basis</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>deposition_s</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>crystallization_onset_s</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_onset_s</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>analysis_window_end_s</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_s</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_status</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_zone</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>demoulding_twisting_start_s</t>
+        </is>
+      </c>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
+          <t>complete_detachment_before_demoulding</t>
+        </is>
+      </c>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_offset_s</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_minus_deposition_s</t>
+        </is>
+      </c>
+      <c r="P28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_onset_minus_deposition_s</t>
+        </is>
+      </c>
+      <c r="Q28" s="1" t="inlineStr">
+        <is>
+          <t>crystallization_onset_minus_deposition_s</t>
+        </is>
+      </c>
+      <c r="R28" s="1" t="inlineStr">
+        <is>
+          <t>reference_us_level</t>
+        </is>
+      </c>
+      <c r="S28" s="1" t="inlineStr">
+        <is>
+          <t>threshold_10pct_lower</t>
+        </is>
+      </c>
+      <c r="T28" s="1" t="inlineStr">
+        <is>
+          <t>us_level_at_decision</t>
+        </is>
+      </c>
+      <c r="U28" s="1" t="inlineStr">
+        <is>
+          <t>change_points_detected_total</t>
+        </is>
+      </c>
+      <c r="V28" s="1" t="inlineStr">
+        <is>
+          <t>change_points_until_detachment_or_last</t>
+        </is>
+      </c>
+      <c r="W28" s="1" t="inlineStr">
+        <is>
+          <t>pattern_description</t>
+        </is>
+      </c>
+      <c r="X28" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="Y28" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rx1Tx1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rx1Tx1_tc</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>T7 temperature-normalized ultrasound; channel_tc = raw / polynomial(T7)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>284</v>
+      </c>
+      <c r="F29" t="n">
+        <v>628</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1454</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2213.480570077896</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2073.480711936951</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>complete_detachment_for_channel</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>2118</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>619.4807119369507</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1789.480711936951</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1170</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>344</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.9854422053609572</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.8868979848248615</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.9387736268774387</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 2073.5s.</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>aa3_trials_experimental_summary.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rx2Tx2_tc</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>T7 temperature-normalized ultrasound; channel_tc = raw / polynomial(T7)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>284</v>
+      </c>
+      <c r="F30" t="n">
+        <v>626</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1456</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2213.480570077896</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2071.500448465347</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>complete_detachment_for_channel</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2118</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>615.5004484653473</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1787.500448465347</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1172</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>342</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.8087176470762016</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.7278458823685815</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.82536306643459</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>3 positive upward change point(s) from detachment onset to run end. First complete offset at 2071.5s.</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>aa3_trials_experimental_summary.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rx1Tx1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rx1Tx1_tc</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>T7 temperature-normalized ultrasound; channel_tc = raw / polynomial(T7)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>286</v>
+      </c>
+      <c r="F31" t="n">
+        <v>630</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1430</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1868.234316587448</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1755.292186975479</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>complete_detachment_for_channel</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1792</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>325.2921869754791</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1469.292186975479</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1144</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>344</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.9886593692731603</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.8897934323458443</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.9108031549980742</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 1755.3s.</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>aa3_trials_experimental_summary.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>reference_2291-4160</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rx2Tx2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rx2Tx2_tc</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>T7 temperature-normalized ultrasound; channel_tc = raw / polynomial(T7)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>286</v>
+      </c>
+      <c r="F32" t="n">
+        <v>630</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1430</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1868.234316587448</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1757.292216777802</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>complete_detachment_for_channel</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1792</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>327.2922167778015</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1471.292216777802</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1144</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>344</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.8195161085032753</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.7375644976529477</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.8063564620894778</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 1757.3s.</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>aa3_trials_experimental_summary.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12927,7 +14145,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -12936,25 +14154,25 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.5085896809895836</v>
+        <v>0.7277184311224509</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.2794148763020843</v>
+        <v>-0.6252391581632644</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.1039998372395843</v>
+        <v>-0.2960977359693864</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.1792968749999986</v>
+        <v>-0.1822584502551017</v>
       </c>
       <c r="G104" t="n">
-        <v>0.05412190755208357</v>
+        <v>0.375876913265305</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12963,25 +14181,25 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.5833931587837853</v>
+        <v>0.8992875532670439</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.42643845016892</v>
+        <v>-0.775361772017046</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.802322635135134</v>
+        <v>-0.09933638139204604</v>
       </c>
       <c r="F105" t="n">
-        <v>0.5230706292229748</v>
+        <v>-0.7500266335227295</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1222972972972975</v>
+        <v>0.7254372336647705</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12990,25 +14208,25 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.5297656249999996</v>
+        <v>0.686317274305555</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.6367294034090918</v>
+        <v>-0.7448531539351855</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.270767045454544</v>
+        <v>-0.04789496527777715</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9388565340909096</v>
+        <v>-0.6899848090277771</v>
       </c>
       <c r="G106" t="n">
-        <v>0.4388742897727269</v>
+        <v>0.7964156539351848</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -13017,25 +14235,25 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.5460038034539458</v>
+        <v>0.6610635080645153</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.7435084292763179</v>
+        <v>-0.6601467993951609</v>
       </c>
       <c r="E107" t="n">
-        <v>-1.367236328125003</v>
+        <v>-0.0352255544354847</v>
       </c>
       <c r="F107" t="n">
-        <v>0.8848966899671034</v>
+        <v>-0.7941406250000007</v>
       </c>
       <c r="G107" t="n">
-        <v>0.6798442639802609</v>
+        <v>0.8284494707661274</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -13044,25 +14262,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1.156705729166669</v>
+        <v>0.7302734374999993</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.7993489583333311</v>
+        <v>-0.06440429687500071</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.8296223958333311</v>
+        <v>-0.3017089843750007</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.377799479166665</v>
+        <v>-0.4354980468750007</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8500651041666689</v>
+        <v>0.07133789062499929</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -13071,25 +14289,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.1710069444444442</v>
+        <v>0.6644596354166659</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.117332175925926</v>
+        <v>-0.06350260416666664</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.1227575231481484</v>
+        <v>-0.2775000000000016</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.0547236689814814</v>
+        <v>-0.406373697916667</v>
       </c>
       <c r="G109" t="n">
-        <v>0.1238064236111112</v>
+        <v>0.08291666666666586</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -13098,25 +14316,25 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-0.4066116898148167</v>
+        <v>-0.03803124999999952</v>
       </c>
       <c r="D110" t="n">
-        <v>0.6432291666666643</v>
+        <v>-0.6776601562499991</v>
       </c>
       <c r="E110" t="n">
-        <v>0.07760054976851904</v>
+        <v>-0.01207421874999781</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.04940682870370594</v>
+        <v>0.9014023437500001</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.2648111979166679</v>
+        <v>-0.1736367187500001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -13125,25 +14343,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>0.6033040364583311</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>-0.06385091145833499</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>-0.277473958333335</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>-0.3600748697916689</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>0.09809570312499716</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -13152,25 +14370,25 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.244635128116345</v>
+        <v>0.8616264279149188</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.10980566135734</v>
+        <v>-0.3498629529936963</v>
       </c>
       <c r="E112" t="n">
-        <v>-1.385512789993074</v>
+        <v>-0.0940076811974766</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1310184383656505</v>
+        <v>-0.817191192883401</v>
       </c>
       <c r="G112" t="n">
-        <v>1.119664884868422</v>
+        <v>0.3994353991596657</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -13179,25 +14397,25 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-0.1250761076877893</v>
+        <v>-0.5298828125000004</v>
       </c>
       <c r="D113" t="n">
-        <v>0.285767862382631</v>
+        <v>-0.3420191988031931</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.2951492811032814</v>
+        <v>0.3326192652925517</v>
       </c>
       <c r="F113" t="n">
-        <v>0.250735401995307</v>
+        <v>0.6085916722074476</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.1162778755868494</v>
+        <v>-0.0693089261968094</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -13206,25 +14424,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-0.1118489583333364</v>
+        <v>-0.2562349759615401</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1463778409090892</v>
+        <v>0.1355168269230749</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.3912346117424264</v>
+        <v>0.03109975961538325</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3881806344696948</v>
+        <v>0.1170372596153832</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.03147490530303187</v>
+        <v>-0.02741887019231015</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13233,25 +14451,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.16318359375</v>
+        <v>0.6906772667253538</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.81298828125</v>
+        <v>-0.06585607394366022</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.7997070312499996</v>
+        <v>-0.3897309639084483</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.4296386718749989</v>
+        <v>-0.3754538952464763</v>
       </c>
       <c r="G115" t="n">
-        <v>0.879150390625</v>
+        <v>0.1403636663732417</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13260,25 +14478,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.05104727909483131</v>
+        <v>0.2913818359374964</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1215281519396569</v>
+        <v>-0.5041232638888928</v>
       </c>
       <c r="E116" t="n">
-        <v>0.2129882812500021</v>
+        <v>-0.260796440972225</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.2596174568965495</v>
+        <v>0.4252794053819393</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.1259462553879267</v>
+        <v>0.04825846354166075</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>old-configuration</t>
+          <t>17_3_f_m_aa3-25_06_26-2160-4374s</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13287,19 +14505,19 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-0.1070397418478244</v>
+        <v>0.076295572916667</v>
       </c>
       <c r="D117" t="n">
-        <v>0.215480638586957</v>
+        <v>-0.5478906250000009</v>
       </c>
       <c r="E117" t="n">
-        <v>0.143257472826086</v>
+        <v>-0.1470442708333337</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.1980723505434767</v>
+        <v>0.5830338541666684</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.05362601902173836</v>
+        <v>0.03560546874999915</v>
       </c>
     </row>
     <row r="118">

--- a/outputs/aasted3_run_comparison/summary/aasted3_reference_based_comparison_summary.xlsx
+++ b/outputs/aasted3_run_comparison/summary/aasted3_reference_based_comparison_summary.xlsx
@@ -12846,7 +12846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:AF32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12856,24 +12856,31 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="34" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="34" customWidth="1" min="29" max="29"/>
+    <col width="21" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13578,90 +13585,125 @@
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
+          <t>analysis_domain</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>analysis_window_start_s</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
           <t>analysis_window_end_s</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>first_change_point_s</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>first_change_point_after_onset_s</t>
+        </is>
+      </c>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
+          <t>first_change_point_zone</t>
+        </is>
+      </c>
+      <c r="N28" s="1" t="inlineStr">
         <is>
           <t>detachment_offset_s</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="O28" s="1" t="inlineStr">
         <is>
           <t>detachment_offset_status</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
+      <c r="P28" s="1" t="inlineStr">
         <is>
           <t>detachment_offset_zone</t>
         </is>
       </c>
-      <c r="L28" s="1" t="inlineStr">
+      <c r="Q28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_zone_start_s</t>
+        </is>
+      </c>
+      <c r="R28" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_zone_end_s</t>
+        </is>
+      </c>
+      <c r="S28" s="1" t="inlineStr">
         <is>
           <t>demoulding_twisting_start_s</t>
         </is>
       </c>
-      <c r="M28" s="1" t="inlineStr">
+      <c r="T28" s="1" t="inlineStr">
         <is>
           <t>complete_detachment_before_demoulding</t>
         </is>
       </c>
-      <c r="N28" s="1" t="inlineStr">
+      <c r="U28" s="1" t="inlineStr">
         <is>
           <t>detachment_onset_to_offset_s</t>
         </is>
       </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="V28" s="1" t="inlineStr">
         <is>
           <t>detachment_offset_minus_deposition_s</t>
         </is>
       </c>
-      <c r="P28" s="1" t="inlineStr">
+      <c r="W28" s="1" t="inlineStr">
         <is>
           <t>detachment_onset_minus_deposition_s</t>
         </is>
       </c>
-      <c r="Q28" s="1" t="inlineStr">
+      <c r="X28" s="1" t="inlineStr">
         <is>
           <t>crystallization_onset_minus_deposition_s</t>
         </is>
       </c>
-      <c r="R28" s="1" t="inlineStr">
+      <c r="Y28" s="1" t="inlineStr">
         <is>
           <t>reference_us_level</t>
         </is>
       </c>
-      <c r="S28" s="1" t="inlineStr">
+      <c r="Z28" s="1" t="inlineStr">
         <is>
           <t>threshold_10pct_lower</t>
         </is>
       </c>
-      <c r="T28" s="1" t="inlineStr">
+      <c r="AA28" s="1" t="inlineStr">
         <is>
           <t>us_level_at_decision</t>
         </is>
       </c>
-      <c r="U28" s="1" t="inlineStr">
+      <c r="AB28" s="1" t="inlineStr">
         <is>
           <t>change_points_detected_total</t>
         </is>
       </c>
-      <c r="V28" s="1" t="inlineStr">
+      <c r="AC28" s="1" t="inlineStr">
         <is>
           <t>change_points_until_detachment_or_last</t>
         </is>
       </c>
-      <c r="W28" s="1" t="inlineStr">
+      <c r="AD28" s="1" t="inlineStr">
         <is>
           <t>pattern_description</t>
         </is>
       </c>
-      <c r="X28" s="1" t="inlineStr">
+      <c r="AE28" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="Y28" s="1" t="inlineStr">
+      <c r="AF28" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
@@ -13697,66 +13739,91 @@
       <c r="G29" t="n">
         <v>1454</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1454</v>
+      </c>
+      <c r="J29" t="n">
         <v>2213.480570077896</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
+        <v>1533.480596780777</v>
+      </c>
+      <c r="L29" t="n">
+        <v>79.48059678077652</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
         <v>2073.480711936951</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>complete_detachment_for_channel</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>transition_2</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="Q29" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R29" t="n">
         <v>2118</v>
       </c>
-      <c r="M29" t="n">
+      <c r="S29" t="n">
+        <v>2118</v>
+      </c>
+      <c r="T29" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="n">
+      <c r="U29" t="n">
         <v>619.4807119369507</v>
       </c>
-      <c r="O29" t="n">
+      <c r="V29" t="n">
         <v>1789.480711936951</v>
       </c>
-      <c r="P29" t="n">
+      <c r="W29" t="n">
         <v>1170</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="X29" t="n">
         <v>344</v>
       </c>
-      <c r="R29" t="n">
+      <c r="Y29" t="n">
         <v>0.9854422053609572</v>
       </c>
-      <c r="S29" t="n">
+      <c r="Z29" t="n">
         <v>0.8868979848248615</v>
       </c>
-      <c r="T29" t="n">
+      <c r="AA29" t="n">
         <v>0.9387736268774387</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AB29" t="n">
         <v>2</v>
       </c>
-      <c r="V29" t="n">
+      <c r="AC29" t="n">
         <v>2</v>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 2073.5s.</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>aa3_trials_experimental_summary.xlsx</t>
         </is>
@@ -13792,66 +13859,91 @@
       <c r="G30" t="n">
         <v>1456</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1456</v>
+      </c>
+      <c r="J30" t="n">
         <v>2213.480570077896</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
+        <v>1517.48148560524</v>
+      </c>
+      <c r="L30" t="n">
+        <v>61.48148560523987</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
         <v>2071.500448465347</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>complete_detachment_for_channel</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>transition_2</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="Q30" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R30" t="n">
         <v>2118</v>
       </c>
-      <c r="M30" t="n">
+      <c r="S30" t="n">
+        <v>2118</v>
+      </c>
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
+      <c r="U30" t="n">
         <v>615.5004484653473</v>
       </c>
-      <c r="O30" t="n">
+      <c r="V30" t="n">
         <v>1787.500448465347</v>
       </c>
-      <c r="P30" t="n">
+      <c r="W30" t="n">
         <v>1172</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="X30" t="n">
         <v>342</v>
       </c>
-      <c r="R30" t="n">
+      <c r="Y30" t="n">
         <v>0.8087176470762016</v>
       </c>
-      <c r="S30" t="n">
+      <c r="Z30" t="n">
         <v>0.7278458823685815</v>
       </c>
-      <c r="T30" t="n">
+      <c r="AA30" t="n">
         <v>0.82536306643459</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AB30" t="n">
         <v>3</v>
       </c>
-      <c r="V30" t="n">
+      <c r="AC30" t="n">
         <v>3</v>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>3 positive upward change point(s) from detachment onset to run end. First complete offset at 2071.5s.</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>aa3_trials_experimental_summary.xlsx</t>
         </is>
@@ -13887,66 +13979,91 @@
       <c r="G31" t="n">
         <v>1430</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1430</v>
+      </c>
+      <c r="J31" t="n">
         <v>1868.234316587448</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
+        <v>1523.292253017426</v>
+      </c>
+      <c r="L31" t="n">
+        <v>93.29225301742554</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
         <v>1755.292186975479</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>complete_detachment_for_channel</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>transition_2</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="Q31" t="n">
+        <v>1629</v>
+      </c>
+      <c r="R31" t="n">
         <v>1792</v>
       </c>
-      <c r="M31" t="n">
+      <c r="S31" t="n">
+        <v>1792</v>
+      </c>
+      <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
+      <c r="U31" t="n">
         <v>325.2921869754791</v>
       </c>
-      <c r="O31" t="n">
+      <c r="V31" t="n">
         <v>1469.292186975479</v>
       </c>
-      <c r="P31" t="n">
+      <c r="W31" t="n">
         <v>1144</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="X31" t="n">
         <v>344</v>
       </c>
-      <c r="R31" t="n">
+      <c r="Y31" t="n">
         <v>0.9886593692731603</v>
       </c>
-      <c r="S31" t="n">
+      <c r="Z31" t="n">
         <v>0.8897934323458443</v>
       </c>
-      <c r="T31" t="n">
+      <c r="AA31" t="n">
         <v>0.9108031549980742</v>
       </c>
-      <c r="U31" t="n">
+      <c r="AB31" t="n">
         <v>2</v>
       </c>
-      <c r="V31" t="n">
+      <c r="AC31" t="n">
         <v>2</v>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 1755.3s.</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>aa3_trials_experimental_summary.xlsx</t>
         </is>
@@ -13982,66 +14099,91 @@
       <c r="G32" t="n">
         <v>1430</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1430</v>
+      </c>
+      <c r="J32" t="n">
         <v>1868.234316587448</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
+        <v>1643.292067527771</v>
+      </c>
+      <c r="L32" t="n">
+        <v>213.292067527771</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
         <v>1757.292216777802</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>complete_detachment_for_channel</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>transition_2</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="Q32" t="n">
+        <v>1629</v>
+      </c>
+      <c r="R32" t="n">
         <v>1792</v>
       </c>
-      <c r="M32" t="n">
+      <c r="S32" t="n">
+        <v>1792</v>
+      </c>
+      <c r="T32" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="n">
+      <c r="U32" t="n">
         <v>327.2922167778015</v>
       </c>
-      <c r="O32" t="n">
+      <c r="V32" t="n">
         <v>1471.292216777802</v>
       </c>
-      <c r="P32" t="n">
+      <c r="W32" t="n">
         <v>1144</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="X32" t="n">
         <v>344</v>
       </c>
-      <c r="R32" t="n">
+      <c r="Y32" t="n">
         <v>0.8195161085032753</v>
       </c>
-      <c r="S32" t="n">
+      <c r="Z32" t="n">
         <v>0.7375644976529477</v>
       </c>
-      <c r="T32" t="n">
+      <c r="AA32" t="n">
         <v>0.8063564620894778</v>
       </c>
-      <c r="U32" t="n">
+      <c r="AB32" t="n">
         <v>2</v>
       </c>
-      <c r="V32" t="n">
+      <c r="AC32" t="n">
         <v>2</v>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 1757.3s.</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>aa3_trials_experimental_summary.xlsx</t>
         </is>

--- a/outputs/aasted3_run_comparison/summary/aasted3_reference_based_comparison_summary.xlsx
+++ b/outputs/aasted3_run_comparison/summary/aasted3_reference_based_comparison_summary.xlsx
@@ -13064,7 +13064,7 @@
         <v>2.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8018543671750219</v>
+        <v>-0.8066211997382844</v>
       </c>
       <c r="N4" t="n">
         <v>1.23716366640188</v>
